--- a/performance.xlsx
+++ b/performance.xlsx
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.476274162530899</v>
+        <v>0.6678383350372314</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5465729236602783</v>
+        <v>0.7592267394065857</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6748681664466858</v>
+        <v>0.7557117938995361</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.731107234954834</v>
+        <v>0.7328646779060364</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7521968483924866</v>
+        <v>0.7346221208572388</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7574692368507385</v>
+        <v>0.7363796234130859</v>
       </c>
     </row>
     <row r="8">
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7680140733718872</v>
+        <v>0.7293497323989868</v>
       </c>
     </row>
     <row r="9">
@@ -513,7 +513,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7750439643859863</v>
+        <v>0.7328646779060364</v>
       </c>
     </row>
     <row r="10">
@@ -524,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7873462438583374</v>
+        <v>0.7346221208572388</v>
       </c>
     </row>
     <row r="11">
@@ -535,7 +535,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7820737957954407</v>
+        <v>0.7381370663642883</v>
       </c>
     </row>
     <row r="12">
@@ -546,7 +546,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7838312983512878</v>
+        <v>0.7363796234130859</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7873462438583374</v>
+        <v>0.7398945689201355</v>
       </c>
     </row>
     <row r="14">
@@ -568,7 +568,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7873462438583374</v>
+        <v>0.7434095144271851</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7873462438583374</v>
+        <v>0.748681902885437</v>
       </c>
     </row>
     <row r="16">
@@ -590,7 +590,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.790861189365387</v>
+        <v>0.753954291343689</v>
       </c>
     </row>
     <row r="17">
@@ -601,7 +601,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7926186323165894</v>
+        <v>0.7557117938995361</v>
       </c>
     </row>
     <row r="18">
@@ -612,7 +612,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7943760752677917</v>
+        <v>0.7592267394065857</v>
       </c>
     </row>
     <row r="19">
@@ -623,7 +623,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7943760752677917</v>
+        <v>0.7592267394065857</v>
       </c>
     </row>
     <row r="20">
@@ -634,7 +634,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7978910207748413</v>
+        <v>0.7592267394065857</v>
       </c>
     </row>
     <row r="21">
@@ -645,7 +645,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0.803163468837738</v>
+        <v>0.7820737957954407</v>
       </c>
     </row>
     <row r="22">
@@ -656,7 +656,7 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.80843585729599</v>
+        <v>0.7891036868095398</v>
       </c>
     </row>
     <row r="23">
@@ -667,7 +667,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8137082457542419</v>
+        <v>0.7926186323165894</v>
       </c>
     </row>
     <row r="24">
@@ -678,7 +678,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8154657483100891</v>
+        <v>0.7926186323165894</v>
       </c>
     </row>
     <row r="25">
@@ -689,7 +689,7 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8154657483100891</v>
+        <v>0.7996485233306885</v>
       </c>
     </row>
     <row r="26">
@@ -700,7 +700,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8189806938171387</v>
+        <v>0.8014059662818909</v>
       </c>
     </row>
     <row r="27">
@@ -711,7 +711,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8224955797195435</v>
+        <v>0.7978910207748413</v>
       </c>
     </row>
     <row r="28">
@@ -722,7 +722,7 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8207381367683411</v>
+        <v>0.7996485233306885</v>
       </c>
     </row>
     <row r="29">
@@ -733,7 +733,7 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8189806938171387</v>
+        <v>0.7943760752677917</v>
       </c>
     </row>
     <row r="30">
@@ -744,7 +744,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8189806938171387</v>
+        <v>0.7943760752677917</v>
       </c>
     </row>
     <row r="31">
@@ -755,7 +755,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8172231912612915</v>
+        <v>0.7926186323165894</v>
       </c>
     </row>
     <row r="32">
@@ -766,7 +766,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>0.826010525226593</v>
+        <v>0.790861189365387</v>
       </c>
     </row>
     <row r="33">
@@ -777,7 +777,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8242530822753906</v>
+        <v>0.7926186323165894</v>
       </c>
     </row>
     <row r="34">
@@ -788,7 +788,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8295254707336426</v>
+        <v>0.7978910207748413</v>
       </c>
     </row>
     <row r="35">
@@ -799,7 +799,7 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8295254707336426</v>
+        <v>0.7978910207748413</v>
       </c>
     </row>
     <row r="36">
@@ -810,7 +810,7 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8277680277824402</v>
+        <v>0.7961335778236389</v>
       </c>
     </row>
     <row r="37">
@@ -821,7 +821,7 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.7961335778236389</v>
       </c>
     </row>
     <row r="38">
@@ -832,7 +832,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8242530822753906</v>
+        <v>0.7961335778236389</v>
       </c>
     </row>
     <row r="39">
@@ -843,7 +843,7 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8207381367683411</v>
+        <v>0.8014059662818909</v>
       </c>
     </row>
     <row r="40">
@@ -854,7 +854,7 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8224955797195435</v>
+        <v>0.8014059662818909</v>
       </c>
     </row>
     <row r="41">
@@ -865,7 +865,7 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8207381367683411</v>
+        <v>0.8049209117889404</v>
       </c>
     </row>
     <row r="42">
@@ -876,7 +876,7 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8224955797195435</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="43">
@@ -887,7 +887,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8224955797195435</v>
+        <v>0.80843585729599</v>
       </c>
     </row>
     <row r="44">
@@ -898,7 +898,7 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8242530822753906</v>
+        <v>0.8101933002471924</v>
       </c>
     </row>
     <row r="45">
@@ -909,7 +909,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>0.826010525226593</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="46">
@@ -920,7 +920,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8242530822753906</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="47">
@@ -931,7 +931,7 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>0.826010525226593</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="48">
@@ -942,7 +942,7 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>0.826010525226593</v>
+        <v>0.8137082457542419</v>
       </c>
     </row>
     <row r="49">
@@ -953,7 +953,7 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>0.826010525226593</v>
+        <v>0.8154657483100891</v>
       </c>
     </row>
     <row r="50">
@@ -964,7 +964,7 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8295254707336426</v>
+        <v>0.8172231912612915</v>
       </c>
     </row>
     <row r="51">
@@ -975,7 +975,7 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8295254707336426</v>
+        <v>0.8172231912612915</v>
       </c>
     </row>
     <row r="52">
@@ -986,7 +986,7 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8312829732894897</v>
+        <v>0.8172231912612915</v>
       </c>
     </row>
     <row r="53">
@@ -997,7 +997,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8312829732894897</v>
+        <v>0.8189806938171387</v>
       </c>
     </row>
     <row r="54">
@@ -1008,7 +1008,7 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8295254707336426</v>
+        <v>0.8224955797195435</v>
       </c>
     </row>
     <row r="55">
@@ -1019,7 +1019,7 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8242530822753906</v>
       </c>
     </row>
     <row r="56">
@@ -1030,7 +1030,7 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.826010525226593</v>
       </c>
     </row>
     <row r="57">
@@ -1041,7 +1041,7 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8312829732894897</v>
+        <v>0.8295254707336426</v>
       </c>
     </row>
     <row r="58">
@@ -1063,7 +1063,7 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8312829732894897</v>
       </c>
     </row>
     <row r="60">
@@ -1074,7 +1074,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8312829732894897</v>
       </c>
     </row>
     <row r="61">
@@ -1085,7 +1085,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8295254707336426</v>
       </c>
     </row>
     <row r="62">
@@ -1096,7 +1096,7 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8330404162406921</v>
       </c>
     </row>
     <row r="63">
@@ -1107,7 +1107,7 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="64">
@@ -1118,7 +1118,7 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8383128046989441</v>
       </c>
     </row>
     <row r="65">
@@ -1129,7 +1129,7 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="66">
@@ -1140,7 +1140,7 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8383128046989441</v>
       </c>
     </row>
     <row r="67">
@@ -1151,7 +1151,7 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="68">
@@ -1162,7 +1162,7 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="69">
@@ -1184,7 +1184,7 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8347979187965393</v>
       </c>
     </row>
     <row r="71">
@@ -1195,7 +1195,7 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="72">
@@ -1206,7 +1206,7 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="73">
@@ -1217,7 +1217,7 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="74">
@@ -1228,7 +1228,7 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="75">
@@ -1250,7 +1250,7 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8383128046989441</v>
       </c>
     </row>
     <row r="77">
@@ -1261,7 +1261,7 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="78">
@@ -1272,7 +1272,7 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="79">
@@ -1283,7 +1283,7 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="80">
@@ -1294,7 +1294,7 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>0.8312829732894897</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="81">
@@ -1305,7 +1305,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8312829732894897</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="82">
@@ -1316,7 +1316,7 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="83">
@@ -1327,7 +1327,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="84">
@@ -1338,7 +1338,7 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="85">
@@ -1349,7 +1349,7 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="86">
@@ -1360,7 +1360,7 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="87">
@@ -1371,7 +1371,7 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="88">
@@ -1382,7 +1382,7 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="89">
@@ -1393,7 +1393,7 @@
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="90">
@@ -1404,7 +1404,7 @@
         <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="91">
@@ -1415,7 +1415,7 @@
         <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="92">
@@ -1426,7 +1426,7 @@
         <v>91</v>
       </c>
       <c r="C92" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="93">
@@ -1437,7 +1437,7 @@
         <v>92</v>
       </c>
       <c r="C93" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="94">
@@ -1448,7 +1448,7 @@
         <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="95">
@@ -1459,7 +1459,7 @@
         <v>94</v>
       </c>
       <c r="C95" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="96">
@@ -1470,7 +1470,7 @@
         <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="97">
@@ -1481,7 +1481,7 @@
         <v>96</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="98">
@@ -1492,7 +1492,7 @@
         <v>97</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="99">
@@ -1503,7 +1503,7 @@
         <v>98</v>
       </c>
       <c r="C99" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="100">
@@ -1514,7 +1514,7 @@
         <v>99</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="101">
@@ -1525,7 +1525,7 @@
         <v>100</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="102">
@@ -1536,7 +1536,7 @@
         <v>101</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="103">
@@ -1547,7 +1547,7 @@
         <v>102</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="104">
@@ -1558,7 +1558,7 @@
         <v>103</v>
       </c>
       <c r="C104" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="105">
@@ -1569,7 +1569,7 @@
         <v>104</v>
       </c>
       <c r="C105" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="106">
@@ -1580,7 +1580,7 @@
         <v>105</v>
       </c>
       <c r="C106" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="107">
@@ -1591,7 +1591,7 @@
         <v>106</v>
       </c>
       <c r="C107" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="108">
@@ -1602,7 +1602,7 @@
         <v>107</v>
       </c>
       <c r="C108" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="109">
@@ -1613,7 +1613,7 @@
         <v>108</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="110">
@@ -1624,7 +1624,7 @@
         <v>109</v>
       </c>
       <c r="C110" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="111">
@@ -1646,7 +1646,7 @@
         <v>111</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="113">
@@ -1679,7 +1679,7 @@
         <v>114</v>
       </c>
       <c r="C115" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="116">
@@ -1690,7 +1690,7 @@
         <v>115</v>
       </c>
       <c r="C116" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="117">
@@ -1701,7 +1701,7 @@
         <v>116</v>
       </c>
       <c r="C117" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="118">
@@ -1745,7 +1745,7 @@
         <v>120</v>
       </c>
       <c r="C121" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="122">
@@ -1756,7 +1756,7 @@
         <v>121</v>
       </c>
       <c r="C122" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="123">
@@ -1767,7 +1767,7 @@
         <v>122</v>
       </c>
       <c r="C123" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="124">
@@ -1789,7 +1789,7 @@
         <v>124</v>
       </c>
       <c r="C125" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="126">
@@ -1800,7 +1800,7 @@
         <v>125</v>
       </c>
       <c r="C126" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="127">
@@ -1822,7 +1822,7 @@
         <v>127</v>
       </c>
       <c r="C128" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="129">
@@ -1833,7 +1833,7 @@
         <v>128</v>
       </c>
       <c r="C129" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="130">
@@ -1844,7 +1844,7 @@
         <v>129</v>
       </c>
       <c r="C130" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="131">
@@ -1855,7 +1855,7 @@
         <v>130</v>
       </c>
       <c r="C131" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="132">
@@ -1866,7 +1866,7 @@
         <v>131</v>
       </c>
       <c r="C132" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="133">
@@ -1877,7 +1877,7 @@
         <v>132</v>
       </c>
       <c r="C133" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="134">
@@ -1888,7 +1888,7 @@
         <v>133</v>
       </c>
       <c r="C134" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="135">
@@ -1899,7 +1899,7 @@
         <v>134</v>
       </c>
       <c r="C135" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="136">
@@ -1910,7 +1910,7 @@
         <v>135</v>
       </c>
       <c r="C136" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="137">
@@ -1921,7 +1921,7 @@
         <v>136</v>
       </c>
       <c r="C137" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="138">
@@ -1932,7 +1932,7 @@
         <v>137</v>
       </c>
       <c r="C138" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="139">
@@ -1943,7 +1943,7 @@
         <v>138</v>
       </c>
       <c r="C139" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="140">
@@ -1954,7 +1954,7 @@
         <v>139</v>
       </c>
       <c r="C140" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="141">
@@ -1965,7 +1965,7 @@
         <v>140</v>
       </c>
       <c r="C141" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="142">
@@ -1976,7 +1976,7 @@
         <v>141</v>
       </c>
       <c r="C142" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="143">
@@ -1987,7 +1987,7 @@
         <v>142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="144">
@@ -1998,7 +1998,7 @@
         <v>143</v>
       </c>
       <c r="C144" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="145">
@@ -2009,7 +2009,7 @@
         <v>144</v>
       </c>
       <c r="C145" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="146">
@@ -2020,7 +2020,7 @@
         <v>145</v>
       </c>
       <c r="C146" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="147">
@@ -2031,7 +2031,7 @@
         <v>146</v>
       </c>
       <c r="C147" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="148">
@@ -2042,7 +2042,7 @@
         <v>147</v>
       </c>
       <c r="C148" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="149">
@@ -2053,7 +2053,7 @@
         <v>148</v>
       </c>
       <c r="C149" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="150">
@@ -2064,7 +2064,7 @@
         <v>149</v>
       </c>
       <c r="C150" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="151">
@@ -2075,7 +2075,7 @@
         <v>150</v>
       </c>
       <c r="C151" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="152">
@@ -2086,7 +2086,7 @@
         <v>151</v>
       </c>
       <c r="C152" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="153">
@@ -2097,7 +2097,7 @@
         <v>152</v>
       </c>
       <c r="C153" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="154">
@@ -2108,7 +2108,7 @@
         <v>153</v>
       </c>
       <c r="C154" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="155">
@@ -2119,7 +2119,7 @@
         <v>154</v>
       </c>
       <c r="C155" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="156">
@@ -2130,7 +2130,7 @@
         <v>155</v>
       </c>
       <c r="C156" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="157">
@@ -2141,7 +2141,7 @@
         <v>156</v>
       </c>
       <c r="C157" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="158">
@@ -2152,7 +2152,7 @@
         <v>157</v>
       </c>
       <c r="C158" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="159">
@@ -2163,7 +2163,7 @@
         <v>158</v>
       </c>
       <c r="C159" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="160">
@@ -2174,7 +2174,7 @@
         <v>159</v>
       </c>
       <c r="C160" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="161">
@@ -2185,7 +2185,7 @@
         <v>160</v>
       </c>
       <c r="C161" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="162">
@@ -2196,7 +2196,7 @@
         <v>161</v>
       </c>
       <c r="C162" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="163">
@@ -2207,7 +2207,7 @@
         <v>162</v>
       </c>
       <c r="C163" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="164">
@@ -2218,7 +2218,7 @@
         <v>163</v>
       </c>
       <c r="C164" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="165">
@@ -2229,7 +2229,7 @@
         <v>164</v>
       </c>
       <c r="C165" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="166">
@@ -2240,7 +2240,7 @@
         <v>165</v>
       </c>
       <c r="C166" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="167">
@@ -2251,7 +2251,7 @@
         <v>166</v>
       </c>
       <c r="C167" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="168">
@@ -2262,7 +2262,7 @@
         <v>167</v>
       </c>
       <c r="C168" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="169">
@@ -2273,7 +2273,7 @@
         <v>168</v>
       </c>
       <c r="C169" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="170">
@@ -2284,7 +2284,7 @@
         <v>169</v>
       </c>
       <c r="C170" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="171">
@@ -2295,7 +2295,7 @@
         <v>170</v>
       </c>
       <c r="C171" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="172">
@@ -2306,7 +2306,7 @@
         <v>171</v>
       </c>
       <c r="C172" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="173">
@@ -2317,7 +2317,7 @@
         <v>172</v>
       </c>
       <c r="C173" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="174">
@@ -2339,7 +2339,7 @@
         <v>174</v>
       </c>
       <c r="C175" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="176">
@@ -2350,7 +2350,7 @@
         <v>175</v>
       </c>
       <c r="C176" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="177">
@@ -2361,7 +2361,7 @@
         <v>176</v>
       </c>
       <c r="C177" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="178">
@@ -2372,7 +2372,7 @@
         <v>177</v>
       </c>
       <c r="C178" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="179">
@@ -2383,7 +2383,7 @@
         <v>178</v>
       </c>
       <c r="C179" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="180">
@@ -2394,7 +2394,7 @@
         <v>179</v>
       </c>
       <c r="C180" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="181">
@@ -2405,7 +2405,7 @@
         <v>180</v>
       </c>
       <c r="C181" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="182">
@@ -2416,7 +2416,7 @@
         <v>181</v>
       </c>
       <c r="C182" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="183">
@@ -2427,7 +2427,7 @@
         <v>182</v>
       </c>
       <c r="C183" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="184">
@@ -2438,7 +2438,7 @@
         <v>183</v>
       </c>
       <c r="C184" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="185">
@@ -2449,7 +2449,7 @@
         <v>184</v>
       </c>
       <c r="C185" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="186">
@@ -2460,7 +2460,7 @@
         <v>185</v>
       </c>
       <c r="C186" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="187">
@@ -2471,7 +2471,7 @@
         <v>186</v>
       </c>
       <c r="C187" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="188">
@@ -2482,7 +2482,7 @@
         <v>187</v>
       </c>
       <c r="C188" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="189">
@@ -2493,7 +2493,7 @@
         <v>188</v>
       </c>
       <c r="C189" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="190">
@@ -2504,7 +2504,7 @@
         <v>189</v>
       </c>
       <c r="C190" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="191">
@@ -2515,7 +2515,7 @@
         <v>190</v>
       </c>
       <c r="C191" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="192">
@@ -2526,7 +2526,7 @@
         <v>191</v>
       </c>
       <c r="C192" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="193">
@@ -2537,7 +2537,7 @@
         <v>192</v>
       </c>
       <c r="C193" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="194">
@@ -2548,7 +2548,7 @@
         <v>193</v>
       </c>
       <c r="C194" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="195">
@@ -2559,7 +2559,7 @@
         <v>194</v>
       </c>
       <c r="C195" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="196">
@@ -2570,7 +2570,7 @@
         <v>195</v>
       </c>
       <c r="C196" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="197">
@@ -2592,7 +2592,7 @@
         <v>197</v>
       </c>
       <c r="C198" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="199">
@@ -2603,7 +2603,7 @@
         <v>198</v>
       </c>
       <c r="C199" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="200">
@@ -2614,7 +2614,7 @@
         <v>199</v>
       </c>
       <c r="C200" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="201">
@@ -2625,7 +2625,7 @@
         <v>200</v>
       </c>
       <c r="C201" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="202">
@@ -2636,7 +2636,7 @@
         <v>201</v>
       </c>
       <c r="C202" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="203">
@@ -2647,7 +2647,7 @@
         <v>202</v>
       </c>
       <c r="C203" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="204">
@@ -2658,7 +2658,7 @@
         <v>203</v>
       </c>
       <c r="C204" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="205">
@@ -2669,7 +2669,7 @@
         <v>204</v>
       </c>
       <c r="C205" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="206">
@@ -2691,7 +2691,7 @@
         <v>206</v>
       </c>
       <c r="C207" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="208">
@@ -2702,7 +2702,7 @@
         <v>207</v>
       </c>
       <c r="C208" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="209">
@@ -2713,7 +2713,7 @@
         <v>208</v>
       </c>
       <c r="C209" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="210">
@@ -2724,7 +2724,7 @@
         <v>209</v>
       </c>
       <c r="C210" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="211">
@@ -2735,7 +2735,7 @@
         <v>210</v>
       </c>
       <c r="C211" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="212">
@@ -2746,7 +2746,7 @@
         <v>211</v>
       </c>
       <c r="C212" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="213">
@@ -2757,7 +2757,7 @@
         <v>212</v>
       </c>
       <c r="C213" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="214">
@@ -2768,7 +2768,7 @@
         <v>213</v>
       </c>
       <c r="C214" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="215">
@@ -2779,7 +2779,7 @@
         <v>214</v>
       </c>
       <c r="C215" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="216">
@@ -2790,7 +2790,7 @@
         <v>215</v>
       </c>
       <c r="C216" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="217">
@@ -2812,7 +2812,7 @@
         <v>217</v>
       </c>
       <c r="C218" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="219">
@@ -2834,7 +2834,7 @@
         <v>219</v>
       </c>
       <c r="C220" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="221">
@@ -2856,7 +2856,7 @@
         <v>221</v>
       </c>
       <c r="C222" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="223">
@@ -2867,7 +2867,7 @@
         <v>222</v>
       </c>
       <c r="C223" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="224">
@@ -2878,7 +2878,7 @@
         <v>223</v>
       </c>
       <c r="C224" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="225">
@@ -2889,7 +2889,7 @@
         <v>224</v>
       </c>
       <c r="C225" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="226">
@@ -2900,7 +2900,7 @@
         <v>225</v>
       </c>
       <c r="C226" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="227">
@@ -2911,7 +2911,7 @@
         <v>226</v>
       </c>
       <c r="C227" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="228">
@@ -2933,7 +2933,7 @@
         <v>228</v>
       </c>
       <c r="C229" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="230">
@@ -2944,7 +2944,7 @@
         <v>229</v>
       </c>
       <c r="C230" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="231">
@@ -2955,7 +2955,7 @@
         <v>230</v>
       </c>
       <c r="C231" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="232">
@@ -2966,7 +2966,7 @@
         <v>231</v>
       </c>
       <c r="C232" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="233">
@@ -2977,7 +2977,7 @@
         <v>232</v>
       </c>
       <c r="C233" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="234">
@@ -2988,7 +2988,7 @@
         <v>233</v>
       </c>
       <c r="C234" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="235">
@@ -2999,7 +2999,7 @@
         <v>234</v>
       </c>
       <c r="C235" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="236">
@@ -3010,7 +3010,7 @@
         <v>235</v>
       </c>
       <c r="C236" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="237">
@@ -3021,7 +3021,7 @@
         <v>236</v>
       </c>
       <c r="C237" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="238">
@@ -3032,7 +3032,7 @@
         <v>237</v>
       </c>
       <c r="C238" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="239">
@@ -3054,7 +3054,7 @@
         <v>239</v>
       </c>
       <c r="C240" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="241">
@@ -3065,7 +3065,7 @@
         <v>240</v>
       </c>
       <c r="C241" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="242">
@@ -3076,7 +3076,7 @@
         <v>241</v>
       </c>
       <c r="C242" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="243">
@@ -3087,7 +3087,7 @@
         <v>242</v>
       </c>
       <c r="C243" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="244">
@@ -3109,7 +3109,7 @@
         <v>244</v>
       </c>
       <c r="C245" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="246">
@@ -3120,7 +3120,7 @@
         <v>245</v>
       </c>
       <c r="C246" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="247">
@@ -3131,7 +3131,7 @@
         <v>246</v>
       </c>
       <c r="C247" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="248">
@@ -3142,7 +3142,7 @@
         <v>247</v>
       </c>
       <c r="C248" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="249">
@@ -3153,7 +3153,7 @@
         <v>248</v>
       </c>
       <c r="C249" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="250">
@@ -3164,7 +3164,7 @@
         <v>249</v>
       </c>
       <c r="C250" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="251">
@@ -3175,7 +3175,7 @@
         <v>250</v>
       </c>
       <c r="C251" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="252">
@@ -3186,7 +3186,7 @@
         <v>251</v>
       </c>
       <c r="C252" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="253">
@@ -3219,7 +3219,7 @@
         <v>254</v>
       </c>
       <c r="C255" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="256">
@@ -3230,7 +3230,7 @@
         <v>255</v>
       </c>
       <c r="C256" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="257">
@@ -3241,7 +3241,7 @@
         <v>256</v>
       </c>
       <c r="C257" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="258">
@@ -3252,7 +3252,7 @@
         <v>257</v>
       </c>
       <c r="C258" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="259">
@@ -3263,7 +3263,7 @@
         <v>258</v>
       </c>
       <c r="C259" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="260">
@@ -3274,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="C260" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="261">
@@ -3285,7 +3285,7 @@
         <v>260</v>
       </c>
       <c r="C261" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="262">
@@ -3296,7 +3296,7 @@
         <v>261</v>
       </c>
       <c r="C262" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="263">
@@ -3307,7 +3307,7 @@
         <v>262</v>
       </c>
       <c r="C263" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="264">
@@ -3318,7 +3318,7 @@
         <v>263</v>
       </c>
       <c r="C264" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="265">
@@ -3329,7 +3329,7 @@
         <v>264</v>
       </c>
       <c r="C265" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="266">
@@ -3340,7 +3340,7 @@
         <v>265</v>
       </c>
       <c r="C266" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="267">
@@ -3351,7 +3351,7 @@
         <v>266</v>
       </c>
       <c r="C267" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="268">
@@ -3373,7 +3373,7 @@
         <v>268</v>
       </c>
       <c r="C269" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="270">
@@ -3384,7 +3384,7 @@
         <v>269</v>
       </c>
       <c r="C270" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="271">
@@ -3395,7 +3395,7 @@
         <v>270</v>
       </c>
       <c r="C271" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="272">
@@ -3406,7 +3406,7 @@
         <v>271</v>
       </c>
       <c r="C272" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="273">
@@ -3417,7 +3417,7 @@
         <v>272</v>
       </c>
       <c r="C273" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="274">
@@ -3428,7 +3428,7 @@
         <v>273</v>
       </c>
       <c r="C274" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="275">
@@ -3439,7 +3439,7 @@
         <v>274</v>
       </c>
       <c r="C275" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="276">
@@ -3450,7 +3450,7 @@
         <v>275</v>
       </c>
       <c r="C276" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="277">
@@ -3461,7 +3461,7 @@
         <v>276</v>
       </c>
       <c r="C277" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="278">
@@ -3472,7 +3472,7 @@
         <v>277</v>
       </c>
       <c r="C278" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="279">
@@ -3483,7 +3483,7 @@
         <v>278</v>
       </c>
       <c r="C279" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="280">
@@ -3494,7 +3494,7 @@
         <v>279</v>
       </c>
       <c r="C280" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="281">
@@ -3505,7 +3505,7 @@
         <v>280</v>
       </c>
       <c r="C281" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="282">
@@ -3516,7 +3516,7 @@
         <v>281</v>
       </c>
       <c r="C282" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="283">
@@ -3527,7 +3527,7 @@
         <v>282</v>
       </c>
       <c r="C283" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="284">
@@ -3538,7 +3538,7 @@
         <v>283</v>
       </c>
       <c r="C284" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="285">
@@ -3549,7 +3549,7 @@
         <v>284</v>
       </c>
       <c r="C285" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="286">
@@ -3560,7 +3560,7 @@
         <v>285</v>
       </c>
       <c r="C286" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="287">
@@ -3571,7 +3571,7 @@
         <v>286</v>
       </c>
       <c r="C287" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="288">
@@ -3582,7 +3582,7 @@
         <v>287</v>
       </c>
       <c r="C288" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="289">
@@ -3593,7 +3593,7 @@
         <v>288</v>
       </c>
       <c r="C289" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="290">
@@ -3604,7 +3604,7 @@
         <v>289</v>
       </c>
       <c r="C290" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="291">
@@ -3615,7 +3615,7 @@
         <v>290</v>
       </c>
       <c r="C291" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="292">
@@ -3626,7 +3626,7 @@
         <v>291</v>
       </c>
       <c r="C292" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="293">
@@ -3637,7 +3637,7 @@
         <v>292</v>
       </c>
       <c r="C293" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="294">
@@ -3648,7 +3648,7 @@
         <v>293</v>
       </c>
       <c r="C294" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="295">
@@ -3659,7 +3659,7 @@
         <v>294</v>
       </c>
       <c r="C295" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="296">
@@ -3670,7 +3670,7 @@
         <v>295</v>
       </c>
       <c r="C296" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="297">
@@ -3681,7 +3681,7 @@
         <v>296</v>
       </c>
       <c r="C297" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="298">
@@ -3692,7 +3692,7 @@
         <v>297</v>
       </c>
       <c r="C298" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="299">
@@ -3714,7 +3714,7 @@
         <v>299</v>
       </c>
       <c r="C300" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="301">
@@ -3725,7 +3725,7 @@
         <v>300</v>
       </c>
       <c r="C301" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="302">
@@ -3736,7 +3736,7 @@
         <v>301</v>
       </c>
       <c r="C302" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="303">
@@ -3758,7 +3758,7 @@
         <v>303</v>
       </c>
       <c r="C304" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="305">
@@ -3769,7 +3769,7 @@
         <v>304</v>
       </c>
       <c r="C305" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="306">
@@ -3802,7 +3802,7 @@
         <v>307</v>
       </c>
       <c r="C308" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="309">
@@ -3813,7 +3813,7 @@
         <v>308</v>
       </c>
       <c r="C309" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="310">
@@ -3824,7 +3824,7 @@
         <v>309</v>
       </c>
       <c r="C310" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="311">
@@ -3835,7 +3835,7 @@
         <v>310</v>
       </c>
       <c r="C311" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="312">
@@ -3857,7 +3857,7 @@
         <v>312</v>
       </c>
       <c r="C313" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="314">
@@ -3868,7 +3868,7 @@
         <v>313</v>
       </c>
       <c r="C314" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="315">
@@ -3879,7 +3879,7 @@
         <v>314</v>
       </c>
       <c r="C315" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="316">
@@ -3890,7 +3890,7 @@
         <v>315</v>
       </c>
       <c r="C316" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="317">
@@ -3901,7 +3901,7 @@
         <v>316</v>
       </c>
       <c r="C317" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="318">
@@ -3912,7 +3912,7 @@
         <v>317</v>
       </c>
       <c r="C318" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="319">
@@ -3923,7 +3923,7 @@
         <v>318</v>
       </c>
       <c r="C319" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="320">
@@ -3934,7 +3934,7 @@
         <v>319</v>
       </c>
       <c r="C320" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="321">
@@ -3956,7 +3956,7 @@
         <v>321</v>
       </c>
       <c r="C322" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="323">
@@ -3967,7 +3967,7 @@
         <v>322</v>
       </c>
       <c r="C323" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="324">
@@ -3978,7 +3978,7 @@
         <v>323</v>
       </c>
       <c r="C324" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="325">
@@ -3989,7 +3989,7 @@
         <v>324</v>
       </c>
       <c r="C325" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="326">
@@ -4000,7 +4000,7 @@
         <v>325</v>
       </c>
       <c r="C326" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="327">
@@ -4011,7 +4011,7 @@
         <v>326</v>
       </c>
       <c r="C327" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="328">
@@ -4022,7 +4022,7 @@
         <v>327</v>
       </c>
       <c r="C328" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="329">
@@ -4033,7 +4033,7 @@
         <v>328</v>
       </c>
       <c r="C329" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="330">
@@ -4055,7 +4055,7 @@
         <v>330</v>
       </c>
       <c r="C331" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="332">
@@ -4077,7 +4077,7 @@
         <v>332</v>
       </c>
       <c r="C333" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="334">
@@ -4099,7 +4099,7 @@
         <v>334</v>
       </c>
       <c r="C335" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="336">
@@ -4110,7 +4110,7 @@
         <v>335</v>
       </c>
       <c r="C336" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="337">
@@ -4121,7 +4121,7 @@
         <v>336</v>
       </c>
       <c r="C337" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="338">
@@ -4176,7 +4176,7 @@
         <v>341</v>
       </c>
       <c r="C342" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="343">
@@ -4198,7 +4198,7 @@
         <v>343</v>
       </c>
       <c r="C344" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="345">
@@ -4209,7 +4209,7 @@
         <v>344</v>
       </c>
       <c r="C345" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="346">
@@ -4231,7 +4231,7 @@
         <v>346</v>
       </c>
       <c r="C347" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="348">
@@ -4242,7 +4242,7 @@
         <v>347</v>
       </c>
       <c r="C348" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="349">
@@ -4253,7 +4253,7 @@
         <v>348</v>
       </c>
       <c r="C349" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="350">
@@ -4264,7 +4264,7 @@
         <v>349</v>
       </c>
       <c r="C350" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="351">
@@ -4286,7 +4286,7 @@
         <v>351</v>
       </c>
       <c r="C352" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="353">
@@ -4297,7 +4297,7 @@
         <v>352</v>
       </c>
       <c r="C353" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="354">
@@ -4308,7 +4308,7 @@
         <v>353</v>
       </c>
       <c r="C354" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="355">
@@ -4319,7 +4319,7 @@
         <v>354</v>
       </c>
       <c r="C355" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="356">
@@ -4330,7 +4330,7 @@
         <v>355</v>
       </c>
       <c r="C356" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="357">
@@ -4341,7 +4341,7 @@
         <v>356</v>
       </c>
       <c r="C357" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="358">
@@ -4352,7 +4352,7 @@
         <v>357</v>
       </c>
       <c r="C358" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="359">
@@ -4418,7 +4418,7 @@
         <v>363</v>
       </c>
       <c r="C364" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="365">
@@ -4429,7 +4429,7 @@
         <v>364</v>
       </c>
       <c r="C365" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="366">
@@ -4451,7 +4451,7 @@
         <v>366</v>
       </c>
       <c r="C367" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="368">
@@ -4462,7 +4462,7 @@
         <v>367</v>
       </c>
       <c r="C368" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="369">
@@ -4484,7 +4484,7 @@
         <v>369</v>
       </c>
       <c r="C370" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="371">
@@ -4506,7 +4506,7 @@
         <v>371</v>
       </c>
       <c r="C372" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="373">
@@ -4517,7 +4517,7 @@
         <v>372</v>
       </c>
       <c r="C373" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="374">
@@ -4528,7 +4528,7 @@
         <v>373</v>
       </c>
       <c r="C374" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="375">
@@ -4539,7 +4539,7 @@
         <v>374</v>
       </c>
       <c r="C375" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="376">
@@ -4550,7 +4550,7 @@
         <v>375</v>
       </c>
       <c r="C376" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="377">
@@ -4561,7 +4561,7 @@
         <v>376</v>
       </c>
       <c r="C377" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="378">
@@ -4572,7 +4572,7 @@
         <v>377</v>
       </c>
       <c r="C378" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="379">
@@ -4583,7 +4583,7 @@
         <v>378</v>
       </c>
       <c r="C379" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="380">
@@ -4594,7 +4594,7 @@
         <v>379</v>
       </c>
       <c r="C380" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="381">
@@ -4616,7 +4616,7 @@
         <v>381</v>
       </c>
       <c r="C382" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="383">
@@ -4627,7 +4627,7 @@
         <v>382</v>
       </c>
       <c r="C383" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="384">
@@ -4638,7 +4638,7 @@
         <v>383</v>
       </c>
       <c r="C384" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="385">
@@ -4649,7 +4649,7 @@
         <v>384</v>
       </c>
       <c r="C385" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="386">
@@ -4682,7 +4682,7 @@
         <v>387</v>
       </c>
       <c r="C388" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="389">
@@ -4693,7 +4693,7 @@
         <v>388</v>
       </c>
       <c r="C389" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="390">
@@ -4704,7 +4704,7 @@
         <v>389</v>
       </c>
       <c r="C390" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="391">
@@ -4715,7 +4715,7 @@
         <v>390</v>
       </c>
       <c r="C391" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="392">
@@ -4726,7 +4726,7 @@
         <v>391</v>
       </c>
       <c r="C392" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="393">
@@ -4737,7 +4737,7 @@
         <v>392</v>
       </c>
       <c r="C393" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="394">
@@ -4748,7 +4748,7 @@
         <v>393</v>
       </c>
       <c r="C394" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="395">
@@ -4759,7 +4759,7 @@
         <v>394</v>
       </c>
       <c r="C395" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="396">
@@ -4770,7 +4770,7 @@
         <v>395</v>
       </c>
       <c r="C396" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="397">
@@ -4792,7 +4792,7 @@
         <v>397</v>
       </c>
       <c r="C398" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="399">
@@ -4803,7 +4803,7 @@
         <v>398</v>
       </c>
       <c r="C399" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="400">
@@ -4814,7 +4814,7 @@
         <v>399</v>
       </c>
       <c r="C400" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="401">
@@ -4825,7 +4825,7 @@
         <v>400</v>
       </c>
       <c r="C401" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="402">
@@ -4858,7 +4858,7 @@
         <v>403</v>
       </c>
       <c r="C404" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="405">
@@ -4869,7 +4869,7 @@
         <v>404</v>
       </c>
       <c r="C405" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="406">
@@ -4880,7 +4880,7 @@
         <v>405</v>
       </c>
       <c r="C406" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="407">
@@ -4891,7 +4891,7 @@
         <v>406</v>
       </c>
       <c r="C407" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="408">
@@ -4902,7 +4902,7 @@
         <v>407</v>
       </c>
       <c r="C408" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="409">
@@ -4913,7 +4913,7 @@
         <v>408</v>
       </c>
       <c r="C409" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="410">
@@ -4957,7 +4957,7 @@
         <v>412</v>
       </c>
       <c r="C413" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="414">
@@ -4990,7 +4990,7 @@
         <v>415</v>
       </c>
       <c r="C416" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="417">
@@ -5001,7 +5001,7 @@
         <v>416</v>
       </c>
       <c r="C417" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="418">
@@ -5023,7 +5023,7 @@
         <v>418</v>
       </c>
       <c r="C419" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="420">
@@ -5034,7 +5034,7 @@
         <v>419</v>
       </c>
       <c r="C420" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="421">
@@ -5045,7 +5045,7 @@
         <v>420</v>
       </c>
       <c r="C421" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="422">
@@ -5056,7 +5056,7 @@
         <v>421</v>
       </c>
       <c r="C422" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="423">
@@ -5067,7 +5067,7 @@
         <v>422</v>
       </c>
       <c r="C423" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="424">
@@ -5078,7 +5078,7 @@
         <v>423</v>
       </c>
       <c r="C424" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="425">
@@ -5089,7 +5089,7 @@
         <v>424</v>
       </c>
       <c r="C425" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="426">
@@ -5111,7 +5111,7 @@
         <v>426</v>
       </c>
       <c r="C427" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="428">
@@ -5133,7 +5133,7 @@
         <v>428</v>
       </c>
       <c r="C429" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="430">
@@ -5144,7 +5144,7 @@
         <v>429</v>
       </c>
       <c r="C430" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="431">
@@ -5155,7 +5155,7 @@
         <v>430</v>
       </c>
       <c r="C431" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="432">
@@ -5177,7 +5177,7 @@
         <v>432</v>
       </c>
       <c r="C433" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="434">
@@ -5188,7 +5188,7 @@
         <v>433</v>
       </c>
       <c r="C434" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="435">
@@ -5199,7 +5199,7 @@
         <v>434</v>
       </c>
       <c r="C435" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="436">
@@ -5210,7 +5210,7 @@
         <v>435</v>
       </c>
       <c r="C436" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="437">
@@ -5221,7 +5221,7 @@
         <v>436</v>
       </c>
       <c r="C437" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="438">
@@ -5232,7 +5232,7 @@
         <v>437</v>
       </c>
       <c r="C438" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="439">
@@ -5254,7 +5254,7 @@
         <v>439</v>
       </c>
       <c r="C440" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="441">
@@ -5265,7 +5265,7 @@
         <v>440</v>
       </c>
       <c r="C441" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="442">
@@ -5287,7 +5287,7 @@
         <v>442</v>
       </c>
       <c r="C443" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="444">
@@ -5298,7 +5298,7 @@
         <v>443</v>
       </c>
       <c r="C444" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="445">
@@ -5309,7 +5309,7 @@
         <v>444</v>
       </c>
       <c r="C445" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="446">
@@ -5320,7 +5320,7 @@
         <v>445</v>
       </c>
       <c r="C446" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="447">
@@ -5331,7 +5331,7 @@
         <v>446</v>
       </c>
       <c r="C447" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="448">
@@ -5342,7 +5342,7 @@
         <v>447</v>
       </c>
       <c r="C448" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="449">
@@ -5364,7 +5364,7 @@
         <v>449</v>
       </c>
       <c r="C450" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="451">
@@ -5386,7 +5386,7 @@
         <v>451</v>
       </c>
       <c r="C452" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="453">
@@ -5397,7 +5397,7 @@
         <v>452</v>
       </c>
       <c r="C453" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="454">
@@ -5408,7 +5408,7 @@
         <v>453</v>
       </c>
       <c r="C454" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="455">
@@ -5419,7 +5419,7 @@
         <v>454</v>
       </c>
       <c r="C455" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="456">
@@ -5430,7 +5430,7 @@
         <v>455</v>
       </c>
       <c r="C456" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="457">
@@ -5441,7 +5441,7 @@
         <v>456</v>
       </c>
       <c r="C457" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="458">
@@ -5463,7 +5463,7 @@
         <v>458</v>
       </c>
       <c r="C459" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="460">
@@ -5474,7 +5474,7 @@
         <v>459</v>
       </c>
       <c r="C460" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="461">
@@ -5485,7 +5485,7 @@
         <v>460</v>
       </c>
       <c r="C461" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="462">
@@ -5507,7 +5507,7 @@
         <v>462</v>
       </c>
       <c r="C463" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="464">
@@ -5518,7 +5518,7 @@
         <v>463</v>
       </c>
       <c r="C464" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="465">
@@ -5529,7 +5529,7 @@
         <v>464</v>
       </c>
       <c r="C465" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="466">
@@ -5551,7 +5551,7 @@
         <v>466</v>
       </c>
       <c r="C467" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="468">
@@ -5562,7 +5562,7 @@
         <v>467</v>
       </c>
       <c r="C468" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="469">
@@ -5573,7 +5573,7 @@
         <v>468</v>
       </c>
       <c r="C469" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="470">
@@ -5584,7 +5584,7 @@
         <v>469</v>
       </c>
       <c r="C470" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="471">
@@ -5595,7 +5595,7 @@
         <v>470</v>
       </c>
       <c r="C471" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="472">
@@ -5606,7 +5606,7 @@
         <v>471</v>
       </c>
       <c r="C472" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="473">
@@ -5617,7 +5617,7 @@
         <v>472</v>
       </c>
       <c r="C473" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="474">
@@ -5628,7 +5628,7 @@
         <v>473</v>
       </c>
       <c r="C474" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="475">
@@ -5639,7 +5639,7 @@
         <v>474</v>
       </c>
       <c r="C475" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="476">
@@ -5650,7 +5650,7 @@
         <v>475</v>
       </c>
       <c r="C476" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="477">
@@ -5661,7 +5661,7 @@
         <v>476</v>
       </c>
       <c r="C477" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="478">
@@ -5672,7 +5672,7 @@
         <v>477</v>
       </c>
       <c r="C478" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="479">
@@ -5683,7 +5683,7 @@
         <v>478</v>
       </c>
       <c r="C479" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="480">
@@ -5694,7 +5694,7 @@
         <v>479</v>
       </c>
       <c r="C480" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="481">
@@ -5705,7 +5705,7 @@
         <v>480</v>
       </c>
       <c r="C481" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="482">
@@ -5716,7 +5716,7 @@
         <v>481</v>
       </c>
       <c r="C482" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="483">
@@ -5727,7 +5727,7 @@
         <v>482</v>
       </c>
       <c r="C483" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="484">
@@ -5738,7 +5738,7 @@
         <v>483</v>
       </c>
       <c r="C484" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="485">
@@ -5760,7 +5760,7 @@
         <v>485</v>
       </c>
       <c r="C486" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="487">
@@ -5771,7 +5771,7 @@
         <v>486</v>
       </c>
       <c r="C487" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="488">
@@ -5782,7 +5782,7 @@
         <v>487</v>
       </c>
       <c r="C488" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="489">
@@ -5793,7 +5793,7 @@
         <v>488</v>
       </c>
       <c r="C489" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="490">
@@ -5815,7 +5815,7 @@
         <v>490</v>
       </c>
       <c r="C491" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="492">
@@ -5826,7 +5826,7 @@
         <v>491</v>
       </c>
       <c r="C492" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="493">
@@ -5859,7 +5859,7 @@
         <v>494</v>
       </c>
       <c r="C495" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="496">
@@ -5870,7 +5870,7 @@
         <v>495</v>
       </c>
       <c r="C496" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="497">
@@ -5881,7 +5881,7 @@
         <v>496</v>
       </c>
       <c r="C497" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="498">
@@ -5892,7 +5892,7 @@
         <v>497</v>
       </c>
       <c r="C498" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="499">
@@ -5903,7 +5903,7 @@
         <v>498</v>
       </c>
       <c r="C499" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="500">
@@ -5914,7 +5914,7 @@
         <v>499</v>
       </c>
       <c r="C500" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="501">
@@ -5925,7 +5925,7 @@
         <v>500</v>
       </c>
       <c r="C501" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="502">
@@ -5936,7 +5936,7 @@
         <v>501</v>
       </c>
       <c r="C502" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="503">
@@ -5947,7 +5947,7 @@
         <v>502</v>
       </c>
       <c r="C503" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="504">
@@ -5958,7 +5958,7 @@
         <v>503</v>
       </c>
       <c r="C504" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="505">
@@ -5969,7 +5969,7 @@
         <v>504</v>
       </c>
       <c r="C505" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="506">
@@ -5980,7 +5980,7 @@
         <v>505</v>
       </c>
       <c r="C506" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="507">
@@ -5991,7 +5991,7 @@
         <v>506</v>
       </c>
       <c r="C507" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="508">
@@ -6002,7 +6002,7 @@
         <v>507</v>
       </c>
       <c r="C508" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="509">
@@ -6035,7 +6035,7 @@
         <v>510</v>
       </c>
       <c r="C511" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="512">
@@ -6046,7 +6046,7 @@
         <v>511</v>
       </c>
       <c r="C512" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="513">
@@ -6057,7 +6057,7 @@
         <v>512</v>
       </c>
       <c r="C513" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="514">
@@ -6068,7 +6068,7 @@
         <v>513</v>
       </c>
       <c r="C514" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="515">
@@ -6079,7 +6079,7 @@
         <v>514</v>
       </c>
       <c r="C515" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="516">
@@ -6090,7 +6090,7 @@
         <v>515</v>
       </c>
       <c r="C516" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="517">
@@ -6101,7 +6101,7 @@
         <v>516</v>
       </c>
       <c r="C517" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="518">
@@ -6112,7 +6112,7 @@
         <v>517</v>
       </c>
       <c r="C518" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="519">
@@ -6123,7 +6123,7 @@
         <v>518</v>
       </c>
       <c r="C519" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="520">
@@ -6134,7 +6134,7 @@
         <v>519</v>
       </c>
       <c r="C520" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="521">
@@ -6145,7 +6145,7 @@
         <v>520</v>
       </c>
       <c r="C521" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="522">
@@ -6156,7 +6156,7 @@
         <v>521</v>
       </c>
       <c r="C522" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="523">
@@ -6167,7 +6167,7 @@
         <v>522</v>
       </c>
       <c r="C523" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="524">
@@ -6178,7 +6178,7 @@
         <v>523</v>
       </c>
       <c r="C524" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="525">
@@ -6189,7 +6189,7 @@
         <v>524</v>
       </c>
       <c r="C525" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="526">
@@ -6200,7 +6200,7 @@
         <v>525</v>
       </c>
       <c r="C526" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="527">
@@ -6211,7 +6211,7 @@
         <v>526</v>
       </c>
       <c r="C527" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="528">
@@ -6222,7 +6222,7 @@
         <v>527</v>
       </c>
       <c r="C528" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="529">
@@ -6233,7 +6233,7 @@
         <v>528</v>
       </c>
       <c r="C529" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="530">
@@ -6244,7 +6244,7 @@
         <v>529</v>
       </c>
       <c r="C530" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="531">
@@ -6255,7 +6255,7 @@
         <v>530</v>
       </c>
       <c r="C531" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="532">
@@ -6266,7 +6266,7 @@
         <v>531</v>
       </c>
       <c r="C532" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="533">
@@ -6277,7 +6277,7 @@
         <v>532</v>
       </c>
       <c r="C533" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="534">
@@ -6288,7 +6288,7 @@
         <v>533</v>
       </c>
       <c r="C534" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="535">
@@ -6299,7 +6299,7 @@
         <v>534</v>
       </c>
       <c r="C535" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="536">
@@ -6310,7 +6310,7 @@
         <v>535</v>
       </c>
       <c r="C536" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="537">
@@ -6321,7 +6321,7 @@
         <v>536</v>
       </c>
       <c r="C537" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="538">
@@ -6332,7 +6332,7 @@
         <v>537</v>
       </c>
       <c r="C538" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="539">
@@ -6343,7 +6343,7 @@
         <v>538</v>
       </c>
       <c r="C539" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="540">
@@ -6354,7 +6354,7 @@
         <v>539</v>
       </c>
       <c r="C540" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="541">
@@ -6365,7 +6365,7 @@
         <v>540</v>
       </c>
       <c r="C541" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="542">
@@ -6376,7 +6376,7 @@
         <v>541</v>
       </c>
       <c r="C542" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="543">
@@ -6387,7 +6387,7 @@
         <v>542</v>
       </c>
       <c r="C543" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="544">
@@ -6398,7 +6398,7 @@
         <v>543</v>
       </c>
       <c r="C544" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="545">
@@ -6409,7 +6409,7 @@
         <v>544</v>
       </c>
       <c r="C545" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="546">
@@ -6420,7 +6420,7 @@
         <v>545</v>
       </c>
       <c r="C546" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="547">
@@ -6431,7 +6431,7 @@
         <v>546</v>
       </c>
       <c r="C547" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="548">
@@ -6442,7 +6442,7 @@
         <v>547</v>
       </c>
       <c r="C548" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="549">
@@ -6453,7 +6453,7 @@
         <v>548</v>
       </c>
       <c r="C549" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="550">
@@ -6464,7 +6464,7 @@
         <v>549</v>
       </c>
       <c r="C550" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="551">
@@ -6475,7 +6475,7 @@
         <v>550</v>
       </c>
       <c r="C551" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="552">
@@ -6486,7 +6486,7 @@
         <v>551</v>
       </c>
       <c r="C552" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="553">
@@ -6497,7 +6497,7 @@
         <v>552</v>
       </c>
       <c r="C553" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="554">
@@ -6508,7 +6508,7 @@
         <v>553</v>
       </c>
       <c r="C554" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="555">
@@ -6519,7 +6519,7 @@
         <v>554</v>
       </c>
       <c r="C555" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="556">
@@ -6530,7 +6530,7 @@
         <v>555</v>
       </c>
       <c r="C556" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="557">
@@ -6541,7 +6541,7 @@
         <v>556</v>
       </c>
       <c r="C557" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="558">
@@ -6552,7 +6552,7 @@
         <v>557</v>
       </c>
       <c r="C558" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="559">
@@ -6563,7 +6563,7 @@
         <v>558</v>
       </c>
       <c r="C559" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="560">
@@ -6574,7 +6574,7 @@
         <v>559</v>
       </c>
       <c r="C560" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="561">
@@ -6585,7 +6585,7 @@
         <v>560</v>
       </c>
       <c r="C561" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="562">
@@ -6596,7 +6596,7 @@
         <v>561</v>
       </c>
       <c r="C562" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="563">
@@ -6607,7 +6607,7 @@
         <v>562</v>
       </c>
       <c r="C563" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="564">
@@ -6618,7 +6618,7 @@
         <v>563</v>
       </c>
       <c r="C564" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="565">
@@ -6629,7 +6629,7 @@
         <v>564</v>
       </c>
       <c r="C565" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="566">
@@ -6640,7 +6640,7 @@
         <v>565</v>
       </c>
       <c r="C566" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="567">
@@ -6651,7 +6651,7 @@
         <v>566</v>
       </c>
       <c r="C567" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="568">
@@ -6662,7 +6662,7 @@
         <v>567</v>
       </c>
       <c r="C568" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="569">
@@ -6673,7 +6673,7 @@
         <v>568</v>
       </c>
       <c r="C569" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="570">
@@ -6684,7 +6684,7 @@
         <v>569</v>
       </c>
       <c r="C570" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="571">
@@ -6695,7 +6695,7 @@
         <v>570</v>
       </c>
       <c r="C571" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="572">
@@ -6706,7 +6706,7 @@
         <v>571</v>
       </c>
       <c r="C572" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="573">
@@ -6717,7 +6717,7 @@
         <v>572</v>
       </c>
       <c r="C573" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="574">
@@ -6728,7 +6728,7 @@
         <v>573</v>
       </c>
       <c r="C574" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="575">
@@ -6739,7 +6739,7 @@
         <v>574</v>
       </c>
       <c r="C575" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="576">
@@ -6750,7 +6750,7 @@
         <v>575</v>
       </c>
       <c r="C576" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="577">
@@ -6761,7 +6761,7 @@
         <v>576</v>
       </c>
       <c r="C577" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="578">
@@ -6772,7 +6772,7 @@
         <v>577</v>
       </c>
       <c r="C578" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="579">
@@ -6783,7 +6783,7 @@
         <v>578</v>
       </c>
       <c r="C579" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="580">
@@ -6794,7 +6794,7 @@
         <v>579</v>
       </c>
       <c r="C580" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="581">
@@ -6805,7 +6805,7 @@
         <v>580</v>
       </c>
       <c r="C581" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="582">
@@ -6816,7 +6816,7 @@
         <v>581</v>
       </c>
       <c r="C582" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="583">
@@ -6827,7 +6827,7 @@
         <v>582</v>
       </c>
       <c r="C583" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="584">
@@ -6838,7 +6838,7 @@
         <v>583</v>
       </c>
       <c r="C584" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="585">
@@ -6849,7 +6849,7 @@
         <v>584</v>
       </c>
       <c r="C585" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="586">
@@ -6860,7 +6860,7 @@
         <v>585</v>
       </c>
       <c r="C586" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="587">
@@ -6871,7 +6871,7 @@
         <v>586</v>
       </c>
       <c r="C587" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="588">
@@ -6882,7 +6882,7 @@
         <v>587</v>
       </c>
       <c r="C588" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="589">
@@ -6893,7 +6893,7 @@
         <v>588</v>
       </c>
       <c r="C589" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="590">
@@ -6904,7 +6904,7 @@
         <v>589</v>
       </c>
       <c r="C590" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="591">
@@ -6915,7 +6915,7 @@
         <v>590</v>
       </c>
       <c r="C591" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="592">
@@ -6926,7 +6926,7 @@
         <v>591</v>
       </c>
       <c r="C592" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="593">
@@ -6937,7 +6937,7 @@
         <v>592</v>
       </c>
       <c r="C593" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="594">
@@ -6948,7 +6948,7 @@
         <v>593</v>
       </c>
       <c r="C594" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="595">
@@ -6959,7 +6959,7 @@
         <v>594</v>
       </c>
       <c r="C595" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="596">
@@ -6970,7 +6970,7 @@
         <v>595</v>
       </c>
       <c r="C596" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="597">
@@ -6981,7 +6981,7 @@
         <v>596</v>
       </c>
       <c r="C597" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="598">
@@ -6992,7 +6992,7 @@
         <v>597</v>
       </c>
       <c r="C598" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="599">
@@ -7003,7 +7003,7 @@
         <v>598</v>
       </c>
       <c r="C599" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="600">
@@ -7014,7 +7014,7 @@
         <v>599</v>
       </c>
       <c r="C600" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="601">
@@ -7025,7 +7025,7 @@
         <v>600</v>
       </c>
       <c r="C601" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="602">
@@ -7036,7 +7036,7 @@
         <v>601</v>
       </c>
       <c r="C602" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="603">
@@ -7047,7 +7047,7 @@
         <v>602</v>
       </c>
       <c r="C603" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="604">
@@ -7058,7 +7058,7 @@
         <v>603</v>
       </c>
       <c r="C604" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="605">
@@ -7069,7 +7069,7 @@
         <v>604</v>
       </c>
       <c r="C605" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="606">
@@ -7080,7 +7080,7 @@
         <v>605</v>
       </c>
       <c r="C606" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="607">
@@ -7091,7 +7091,7 @@
         <v>606</v>
       </c>
       <c r="C607" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="608">
@@ -7102,7 +7102,7 @@
         <v>607</v>
       </c>
       <c r="C608" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="609">
@@ -7113,7 +7113,7 @@
         <v>608</v>
       </c>
       <c r="C609" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="610">
@@ -7124,7 +7124,7 @@
         <v>609</v>
       </c>
       <c r="C610" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="611">
@@ -7135,7 +7135,7 @@
         <v>610</v>
       </c>
       <c r="C611" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="612">
@@ -7146,7 +7146,7 @@
         <v>611</v>
       </c>
       <c r="C612" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="613">
@@ -7157,7 +7157,7 @@
         <v>612</v>
       </c>
       <c r="C613" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="614">
@@ -7168,7 +7168,7 @@
         <v>613</v>
       </c>
       <c r="C614" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="615">
@@ -7179,7 +7179,7 @@
         <v>614</v>
       </c>
       <c r="C615" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="616">
@@ -7190,7 +7190,7 @@
         <v>615</v>
       </c>
       <c r="C616" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="617">
@@ -7201,7 +7201,7 @@
         <v>616</v>
       </c>
       <c r="C617" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="618">
@@ -7212,7 +7212,7 @@
         <v>617</v>
       </c>
       <c r="C618" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="619">
@@ -7223,7 +7223,7 @@
         <v>618</v>
       </c>
       <c r="C619" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="620">
@@ -7234,7 +7234,7 @@
         <v>619</v>
       </c>
       <c r="C620" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="621">
@@ -7245,7 +7245,7 @@
         <v>620</v>
       </c>
       <c r="C621" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="622">
@@ -7256,7 +7256,7 @@
         <v>621</v>
       </c>
       <c r="C622" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="623">
@@ -7267,7 +7267,7 @@
         <v>622</v>
       </c>
       <c r="C623" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="624">
@@ -7278,7 +7278,7 @@
         <v>623</v>
       </c>
       <c r="C624" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="625">
@@ -7289,7 +7289,7 @@
         <v>624</v>
       </c>
       <c r="C625" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="626">
@@ -7300,7 +7300,7 @@
         <v>625</v>
       </c>
       <c r="C626" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="627">
@@ -7311,7 +7311,7 @@
         <v>626</v>
       </c>
       <c r="C627" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="628">
@@ -7322,7 +7322,7 @@
         <v>627</v>
       </c>
       <c r="C628" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="629">
@@ -7333,7 +7333,7 @@
         <v>628</v>
       </c>
       <c r="C629" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="630">
@@ -7344,7 +7344,7 @@
         <v>629</v>
       </c>
       <c r="C630" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="631">
@@ -7355,7 +7355,7 @@
         <v>630</v>
       </c>
       <c r="C631" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="632">
@@ -7366,7 +7366,7 @@
         <v>631</v>
       </c>
       <c r="C632" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="633">
@@ -7377,7 +7377,7 @@
         <v>632</v>
       </c>
       <c r="C633" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="634">
@@ -7388,7 +7388,7 @@
         <v>633</v>
       </c>
       <c r="C634" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="635">
@@ -7399,7 +7399,7 @@
         <v>634</v>
       </c>
       <c r="C635" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="636">
@@ -7410,7 +7410,7 @@
         <v>635</v>
       </c>
       <c r="C636" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="637">
@@ -7421,7 +7421,7 @@
         <v>636</v>
       </c>
       <c r="C637" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="638">
@@ -7432,7 +7432,7 @@
         <v>637</v>
       </c>
       <c r="C638" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="639">
@@ -7443,7 +7443,7 @@
         <v>638</v>
       </c>
       <c r="C639" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="640">
@@ -7454,7 +7454,7 @@
         <v>639</v>
       </c>
       <c r="C640" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="641">
@@ -7465,7 +7465,7 @@
         <v>640</v>
       </c>
       <c r="C641" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="642">
@@ -7476,7 +7476,7 @@
         <v>641</v>
       </c>
       <c r="C642" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="643">
@@ -7487,7 +7487,7 @@
         <v>642</v>
       </c>
       <c r="C643" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="644">
@@ -7498,7 +7498,7 @@
         <v>643</v>
       </c>
       <c r="C644" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="645">
@@ -7509,7 +7509,7 @@
         <v>644</v>
       </c>
       <c r="C645" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="646">
@@ -7520,7 +7520,7 @@
         <v>645</v>
       </c>
       <c r="C646" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="647">
@@ -7531,7 +7531,7 @@
         <v>646</v>
       </c>
       <c r="C647" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="648">
@@ -7542,7 +7542,7 @@
         <v>647</v>
       </c>
       <c r="C648" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="649">
@@ -7553,7 +7553,7 @@
         <v>648</v>
       </c>
       <c r="C649" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="650">
@@ -7564,7 +7564,7 @@
         <v>649</v>
       </c>
       <c r="C650" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="651">
@@ -7575,7 +7575,7 @@
         <v>650</v>
       </c>
       <c r="C651" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="652">
@@ -7586,7 +7586,7 @@
         <v>651</v>
       </c>
       <c r="C652" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="653">
@@ -7597,7 +7597,7 @@
         <v>652</v>
       </c>
       <c r="C653" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="654">
@@ -7608,7 +7608,7 @@
         <v>653</v>
       </c>
       <c r="C654" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="655">
@@ -7619,7 +7619,7 @@
         <v>654</v>
       </c>
       <c r="C655" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="656">
@@ -7630,7 +7630,7 @@
         <v>655</v>
       </c>
       <c r="C656" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="657">
@@ -7641,7 +7641,7 @@
         <v>656</v>
       </c>
       <c r="C657" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="658">
@@ -7652,7 +7652,7 @@
         <v>657</v>
       </c>
       <c r="C658" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="659">
@@ -7663,7 +7663,7 @@
         <v>658</v>
       </c>
       <c r="C659" t="n">
-        <v>0.868189811706543</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="660">
@@ -7674,7 +7674,7 @@
         <v>659</v>
       </c>
       <c r="C660" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="661">
@@ -7685,7 +7685,7 @@
         <v>660</v>
       </c>
       <c r="C661" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="662">
@@ -7696,7 +7696,7 @@
         <v>661</v>
       </c>
       <c r="C662" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="663">
@@ -7707,7 +7707,7 @@
         <v>662</v>
       </c>
       <c r="C663" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="664">
@@ -7718,7 +7718,7 @@
         <v>663</v>
       </c>
       <c r="C664" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="665">
@@ -7729,7 +7729,7 @@
         <v>664</v>
       </c>
       <c r="C665" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="666">
@@ -7740,7 +7740,7 @@
         <v>665</v>
       </c>
       <c r="C666" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="667">
@@ -7751,7 +7751,7 @@
         <v>666</v>
       </c>
       <c r="C667" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="668">
@@ -7762,7 +7762,7 @@
         <v>667</v>
       </c>
       <c r="C668" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="669">
@@ -7773,7 +7773,7 @@
         <v>668</v>
       </c>
       <c r="C669" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="670">
@@ -7784,7 +7784,7 @@
         <v>669</v>
       </c>
       <c r="C670" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="671">
@@ -7795,7 +7795,7 @@
         <v>670</v>
       </c>
       <c r="C671" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="672">
@@ -7806,7 +7806,7 @@
         <v>671</v>
       </c>
       <c r="C672" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="673">
@@ -7817,7 +7817,7 @@
         <v>672</v>
       </c>
       <c r="C673" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="674">
@@ -7828,7 +7828,7 @@
         <v>673</v>
       </c>
       <c r="C674" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="675">
@@ -7839,7 +7839,7 @@
         <v>674</v>
       </c>
       <c r="C675" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="676">
@@ -7850,7 +7850,7 @@
         <v>675</v>
       </c>
       <c r="C676" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="677">
@@ -7861,7 +7861,7 @@
         <v>676</v>
       </c>
       <c r="C677" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="678">
@@ -7872,7 +7872,7 @@
         <v>677</v>
       </c>
       <c r="C678" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="679">
@@ -7883,7 +7883,7 @@
         <v>678</v>
       </c>
       <c r="C679" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="680">
@@ -7894,7 +7894,7 @@
         <v>679</v>
       </c>
       <c r="C680" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="681">
@@ -7905,7 +7905,7 @@
         <v>680</v>
       </c>
       <c r="C681" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="682">
@@ -7916,7 +7916,7 @@
         <v>681</v>
       </c>
       <c r="C682" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="683">
@@ -7927,7 +7927,7 @@
         <v>682</v>
       </c>
       <c r="C683" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="684">
@@ -7938,7 +7938,7 @@
         <v>683</v>
       </c>
       <c r="C684" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="685">
@@ -7949,7 +7949,7 @@
         <v>684</v>
       </c>
       <c r="C685" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="686">
@@ -7960,7 +7960,7 @@
         <v>685</v>
       </c>
       <c r="C686" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="687">
@@ -7971,7 +7971,7 @@
         <v>686</v>
       </c>
       <c r="C687" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="688">
@@ -7982,7 +7982,7 @@
         <v>687</v>
       </c>
       <c r="C688" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="689">
@@ -7993,7 +7993,7 @@
         <v>688</v>
       </c>
       <c r="C689" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="690">
@@ -8004,7 +8004,7 @@
         <v>689</v>
       </c>
       <c r="C690" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="691">
@@ -8015,7 +8015,7 @@
         <v>690</v>
       </c>
       <c r="C691" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="692">
@@ -8026,7 +8026,7 @@
         <v>691</v>
       </c>
       <c r="C692" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="693">
@@ -8037,7 +8037,7 @@
         <v>692</v>
       </c>
       <c r="C693" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="694">
@@ -8048,7 +8048,7 @@
         <v>693</v>
       </c>
       <c r="C694" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="695">
@@ -8059,7 +8059,7 @@
         <v>694</v>
       </c>
       <c r="C695" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="696">
@@ -8070,7 +8070,7 @@
         <v>695</v>
       </c>
       <c r="C696" t="n">
-        <v>0.862917423248291</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="697">
@@ -8081,7 +8081,7 @@
         <v>696</v>
       </c>
       <c r="C697" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="698">
@@ -8092,7 +8092,7 @@
         <v>697</v>
       </c>
       <c r="C698" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="699">
@@ -8103,7 +8103,7 @@
         <v>698</v>
       </c>
       <c r="C699" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="700">
@@ -8114,7 +8114,7 @@
         <v>699</v>
       </c>
       <c r="C700" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="701">
@@ -8125,7 +8125,7 @@
         <v>700</v>
       </c>
       <c r="C701" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="702">
@@ -8136,7 +8136,7 @@
         <v>701</v>
       </c>
       <c r="C702" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="703">
@@ -8147,7 +8147,7 @@
         <v>702</v>
       </c>
       <c r="C703" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="704">
@@ -8158,7 +8158,7 @@
         <v>703</v>
       </c>
       <c r="C704" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="705">
@@ -8169,7 +8169,7 @@
         <v>704</v>
       </c>
       <c r="C705" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="706">
@@ -8180,7 +8180,7 @@
         <v>705</v>
       </c>
       <c r="C706" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="707">
@@ -8191,7 +8191,7 @@
         <v>706</v>
       </c>
       <c r="C707" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="708">
@@ -8202,7 +8202,7 @@
         <v>707</v>
       </c>
       <c r="C708" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="709">
@@ -8213,7 +8213,7 @@
         <v>708</v>
       </c>
       <c r="C709" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="710">
@@ -8224,7 +8224,7 @@
         <v>709</v>
       </c>
       <c r="C710" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="711">
@@ -8235,7 +8235,7 @@
         <v>710</v>
       </c>
       <c r="C711" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="712">
@@ -8246,7 +8246,7 @@
         <v>711</v>
       </c>
       <c r="C712" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="713">
@@ -8257,7 +8257,7 @@
         <v>712</v>
       </c>
       <c r="C713" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="714">
@@ -8268,7 +8268,7 @@
         <v>713</v>
       </c>
       <c r="C714" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="715">
@@ -8279,7 +8279,7 @@
         <v>714</v>
       </c>
       <c r="C715" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="716">
@@ -8290,7 +8290,7 @@
         <v>715</v>
       </c>
       <c r="C716" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="717">
@@ -8301,7 +8301,7 @@
         <v>716</v>
       </c>
       <c r="C717" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="718">
@@ -8312,7 +8312,7 @@
         <v>717</v>
       </c>
       <c r="C718" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="719">
@@ -8323,7 +8323,7 @@
         <v>718</v>
       </c>
       <c r="C719" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="720">
@@ -8334,7 +8334,7 @@
         <v>719</v>
       </c>
       <c r="C720" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="721">
@@ -8345,7 +8345,7 @@
         <v>720</v>
       </c>
       <c r="C721" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="722">
@@ -8356,7 +8356,7 @@
         <v>721</v>
       </c>
       <c r="C722" t="n">
-        <v>0.868189811706543</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="723">
@@ -8367,7 +8367,7 @@
         <v>722</v>
       </c>
       <c r="C723" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="724">
@@ -8378,7 +8378,7 @@
         <v>723</v>
       </c>
       <c r="C724" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="725">
@@ -8389,7 +8389,7 @@
         <v>724</v>
       </c>
       <c r="C725" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="726">
@@ -8400,7 +8400,7 @@
         <v>725</v>
       </c>
       <c r="C726" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="727">
@@ -8411,7 +8411,7 @@
         <v>726</v>
       </c>
       <c r="C727" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="728">
@@ -8422,7 +8422,7 @@
         <v>727</v>
       </c>
       <c r="C728" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="729">
@@ -8433,7 +8433,7 @@
         <v>728</v>
       </c>
       <c r="C729" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="730">
@@ -8444,7 +8444,7 @@
         <v>729</v>
       </c>
       <c r="C730" t="n">
-        <v>0.868189811706543</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="731">
@@ -8455,7 +8455,7 @@
         <v>730</v>
       </c>
       <c r="C731" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="732">
@@ -8466,7 +8466,7 @@
         <v>731</v>
       </c>
       <c r="C732" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="733">
@@ -8477,7 +8477,7 @@
         <v>732</v>
       </c>
       <c r="C733" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="734">
@@ -8488,7 +8488,7 @@
         <v>733</v>
       </c>
       <c r="C734" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="735">
@@ -8499,7 +8499,7 @@
         <v>734</v>
       </c>
       <c r="C735" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="736">
@@ -8510,7 +8510,7 @@
         <v>735</v>
       </c>
       <c r="C736" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="737">
@@ -8521,7 +8521,7 @@
         <v>736</v>
       </c>
       <c r="C737" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="738">
@@ -8532,7 +8532,7 @@
         <v>737</v>
       </c>
       <c r="C738" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="739">
@@ -8543,7 +8543,7 @@
         <v>738</v>
       </c>
       <c r="C739" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="740">
@@ -8554,7 +8554,7 @@
         <v>739</v>
       </c>
       <c r="C740" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="741">
@@ -8565,7 +8565,7 @@
         <v>740</v>
       </c>
       <c r="C741" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="742">
@@ -8576,7 +8576,7 @@
         <v>741</v>
       </c>
       <c r="C742" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="743">
@@ -8587,7 +8587,7 @@
         <v>742</v>
       </c>
       <c r="C743" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="744">
@@ -8598,7 +8598,7 @@
         <v>743</v>
       </c>
       <c r="C744" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="745">
@@ -8609,7 +8609,7 @@
         <v>744</v>
       </c>
       <c r="C745" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="746">
@@ -8620,7 +8620,7 @@
         <v>745</v>
       </c>
       <c r="C746" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="747">
@@ -8631,7 +8631,7 @@
         <v>746</v>
       </c>
       <c r="C747" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="748">
@@ -8642,7 +8642,7 @@
         <v>747</v>
       </c>
       <c r="C748" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="749">
@@ -8653,7 +8653,7 @@
         <v>748</v>
       </c>
       <c r="C749" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="750">
@@ -8675,7 +8675,7 @@
         <v>750</v>
       </c>
       <c r="C751" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="752">
@@ -8686,7 +8686,7 @@
         <v>751</v>
       </c>
       <c r="C752" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="753">
@@ -8697,7 +8697,7 @@
         <v>752</v>
       </c>
       <c r="C753" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="754">
@@ -8708,7 +8708,7 @@
         <v>753</v>
       </c>
       <c r="C754" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="755">
@@ -8719,7 +8719,7 @@
         <v>754</v>
       </c>
       <c r="C755" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="756">
@@ -8730,7 +8730,7 @@
         <v>755</v>
       </c>
       <c r="C756" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="757">
@@ -8741,7 +8741,7 @@
         <v>756</v>
       </c>
       <c r="C757" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="758">
@@ -8752,7 +8752,7 @@
         <v>757</v>
       </c>
       <c r="C758" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="759">
@@ -8763,7 +8763,7 @@
         <v>758</v>
       </c>
       <c r="C759" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="760">
@@ -8774,7 +8774,7 @@
         <v>759</v>
       </c>
       <c r="C760" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="761">
@@ -8785,7 +8785,7 @@
         <v>760</v>
       </c>
       <c r="C761" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="762">
@@ -8796,7 +8796,7 @@
         <v>761</v>
       </c>
       <c r="C762" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="763">
@@ -8807,7 +8807,7 @@
         <v>762</v>
       </c>
       <c r="C763" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="764">
@@ -8818,7 +8818,7 @@
         <v>763</v>
       </c>
       <c r="C764" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="765">
@@ -8829,7 +8829,7 @@
         <v>764</v>
       </c>
       <c r="C765" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="766">
@@ -8840,7 +8840,7 @@
         <v>765</v>
       </c>
       <c r="C766" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="767">
@@ -8851,7 +8851,7 @@
         <v>766</v>
       </c>
       <c r="C767" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="768">
@@ -8862,7 +8862,7 @@
         <v>767</v>
       </c>
       <c r="C768" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="769">
@@ -8873,7 +8873,7 @@
         <v>768</v>
       </c>
       <c r="C769" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="770">
@@ -8884,7 +8884,7 @@
         <v>769</v>
       </c>
       <c r="C770" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="771">
@@ -8895,7 +8895,7 @@
         <v>770</v>
       </c>
       <c r="C771" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="772">
@@ -8906,7 +8906,7 @@
         <v>771</v>
       </c>
       <c r="C772" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="773">
@@ -8917,7 +8917,7 @@
         <v>772</v>
       </c>
       <c r="C773" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="774">
@@ -8928,7 +8928,7 @@
         <v>773</v>
       </c>
       <c r="C774" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="775">
@@ -8939,7 +8939,7 @@
         <v>774</v>
       </c>
       <c r="C775" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="776">
@@ -8950,7 +8950,7 @@
         <v>775</v>
       </c>
       <c r="C776" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="777">
@@ -8961,7 +8961,7 @@
         <v>776</v>
       </c>
       <c r="C777" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="778">
@@ -8972,7 +8972,7 @@
         <v>777</v>
       </c>
       <c r="C778" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="779">
@@ -8983,7 +8983,7 @@
         <v>778</v>
       </c>
       <c r="C779" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="780">
@@ -8994,7 +8994,7 @@
         <v>779</v>
       </c>
       <c r="C780" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="781">
@@ -9005,7 +9005,7 @@
         <v>780</v>
       </c>
       <c r="C781" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="782">
@@ -9016,7 +9016,7 @@
         <v>781</v>
       </c>
       <c r="C782" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="783">
@@ -9027,7 +9027,7 @@
         <v>782</v>
       </c>
       <c r="C783" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="784">
@@ -9038,7 +9038,7 @@
         <v>783</v>
       </c>
       <c r="C784" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="785">
@@ -9049,7 +9049,7 @@
         <v>784</v>
       </c>
       <c r="C785" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="786">
@@ -9060,7 +9060,7 @@
         <v>785</v>
       </c>
       <c r="C786" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="787">
@@ -9071,7 +9071,7 @@
         <v>786</v>
       </c>
       <c r="C787" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="788">
@@ -9082,7 +9082,7 @@
         <v>787</v>
       </c>
       <c r="C788" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="789">
@@ -9093,7 +9093,7 @@
         <v>788</v>
       </c>
       <c r="C789" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="790">
@@ -9104,7 +9104,7 @@
         <v>789</v>
       </c>
       <c r="C790" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="791">
@@ -9115,7 +9115,7 @@
         <v>790</v>
       </c>
       <c r="C791" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="792">
@@ -9126,7 +9126,7 @@
         <v>791</v>
       </c>
       <c r="C792" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="793">
@@ -9137,7 +9137,7 @@
         <v>792</v>
       </c>
       <c r="C793" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="794">
@@ -9148,7 +9148,7 @@
         <v>793</v>
       </c>
       <c r="C794" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="795">
@@ -9159,7 +9159,7 @@
         <v>794</v>
       </c>
       <c r="C795" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="796">
@@ -9170,7 +9170,7 @@
         <v>795</v>
       </c>
       <c r="C796" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="797">
@@ -9181,7 +9181,7 @@
         <v>796</v>
       </c>
       <c r="C797" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="798">
@@ -9192,7 +9192,7 @@
         <v>797</v>
       </c>
       <c r="C798" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="799">
@@ -9203,7 +9203,7 @@
         <v>798</v>
       </c>
       <c r="C799" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="800">
@@ -9214,7 +9214,7 @@
         <v>799</v>
       </c>
       <c r="C800" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="801">
@@ -9225,7 +9225,7 @@
         <v>800</v>
       </c>
       <c r="C801" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="802">
@@ -9236,7 +9236,7 @@
         <v>801</v>
       </c>
       <c r="C802" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="803">
@@ -9247,7 +9247,7 @@
         <v>802</v>
       </c>
       <c r="C803" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="804">
@@ -9258,7 +9258,7 @@
         <v>803</v>
       </c>
       <c r="C804" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="805">
@@ -9269,7 +9269,7 @@
         <v>804</v>
       </c>
       <c r="C805" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="806">
@@ -9280,7 +9280,7 @@
         <v>805</v>
       </c>
       <c r="C806" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="807">
@@ -9291,7 +9291,7 @@
         <v>806</v>
       </c>
       <c r="C807" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="808">
@@ -9302,7 +9302,7 @@
         <v>807</v>
       </c>
       <c r="C808" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="809">
@@ -9313,7 +9313,7 @@
         <v>808</v>
       </c>
       <c r="C809" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="810">
@@ -9324,7 +9324,7 @@
         <v>809</v>
       </c>
       <c r="C810" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="811">
@@ -9335,7 +9335,7 @@
         <v>810</v>
       </c>
       <c r="C811" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="812">
@@ -9346,7 +9346,7 @@
         <v>811</v>
       </c>
       <c r="C812" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="813">
@@ -9357,7 +9357,7 @@
         <v>812</v>
       </c>
       <c r="C813" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="814">
@@ -9368,7 +9368,7 @@
         <v>813</v>
       </c>
       <c r="C814" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="815">
@@ -9379,7 +9379,7 @@
         <v>814</v>
       </c>
       <c r="C815" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="816">
@@ -9390,7 +9390,7 @@
         <v>815</v>
       </c>
       <c r="C816" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="817">
@@ -9401,7 +9401,7 @@
         <v>816</v>
       </c>
       <c r="C817" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="818">
@@ -9412,7 +9412,7 @@
         <v>817</v>
       </c>
       <c r="C818" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="819">
@@ -9423,7 +9423,7 @@
         <v>818</v>
       </c>
       <c r="C819" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="820">
@@ -9434,7 +9434,7 @@
         <v>819</v>
       </c>
       <c r="C820" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="821">
@@ -9445,7 +9445,7 @@
         <v>820</v>
       </c>
       <c r="C821" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="822">
@@ -9456,7 +9456,7 @@
         <v>821</v>
       </c>
       <c r="C822" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="823">
@@ -9467,7 +9467,7 @@
         <v>822</v>
       </c>
       <c r="C823" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="824">
@@ -9478,7 +9478,7 @@
         <v>823</v>
       </c>
       <c r="C824" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="825">
@@ -9489,7 +9489,7 @@
         <v>824</v>
       </c>
       <c r="C825" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="826">
@@ -9500,7 +9500,7 @@
         <v>825</v>
       </c>
       <c r="C826" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="827">
@@ -9511,7 +9511,7 @@
         <v>826</v>
       </c>
       <c r="C827" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="828">
@@ -9522,7 +9522,7 @@
         <v>827</v>
       </c>
       <c r="C828" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="829">
@@ -9533,7 +9533,7 @@
         <v>828</v>
       </c>
       <c r="C829" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="830">
@@ -9544,7 +9544,7 @@
         <v>829</v>
       </c>
       <c r="C830" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="831">
@@ -9555,7 +9555,7 @@
         <v>830</v>
       </c>
       <c r="C831" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="832">
@@ -9566,7 +9566,7 @@
         <v>831</v>
       </c>
       <c r="C832" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="833">
@@ -9577,7 +9577,7 @@
         <v>832</v>
       </c>
       <c r="C833" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="834">
@@ -9599,7 +9599,7 @@
         <v>834</v>
       </c>
       <c r="C835" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="836">
@@ -9610,7 +9610,7 @@
         <v>835</v>
       </c>
       <c r="C836" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="837">
@@ -9621,7 +9621,7 @@
         <v>836</v>
       </c>
       <c r="C837" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="838">
@@ -9632,7 +9632,7 @@
         <v>837</v>
       </c>
       <c r="C838" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="839">
@@ -9643,7 +9643,7 @@
         <v>838</v>
       </c>
       <c r="C839" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="840">
@@ -9654,7 +9654,7 @@
         <v>839</v>
       </c>
       <c r="C840" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="841">
@@ -9665,7 +9665,7 @@
         <v>840</v>
       </c>
       <c r="C841" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="842">
@@ -9676,7 +9676,7 @@
         <v>841</v>
       </c>
       <c r="C842" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="843">
@@ -9698,7 +9698,7 @@
         <v>843</v>
       </c>
       <c r="C844" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8875219821929932</v>
       </c>
     </row>
     <row r="845">
@@ -9709,7 +9709,7 @@
         <v>844</v>
       </c>
       <c r="C845" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8875219821929932</v>
       </c>
     </row>
     <row r="846">
@@ -9731,7 +9731,7 @@
         <v>846</v>
       </c>
       <c r="C847" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="848">
@@ -9753,7 +9753,7 @@
         <v>848</v>
       </c>
       <c r="C849" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="850">
@@ -9764,7 +9764,7 @@
         <v>849</v>
       </c>
       <c r="C850" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="851">
@@ -9775,7 +9775,7 @@
         <v>850</v>
       </c>
       <c r="C851" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="852">
@@ -9786,7 +9786,7 @@
         <v>851</v>
       </c>
       <c r="C852" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="853">
@@ -9797,7 +9797,7 @@
         <v>852</v>
       </c>
       <c r="C853" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="854">
@@ -9808,7 +9808,7 @@
         <v>853</v>
       </c>
       <c r="C854" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="855">
@@ -9819,7 +9819,7 @@
         <v>854</v>
       </c>
       <c r="C855" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="856">
@@ -9830,7 +9830,7 @@
         <v>855</v>
       </c>
       <c r="C856" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="857">
@@ -9841,7 +9841,7 @@
         <v>856</v>
       </c>
       <c r="C857" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="858">
@@ -9852,7 +9852,7 @@
         <v>857</v>
       </c>
       <c r="C858" t="n">
-        <v>0.880492091178894</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="859">
@@ -9863,7 +9863,7 @@
         <v>858</v>
       </c>
       <c r="C859" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="860">
@@ -9874,7 +9874,7 @@
         <v>859</v>
       </c>
       <c r="C860" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="861">
@@ -9885,7 +9885,7 @@
         <v>860</v>
       </c>
       <c r="C861" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="862">
@@ -9896,7 +9896,7 @@
         <v>861</v>
       </c>
       <c r="C862" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="863">
@@ -9907,7 +9907,7 @@
         <v>862</v>
       </c>
       <c r="C863" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="864">
@@ -9918,7 +9918,7 @@
         <v>863</v>
       </c>
       <c r="C864" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="865">
@@ -9929,7 +9929,7 @@
         <v>864</v>
       </c>
       <c r="C865" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="866">
@@ -9940,7 +9940,7 @@
         <v>865</v>
       </c>
       <c r="C866" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="867">
@@ -9951,7 +9951,7 @@
         <v>866</v>
       </c>
       <c r="C867" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="868">
@@ -9962,7 +9962,7 @@
         <v>867</v>
       </c>
       <c r="C868" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="869">
@@ -9973,7 +9973,7 @@
         <v>868</v>
       </c>
       <c r="C869" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="870">
@@ -9984,7 +9984,7 @@
         <v>869</v>
       </c>
       <c r="C870" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="871">
@@ -9995,7 +9995,7 @@
         <v>870</v>
       </c>
       <c r="C871" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="872">
@@ -10006,7 +10006,7 @@
         <v>871</v>
       </c>
       <c r="C872" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="873">
@@ -10017,7 +10017,7 @@
         <v>872</v>
       </c>
       <c r="C873" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="874">
@@ -10028,7 +10028,7 @@
         <v>873</v>
       </c>
       <c r="C874" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="875">
@@ -10039,7 +10039,7 @@
         <v>874</v>
       </c>
       <c r="C875" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="876">
@@ -10050,7 +10050,7 @@
         <v>875</v>
       </c>
       <c r="C876" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="877">
@@ -10061,7 +10061,7 @@
         <v>876</v>
       </c>
       <c r="C877" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="878">
@@ -10072,7 +10072,7 @@
         <v>877</v>
       </c>
       <c r="C878" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="879">
@@ -10083,7 +10083,7 @@
         <v>878</v>
       </c>
       <c r="C879" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="880">
@@ -10094,7 +10094,7 @@
         <v>879</v>
       </c>
       <c r="C880" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="881">
@@ -10105,7 +10105,7 @@
         <v>880</v>
       </c>
       <c r="C881" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="882">
@@ -10116,7 +10116,7 @@
         <v>881</v>
       </c>
       <c r="C882" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="883">
@@ -10127,7 +10127,7 @@
         <v>882</v>
       </c>
       <c r="C883" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="884">
@@ -10138,7 +10138,7 @@
         <v>883</v>
       </c>
       <c r="C884" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="885">
@@ -10149,7 +10149,7 @@
         <v>884</v>
       </c>
       <c r="C885" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="886">
@@ -10160,7 +10160,7 @@
         <v>885</v>
       </c>
       <c r="C886" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="887">
@@ -10171,7 +10171,7 @@
         <v>886</v>
       </c>
       <c r="C887" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="888">
@@ -10182,7 +10182,7 @@
         <v>887</v>
       </c>
       <c r="C888" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="889">
@@ -10193,7 +10193,7 @@
         <v>888</v>
       </c>
       <c r="C889" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="890">
@@ -10204,7 +10204,7 @@
         <v>889</v>
       </c>
       <c r="C890" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="891">
@@ -10215,7 +10215,7 @@
         <v>890</v>
       </c>
       <c r="C891" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="892">
@@ -10226,7 +10226,7 @@
         <v>891</v>
       </c>
       <c r="C892" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="893">
@@ -10237,7 +10237,7 @@
         <v>892</v>
       </c>
       <c r="C893" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="894">
@@ -10248,7 +10248,7 @@
         <v>893</v>
       </c>
       <c r="C894" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="895">
@@ -10259,7 +10259,7 @@
         <v>894</v>
       </c>
       <c r="C895" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="896">
@@ -10270,7 +10270,7 @@
         <v>895</v>
       </c>
       <c r="C896" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="897">
@@ -10281,7 +10281,7 @@
         <v>896</v>
       </c>
       <c r="C897" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="898">
@@ -10292,7 +10292,7 @@
         <v>897</v>
       </c>
       <c r="C898" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="899">
@@ -10303,7 +10303,7 @@
         <v>898</v>
       </c>
       <c r="C899" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="900">
@@ -10314,7 +10314,7 @@
         <v>899</v>
       </c>
       <c r="C900" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="901">
@@ -10325,7 +10325,7 @@
         <v>900</v>
       </c>
       <c r="C901" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="902">
@@ -10336,7 +10336,7 @@
         <v>901</v>
       </c>
       <c r="C902" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="903">
@@ -10347,7 +10347,7 @@
         <v>902</v>
       </c>
       <c r="C903" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="904">
@@ -10369,7 +10369,7 @@
         <v>904</v>
       </c>
       <c r="C905" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="906">
@@ -10380,7 +10380,7 @@
         <v>905</v>
       </c>
       <c r="C906" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="907">
@@ -10391,7 +10391,7 @@
         <v>906</v>
       </c>
       <c r="C907" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="908">
@@ -10402,7 +10402,7 @@
         <v>907</v>
       </c>
       <c r="C908" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="909">
@@ -10413,7 +10413,7 @@
         <v>908</v>
       </c>
       <c r="C909" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="910">
@@ -10424,7 +10424,7 @@
         <v>909</v>
       </c>
       <c r="C910" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="911">
@@ -10435,7 +10435,7 @@
         <v>910</v>
       </c>
       <c r="C911" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="912">
@@ -10446,7 +10446,7 @@
         <v>911</v>
       </c>
       <c r="C912" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="913">
@@ -10457,7 +10457,7 @@
         <v>912</v>
       </c>
       <c r="C913" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="914">
@@ -10468,7 +10468,7 @@
         <v>913</v>
       </c>
       <c r="C914" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="915">
@@ -10479,7 +10479,7 @@
         <v>914</v>
       </c>
       <c r="C915" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="916">
@@ -10490,7 +10490,7 @@
         <v>915</v>
       </c>
       <c r="C916" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="917">
@@ -10501,7 +10501,7 @@
         <v>916</v>
       </c>
       <c r="C917" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="918">
@@ -10512,7 +10512,7 @@
         <v>917</v>
       </c>
       <c r="C918" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="919">
@@ -10523,7 +10523,7 @@
         <v>918</v>
       </c>
       <c r="C919" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="920">
@@ -10534,7 +10534,7 @@
         <v>919</v>
       </c>
       <c r="C920" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="921">
@@ -10545,7 +10545,7 @@
         <v>920</v>
       </c>
       <c r="C921" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="922">
@@ -10556,7 +10556,7 @@
         <v>921</v>
       </c>
       <c r="C922" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="923">
@@ -10567,7 +10567,7 @@
         <v>922</v>
       </c>
       <c r="C923" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="924">
@@ -10578,7 +10578,7 @@
         <v>923</v>
       </c>
       <c r="C924" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="925">
@@ -10589,7 +10589,7 @@
         <v>924</v>
       </c>
       <c r="C925" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="926">
@@ -10600,7 +10600,7 @@
         <v>925</v>
       </c>
       <c r="C926" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="927">
@@ -10611,7 +10611,7 @@
         <v>926</v>
       </c>
       <c r="C927" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="928">
@@ -10622,7 +10622,7 @@
         <v>927</v>
       </c>
       <c r="C928" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="929">
@@ -10633,7 +10633,7 @@
         <v>928</v>
       </c>
       <c r="C929" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="930">
@@ -10644,7 +10644,7 @@
         <v>929</v>
       </c>
       <c r="C930" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="931">
@@ -10655,7 +10655,7 @@
         <v>930</v>
       </c>
       <c r="C931" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="932">
@@ -10666,7 +10666,7 @@
         <v>931</v>
       </c>
       <c r="C932" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="933">
@@ -10677,7 +10677,7 @@
         <v>932</v>
       </c>
       <c r="C933" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="934">
@@ -10688,7 +10688,7 @@
         <v>933</v>
       </c>
       <c r="C934" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="935">
@@ -10699,7 +10699,7 @@
         <v>934</v>
       </c>
       <c r="C935" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="936">
@@ -10710,7 +10710,7 @@
         <v>935</v>
       </c>
       <c r="C936" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="937">
@@ -10721,7 +10721,7 @@
         <v>936</v>
       </c>
       <c r="C937" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="938">
@@ -10732,7 +10732,7 @@
         <v>937</v>
       </c>
       <c r="C938" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="939">
@@ -10743,7 +10743,7 @@
         <v>938</v>
       </c>
       <c r="C939" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="940">
@@ -10754,7 +10754,7 @@
         <v>939</v>
       </c>
       <c r="C940" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="941">
@@ -10765,7 +10765,7 @@
         <v>940</v>
       </c>
       <c r="C941" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="942">
@@ -10776,7 +10776,7 @@
         <v>941</v>
       </c>
       <c r="C942" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="943">
@@ -10787,7 +10787,7 @@
         <v>942</v>
       </c>
       <c r="C943" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="944">
@@ -10798,7 +10798,7 @@
         <v>943</v>
       </c>
       <c r="C944" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="945">
@@ -10809,7 +10809,7 @@
         <v>944</v>
       </c>
       <c r="C945" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="946">
@@ -10820,7 +10820,7 @@
         <v>945</v>
       </c>
       <c r="C946" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="947">
@@ -10831,7 +10831,7 @@
         <v>946</v>
       </c>
       <c r="C947" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="948">
@@ -10842,7 +10842,7 @@
         <v>947</v>
       </c>
       <c r="C948" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="949">
@@ -10853,7 +10853,7 @@
         <v>948</v>
       </c>
       <c r="C949" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="950">
@@ -10864,7 +10864,7 @@
         <v>949</v>
       </c>
       <c r="C950" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="951">
@@ -10875,7 +10875,7 @@
         <v>950</v>
       </c>
       <c r="C951" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="952">
@@ -10886,7 +10886,7 @@
         <v>951</v>
       </c>
       <c r="C952" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="953">
@@ -10897,7 +10897,7 @@
         <v>952</v>
       </c>
       <c r="C953" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="954">
@@ -10908,7 +10908,7 @@
         <v>953</v>
       </c>
       <c r="C954" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="955">
@@ -10919,7 +10919,7 @@
         <v>954</v>
       </c>
       <c r="C955" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="956">
@@ -10930,7 +10930,7 @@
         <v>955</v>
       </c>
       <c r="C956" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="957">
@@ -10941,7 +10941,7 @@
         <v>956</v>
       </c>
       <c r="C957" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="958">
@@ -10952,7 +10952,7 @@
         <v>957</v>
       </c>
       <c r="C958" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="959">
@@ -10963,7 +10963,7 @@
         <v>958</v>
       </c>
       <c r="C959" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="960">
@@ -10974,7 +10974,7 @@
         <v>959</v>
       </c>
       <c r="C960" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="961">
@@ -10985,7 +10985,7 @@
         <v>960</v>
       </c>
       <c r="C961" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="962">
@@ -10996,7 +10996,7 @@
         <v>961</v>
       </c>
       <c r="C962" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="963">
@@ -11007,7 +11007,7 @@
         <v>962</v>
       </c>
       <c r="C963" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="964">
@@ -11018,7 +11018,7 @@
         <v>963</v>
       </c>
       <c r="C964" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="965">
@@ -11029,7 +11029,7 @@
         <v>964</v>
       </c>
       <c r="C965" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="966">
@@ -11040,7 +11040,7 @@
         <v>965</v>
       </c>
       <c r="C966" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="967">
@@ -11051,7 +11051,7 @@
         <v>966</v>
       </c>
       <c r="C967" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="968">
@@ -11062,7 +11062,7 @@
         <v>967</v>
       </c>
       <c r="C968" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="969">
@@ -11073,7 +11073,7 @@
         <v>968</v>
       </c>
       <c r="C969" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="970">
@@ -11084,7 +11084,7 @@
         <v>969</v>
       </c>
       <c r="C970" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="971">
@@ -11095,7 +11095,7 @@
         <v>970</v>
       </c>
       <c r="C971" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="972">
@@ -11106,7 +11106,7 @@
         <v>971</v>
       </c>
       <c r="C972" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="973">
@@ -11117,7 +11117,7 @@
         <v>972</v>
       </c>
       <c r="C973" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="974">
@@ -11128,7 +11128,7 @@
         <v>973</v>
       </c>
       <c r="C974" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="975">
@@ -11139,7 +11139,7 @@
         <v>974</v>
       </c>
       <c r="C975" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="976">
@@ -11150,7 +11150,7 @@
         <v>975</v>
       </c>
       <c r="C976" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="977">
@@ -11161,7 +11161,7 @@
         <v>976</v>
       </c>
       <c r="C977" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="978">
@@ -11172,7 +11172,7 @@
         <v>977</v>
       </c>
       <c r="C978" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="979">
@@ -11183,7 +11183,7 @@
         <v>978</v>
       </c>
       <c r="C979" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="980">
@@ -11194,7 +11194,7 @@
         <v>979</v>
       </c>
       <c r="C980" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="981">
@@ -11205,7 +11205,7 @@
         <v>980</v>
       </c>
       <c r="C981" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="982">
@@ -11216,7 +11216,7 @@
         <v>981</v>
       </c>
       <c r="C982" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="983">
@@ -11227,7 +11227,7 @@
         <v>982</v>
       </c>
       <c r="C983" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="984">
@@ -11238,7 +11238,7 @@
         <v>983</v>
       </c>
       <c r="C984" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="985">
@@ -11249,7 +11249,7 @@
         <v>984</v>
       </c>
       <c r="C985" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="986">
@@ -11260,7 +11260,7 @@
         <v>985</v>
       </c>
       <c r="C986" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="987">
@@ -11271,7 +11271,7 @@
         <v>986</v>
       </c>
       <c r="C987" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="988">
@@ -11282,7 +11282,7 @@
         <v>987</v>
       </c>
       <c r="C988" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="989">
@@ -11293,7 +11293,7 @@
         <v>988</v>
       </c>
       <c r="C989" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="990">
@@ -11304,7 +11304,7 @@
         <v>989</v>
       </c>
       <c r="C990" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="991">
@@ -11315,7 +11315,7 @@
         <v>990</v>
       </c>
       <c r="C991" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="992">
@@ -11326,7 +11326,7 @@
         <v>991</v>
       </c>
       <c r="C992" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="993">
@@ -11337,7 +11337,7 @@
         <v>992</v>
       </c>
       <c r="C993" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8840070366859436</v>
       </c>
     </row>
     <row r="994">
@@ -11348,7 +11348,7 @@
         <v>993</v>
       </c>
       <c r="C994" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="995">
@@ -11359,7 +11359,7 @@
         <v>994</v>
       </c>
       <c r="C995" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.885764479637146</v>
       </c>
     </row>
     <row r="996">
@@ -11370,7 +11370,7 @@
         <v>995</v>
       </c>
       <c r="C996" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="997">
@@ -11381,7 +11381,7 @@
         <v>996</v>
       </c>
       <c r="C997" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="998">
@@ -11392,7 +11392,7 @@
         <v>997</v>
       </c>
       <c r="C998" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="999">
@@ -11403,7 +11403,7 @@
         <v>998</v>
       </c>
       <c r="C999" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
     <row r="1000">
@@ -11414,7 +11414,7 @@
         <v>999</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="1001">
@@ -11425,7 +11425,7 @@
         <v>1000</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8822495341300964</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6678383350372314</v>
+        <v>0.5483304262161255</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7592267394065857</v>
+        <v>0.6203866600990295</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7557117938995361</v>
+        <v>0.6326889395713806</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7328646779060364</v>
+        <v>0.6449912190437317</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7346221208572388</v>
+        <v>0.6660808324813843</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7363796234130859</v>
+        <v>0.6818980574607849</v>
       </c>
     </row>
     <row r="8">
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7293497323989868</v>
+        <v>0.694200336933136</v>
       </c>
     </row>
     <row r="9">
@@ -513,7 +513,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7328646779060364</v>
+        <v>0.7047451734542847</v>
       </c>
     </row>
     <row r="10">
@@ -524,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7346221208572388</v>
+        <v>0.7188048958778381</v>
       </c>
     </row>
     <row r="11">
@@ -535,7 +535,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7381370663642883</v>
+        <v>0.7346221208572388</v>
       </c>
     </row>
     <row r="12">
@@ -546,7 +546,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7363796234130859</v>
+        <v>0.7381370663642883</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7398945689201355</v>
+        <v>0.7434095144271851</v>
       </c>
     </row>
     <row r="14">
@@ -568,7 +568,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7434095144271851</v>
+        <v>0.7504393458366394</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.748681902885437</v>
+        <v>0.753954291343689</v>
       </c>
     </row>
     <row r="16">
@@ -590,7 +590,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.753954291343689</v>
+        <v>0.76625657081604</v>
       </c>
     </row>
     <row r="17">
@@ -601,7 +601,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7557117938995361</v>
+        <v>0.7680140733718872</v>
       </c>
     </row>
     <row r="18">
@@ -612,7 +612,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7592267394065857</v>
+        <v>0.7627416253089905</v>
       </c>
     </row>
     <row r="19">
@@ -623,7 +623,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7592267394065857</v>
+        <v>0.7768014073371887</v>
       </c>
     </row>
     <row r="20">
@@ -634,7 +634,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7592267394065857</v>
+        <v>0.7820737957954407</v>
       </c>
     </row>
     <row r="21">
@@ -645,7 +645,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7820737957954407</v>
+        <v>0.7891036868095398</v>
       </c>
     </row>
     <row r="22">
@@ -656,7 +656,7 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7891036868095398</v>
+        <v>0.7961335778236389</v>
       </c>
     </row>
     <row r="23">
@@ -667,7 +667,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7926186323165894</v>
+        <v>0.803163468837738</v>
       </c>
     </row>
     <row r="24">
@@ -678,7 +678,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7926186323165894</v>
+        <v>0.8014059662818909</v>
       </c>
     </row>
     <row r="25">
@@ -689,7 +689,7 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7996485233306885</v>
+        <v>0.803163468837738</v>
       </c>
     </row>
     <row r="26">
@@ -700,7 +700,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8014059662818909</v>
+        <v>0.803163468837738</v>
       </c>
     </row>
     <row r="27">
@@ -711,7 +711,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7978910207748413</v>
+        <v>0.8049209117889404</v>
       </c>
     </row>
     <row r="28">
@@ -722,7 +722,7 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7996485233306885</v>
+        <v>0.8066783547401428</v>
       </c>
     </row>
     <row r="29">
@@ -733,7 +733,7 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7943760752677917</v>
+        <v>0.8049209117889404</v>
       </c>
     </row>
     <row r="30">
@@ -744,7 +744,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7943760752677917</v>
+        <v>0.803163468837738</v>
       </c>
     </row>
     <row r="31">
@@ -755,7 +755,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7926186323165894</v>
+        <v>0.8101933002471924</v>
       </c>
     </row>
     <row r="32">
@@ -766,7 +766,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>0.790861189365387</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="33">
@@ -777,7 +777,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7926186323165894</v>
+        <v>0.8172231912612915</v>
       </c>
     </row>
     <row r="34">
@@ -788,7 +788,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7978910207748413</v>
+        <v>0.8207381367683411</v>
       </c>
     </row>
     <row r="35">
@@ -799,7 +799,7 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7978910207748413</v>
+        <v>0.8137082457542419</v>
       </c>
     </row>
     <row r="36">
@@ -810,7 +810,7 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7961335778236389</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="37">
@@ -821,7 +821,7 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7961335778236389</v>
+        <v>0.8137082457542419</v>
       </c>
     </row>
     <row r="38">
@@ -832,7 +832,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7961335778236389</v>
+        <v>0.8101933002471924</v>
       </c>
     </row>
     <row r="39">
@@ -843,7 +843,7 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8014059662818909</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="40">
@@ -854,7 +854,7 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8014059662818909</v>
+        <v>0.8101933002471924</v>
       </c>
     </row>
     <row r="41">
@@ -865,7 +865,7 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8049209117889404</v>
+        <v>0.8137082457542419</v>
       </c>
     </row>
     <row r="42">
@@ -876,7 +876,7 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8119508028030396</v>
+        <v>0.8101933002471924</v>
       </c>
     </row>
     <row r="43">
@@ -887,7 +887,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>0.80843585729599</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="44">
@@ -909,7 +909,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8119508028030396</v>
+        <v>0.8101933002471924</v>
       </c>
     </row>
     <row r="46">
@@ -920,7 +920,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8119508028030396</v>
+        <v>0.8101933002471924</v>
       </c>
     </row>
     <row r="47">
@@ -931,7 +931,7 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8119508028030396</v>
+        <v>0.8137082457542419</v>
       </c>
     </row>
     <row r="48">
@@ -953,7 +953,7 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8154657483100891</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="50">
@@ -964,7 +964,7 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8172231912612915</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="51">
@@ -975,7 +975,7 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8172231912612915</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="52">
@@ -986,7 +986,7 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8172231912612915</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="53">
@@ -997,7 +997,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8189806938171387</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="54">
@@ -1008,7 +1008,7 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8224955797195435</v>
+        <v>0.8119508028030396</v>
       </c>
     </row>
     <row r="55">
@@ -1019,7 +1019,7 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8242530822753906</v>
+        <v>0.8137082457542419</v>
       </c>
     </row>
     <row r="56">
@@ -1030,7 +1030,7 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>0.826010525226593</v>
+        <v>0.8154657483100891</v>
       </c>
     </row>
     <row r="57">
@@ -1041,7 +1041,7 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8295254707336426</v>
+        <v>0.8172231912612915</v>
       </c>
     </row>
     <row r="58">
@@ -1052,7 +1052,7 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8312829732894897</v>
+        <v>0.8189806938171387</v>
       </c>
     </row>
     <row r="59">
@@ -1063,7 +1063,7 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8312829732894897</v>
+        <v>0.8224955797195435</v>
       </c>
     </row>
     <row r="60">
@@ -1074,7 +1074,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8312829732894897</v>
+        <v>0.8189806938171387</v>
       </c>
     </row>
     <row r="61">
@@ -1085,7 +1085,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8295254707336426</v>
+        <v>0.826010525226593</v>
       </c>
     </row>
     <row r="62">
@@ -1096,7 +1096,7 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8330404162406921</v>
+        <v>0.826010525226593</v>
       </c>
     </row>
     <row r="63">
@@ -1107,7 +1107,7 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8224955797195435</v>
       </c>
     </row>
     <row r="64">
@@ -1118,7 +1118,7 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8224955797195435</v>
       </c>
     </row>
     <row r="65">
@@ -1129,7 +1129,7 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8207381367683411</v>
       </c>
     </row>
     <row r="66">
@@ -1140,7 +1140,7 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8242530822753906</v>
       </c>
     </row>
     <row r="67">
@@ -1151,7 +1151,7 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8277680277824402</v>
       </c>
     </row>
     <row r="68">
@@ -1162,7 +1162,7 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8277680277824402</v>
       </c>
     </row>
     <row r="69">
@@ -1173,7 +1173,7 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8277680277824402</v>
       </c>
     </row>
     <row r="70">
@@ -1184,7 +1184,7 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8347979187965393</v>
+        <v>0.8295254707336426</v>
       </c>
     </row>
     <row r="71">
@@ -1195,7 +1195,7 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8295254707336426</v>
       </c>
     </row>
     <row r="72">
@@ -1206,7 +1206,7 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8312829732894897</v>
       </c>
     </row>
     <row r="73">
@@ -1217,7 +1217,7 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8330404162406921</v>
       </c>
     </row>
     <row r="74">
@@ -1228,7 +1228,7 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8330404162406921</v>
       </c>
     </row>
     <row r="75">
@@ -1239,7 +1239,7 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8365553617477417</v>
+        <v>0.8330404162406921</v>
       </c>
     </row>
     <row r="76">
@@ -1250,7 +1250,7 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="77">
@@ -1261,7 +1261,7 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="78">
@@ -1272,7 +1272,7 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="79">
@@ -1283,7 +1283,7 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="80">
@@ -1294,7 +1294,7 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="81">
@@ -1305,7 +1305,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="82">
@@ -1316,7 +1316,7 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="83">
@@ -1327,7 +1327,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="84">
@@ -1338,7 +1338,7 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8347979187965393</v>
       </c>
     </row>
     <row r="85">
@@ -1349,7 +1349,7 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8347979187965393</v>
       </c>
     </row>
     <row r="86">
@@ -1360,7 +1360,7 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8347979187965393</v>
       </c>
     </row>
     <row r="87">
@@ -1371,7 +1371,7 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8347979187965393</v>
       </c>
     </row>
     <row r="88">
@@ -1382,7 +1382,7 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8347979187965393</v>
       </c>
     </row>
     <row r="89">
@@ -1393,7 +1393,7 @@
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8330404162406921</v>
       </c>
     </row>
     <row r="90">
@@ -1404,7 +1404,7 @@
         <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8347979187965393</v>
       </c>
     </row>
     <row r="91">
@@ -1415,7 +1415,7 @@
         <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="92">
@@ -1426,7 +1426,7 @@
         <v>91</v>
       </c>
       <c r="C92" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8330404162406921</v>
       </c>
     </row>
     <row r="93">
@@ -1437,7 +1437,7 @@
         <v>92</v>
       </c>
       <c r="C93" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8330404162406921</v>
       </c>
     </row>
     <row r="94">
@@ -1448,7 +1448,7 @@
         <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8330404162406921</v>
       </c>
     </row>
     <row r="95">
@@ -1459,7 +1459,7 @@
         <v>94</v>
       </c>
       <c r="C95" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8347979187965393</v>
       </c>
     </row>
     <row r="96">
@@ -1470,7 +1470,7 @@
         <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8365553617477417</v>
       </c>
     </row>
     <row r="97">
@@ -1481,7 +1481,7 @@
         <v>96</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8383128046989441</v>
       </c>
     </row>
     <row r="98">
@@ -1492,7 +1492,7 @@
         <v>97</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="99">
@@ -1503,7 +1503,7 @@
         <v>98</v>
       </c>
       <c r="C99" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="100">
@@ -1514,7 +1514,7 @@
         <v>99</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="101">
@@ -1525,7 +1525,7 @@
         <v>100</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="102">
@@ -1536,7 +1536,7 @@
         <v>101</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="103">
@@ -1547,7 +1547,7 @@
         <v>102</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="104">
@@ -1558,7 +1558,7 @@
         <v>103</v>
       </c>
       <c r="C104" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="105">
@@ -1569,7 +1569,7 @@
         <v>104</v>
       </c>
       <c r="C105" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="106">
@@ -1591,7 +1591,7 @@
         <v>106</v>
       </c>
       <c r="C107" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="108">
@@ -1602,7 +1602,7 @@
         <v>107</v>
       </c>
       <c r="C108" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="109">
@@ -1613,7 +1613,7 @@
         <v>108</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="110">
@@ -1657,7 +1657,7 @@
         <v>112</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="114">
@@ -1668,7 +1668,7 @@
         <v>113</v>
       </c>
       <c r="C114" t="n">
-        <v>0.8383128046989441</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="115">
@@ -1679,7 +1679,7 @@
         <v>114</v>
       </c>
       <c r="C115" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="116">
@@ -1690,7 +1690,7 @@
         <v>115</v>
       </c>
       <c r="C116" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="117">
@@ -1712,7 +1712,7 @@
         <v>117</v>
       </c>
       <c r="C118" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="119">
@@ -1723,7 +1723,7 @@
         <v>118</v>
       </c>
       <c r="C119" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="120">
@@ -1734,7 +1734,7 @@
         <v>119</v>
       </c>
       <c r="C120" t="n">
-        <v>0.8418277502059937</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="121">
@@ -1745,7 +1745,7 @@
         <v>120</v>
       </c>
       <c r="C121" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="122">
@@ -1756,7 +1756,7 @@
         <v>121</v>
       </c>
       <c r="C122" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8400703072547913</v>
       </c>
     </row>
     <row r="123">
@@ -1767,7 +1767,7 @@
         <v>122</v>
       </c>
       <c r="C123" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="124">
@@ -1778,7 +1778,7 @@
         <v>123</v>
       </c>
       <c r="C124" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="125">
@@ -1789,7 +1789,7 @@
         <v>124</v>
       </c>
       <c r="C125" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="126">
@@ -1800,7 +1800,7 @@
         <v>125</v>
       </c>
       <c r="C126" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="127">
@@ -1811,7 +1811,7 @@
         <v>126</v>
       </c>
       <c r="C127" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="128">
@@ -1822,7 +1822,7 @@
         <v>127</v>
       </c>
       <c r="C128" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="129">
@@ -1833,7 +1833,7 @@
         <v>128</v>
       </c>
       <c r="C129" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="130">
@@ -1844,7 +1844,7 @@
         <v>129</v>
       </c>
       <c r="C130" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="131">
@@ -1855,7 +1855,7 @@
         <v>130</v>
       </c>
       <c r="C131" t="n">
-        <v>0.8400703072547913</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="132">
@@ -1877,7 +1877,7 @@
         <v>132</v>
       </c>
       <c r="C133" t="n">
-        <v>0.8435852527618408</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="134">
@@ -1888,7 +1888,7 @@
         <v>133</v>
       </c>
       <c r="C134" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8418277502059937</v>
       </c>
     </row>
     <row r="135">
@@ -1932,7 +1932,7 @@
         <v>137</v>
       </c>
       <c r="C138" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="139">
@@ -1943,7 +1943,7 @@
         <v>138</v>
       </c>
       <c r="C139" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="140">
@@ -1954,7 +1954,7 @@
         <v>139</v>
       </c>
       <c r="C140" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="141">
@@ -1965,7 +1965,7 @@
         <v>140</v>
       </c>
       <c r="C141" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="142">
@@ -1987,7 +1987,7 @@
         <v>142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="144">
@@ -1998,7 +1998,7 @@
         <v>143</v>
       </c>
       <c r="C144" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="145">
@@ -2009,7 +2009,7 @@
         <v>144</v>
       </c>
       <c r="C145" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="146">
@@ -2031,7 +2031,7 @@
         <v>146</v>
       </c>
       <c r="C147" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="148">
@@ -2042,7 +2042,7 @@
         <v>147</v>
       </c>
       <c r="C148" t="n">
-        <v>0.8453426957130432</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="149">
@@ -2053,7 +2053,7 @@
         <v>148</v>
       </c>
       <c r="C149" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="150">
@@ -2064,7 +2064,7 @@
         <v>149</v>
       </c>
       <c r="C150" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="151">
@@ -2075,7 +2075,7 @@
         <v>150</v>
       </c>
       <c r="C151" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="152">
@@ -2086,7 +2086,7 @@
         <v>151</v>
       </c>
       <c r="C152" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8435852527618408</v>
       </c>
     </row>
     <row r="153">
@@ -2097,7 +2097,7 @@
         <v>152</v>
       </c>
       <c r="C153" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="154">
@@ -2108,7 +2108,7 @@
         <v>153</v>
       </c>
       <c r="C154" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="155">
@@ -2119,7 +2119,7 @@
         <v>154</v>
       </c>
       <c r="C155" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="156">
@@ -2130,7 +2130,7 @@
         <v>155</v>
       </c>
       <c r="C156" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="157">
@@ -2141,7 +2141,7 @@
         <v>156</v>
       </c>
       <c r="C157" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="158">
@@ -2152,7 +2152,7 @@
         <v>157</v>
       </c>
       <c r="C158" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="159">
@@ -2163,7 +2163,7 @@
         <v>158</v>
       </c>
       <c r="C159" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="160">
@@ -2218,7 +2218,7 @@
         <v>163</v>
       </c>
       <c r="C164" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="165">
@@ -2229,7 +2229,7 @@
         <v>164</v>
       </c>
       <c r="C165" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="166">
@@ -2240,7 +2240,7 @@
         <v>165</v>
       </c>
       <c r="C166" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="167">
@@ -2251,7 +2251,7 @@
         <v>166</v>
       </c>
       <c r="C167" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="168">
@@ -2262,7 +2262,7 @@
         <v>167</v>
       </c>
       <c r="C168" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="169">
@@ -2273,7 +2273,7 @@
         <v>168</v>
       </c>
       <c r="C169" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="170">
@@ -2317,7 +2317,7 @@
         <v>172</v>
       </c>
       <c r="C173" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="174">
@@ -2328,7 +2328,7 @@
         <v>173</v>
       </c>
       <c r="C174" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="175">
@@ -2339,7 +2339,7 @@
         <v>174</v>
       </c>
       <c r="C175" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="176">
@@ -2350,7 +2350,7 @@
         <v>175</v>
       </c>
       <c r="C176" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="177">
@@ -2361,7 +2361,7 @@
         <v>176</v>
       </c>
       <c r="C177" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="178">
@@ -2372,7 +2372,7 @@
         <v>177</v>
       </c>
       <c r="C178" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="179">
@@ -2383,7 +2383,7 @@
         <v>178</v>
       </c>
       <c r="C179" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="180">
@@ -2394,7 +2394,7 @@
         <v>179</v>
       </c>
       <c r="C180" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="181">
@@ -2405,7 +2405,7 @@
         <v>180</v>
       </c>
       <c r="C181" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="182">
@@ -2416,7 +2416,7 @@
         <v>181</v>
       </c>
       <c r="C182" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="183">
@@ -2427,7 +2427,7 @@
         <v>182</v>
       </c>
       <c r="C183" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="184">
@@ -2438,7 +2438,7 @@
         <v>183</v>
       </c>
       <c r="C184" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="185">
@@ -2449,7 +2449,7 @@
         <v>184</v>
       </c>
       <c r="C185" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="186">
@@ -2460,7 +2460,7 @@
         <v>185</v>
       </c>
       <c r="C186" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="187">
@@ -2471,7 +2471,7 @@
         <v>186</v>
       </c>
       <c r="C187" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="188">
@@ -2482,7 +2482,7 @@
         <v>187</v>
       </c>
       <c r="C188" t="n">
-        <v>0.8506151437759399</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="189">
@@ -2493,7 +2493,7 @@
         <v>188</v>
       </c>
       <c r="C189" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="190">
@@ -2504,7 +2504,7 @@
         <v>189</v>
       </c>
       <c r="C190" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="191">
@@ -2515,7 +2515,7 @@
         <v>190</v>
       </c>
       <c r="C191" t="n">
-        <v>0.8523725867271423</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="192">
@@ -2570,7 +2570,7 @@
         <v>195</v>
       </c>
       <c r="C196" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="197">
@@ -2581,7 +2581,7 @@
         <v>196</v>
       </c>
       <c r="C197" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="198">
@@ -2592,7 +2592,7 @@
         <v>197</v>
       </c>
       <c r="C198" t="n">
-        <v>0.8471001982688904</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="199">
@@ -2603,7 +2603,7 @@
         <v>198</v>
       </c>
       <c r="C199" t="n">
-        <v>0.8488576412200928</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="200">
@@ -2636,7 +2636,7 @@
         <v>201</v>
       </c>
       <c r="C202" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="203">
@@ -2647,7 +2647,7 @@
         <v>202</v>
       </c>
       <c r="C203" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="204">
@@ -2658,7 +2658,7 @@
         <v>203</v>
       </c>
       <c r="C204" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="205">
@@ -2669,7 +2669,7 @@
         <v>204</v>
       </c>
       <c r="C205" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="206">
@@ -2680,7 +2680,7 @@
         <v>205</v>
       </c>
       <c r="C206" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="207">
@@ -2691,7 +2691,7 @@
         <v>206</v>
       </c>
       <c r="C207" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="208">
@@ -2702,7 +2702,7 @@
         <v>207</v>
       </c>
       <c r="C208" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="209">
@@ -2713,7 +2713,7 @@
         <v>208</v>
       </c>
       <c r="C209" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="210">
@@ -2724,7 +2724,7 @@
         <v>209</v>
       </c>
       <c r="C210" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="211">
@@ -2735,7 +2735,7 @@
         <v>210</v>
       </c>
       <c r="C211" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="212">
@@ -2746,7 +2746,7 @@
         <v>211</v>
       </c>
       <c r="C212" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="213">
@@ -2757,7 +2757,7 @@
         <v>212</v>
       </c>
       <c r="C213" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="214">
@@ -2768,7 +2768,7 @@
         <v>213</v>
       </c>
       <c r="C214" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="215">
@@ -2779,7 +2779,7 @@
         <v>214</v>
       </c>
       <c r="C215" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="216">
@@ -2790,7 +2790,7 @@
         <v>215</v>
       </c>
       <c r="C216" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="217">
@@ -2801,7 +2801,7 @@
         <v>216</v>
       </c>
       <c r="C217" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="218">
@@ -2812,7 +2812,7 @@
         <v>217</v>
       </c>
       <c r="C218" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="219">
@@ -2823,7 +2823,7 @@
         <v>218</v>
       </c>
       <c r="C219" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="220">
@@ -2834,7 +2834,7 @@
         <v>219</v>
       </c>
       <c r="C220" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="221">
@@ -2845,7 +2845,7 @@
         <v>220</v>
       </c>
       <c r="C221" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="222">
@@ -2856,7 +2856,7 @@
         <v>221</v>
       </c>
       <c r="C222" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="223">
@@ -2867,7 +2867,7 @@
         <v>222</v>
       </c>
       <c r="C223" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="224">
@@ -2878,7 +2878,7 @@
         <v>223</v>
       </c>
       <c r="C224" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="225">
@@ -2889,7 +2889,7 @@
         <v>224</v>
       </c>
       <c r="C225" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="226">
@@ -2900,7 +2900,7 @@
         <v>225</v>
       </c>
       <c r="C226" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="227">
@@ -2911,7 +2911,7 @@
         <v>226</v>
       </c>
       <c r="C227" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="228">
@@ -2922,7 +2922,7 @@
         <v>227</v>
       </c>
       <c r="C228" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="229">
@@ -2933,7 +2933,7 @@
         <v>228</v>
       </c>
       <c r="C229" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="230">
@@ -2944,7 +2944,7 @@
         <v>229</v>
       </c>
       <c r="C230" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="231">
@@ -2955,7 +2955,7 @@
         <v>230</v>
       </c>
       <c r="C231" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="232">
@@ -2966,7 +2966,7 @@
         <v>231</v>
       </c>
       <c r="C232" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="233">
@@ -2977,7 +2977,7 @@
         <v>232</v>
       </c>
       <c r="C233" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="234">
@@ -2988,7 +2988,7 @@
         <v>233</v>
       </c>
       <c r="C234" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="235">
@@ -2999,7 +2999,7 @@
         <v>234</v>
       </c>
       <c r="C235" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="236">
@@ -3010,7 +3010,7 @@
         <v>235</v>
       </c>
       <c r="C236" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="237">
@@ -3021,7 +3021,7 @@
         <v>236</v>
       </c>
       <c r="C237" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="238">
@@ -3032,7 +3032,7 @@
         <v>237</v>
       </c>
       <c r="C238" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="239">
@@ -3043,7 +3043,7 @@
         <v>238</v>
       </c>
       <c r="C239" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="240">
@@ -3054,7 +3054,7 @@
         <v>239</v>
       </c>
       <c r="C240" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="241">
@@ -3065,7 +3065,7 @@
         <v>240</v>
       </c>
       <c r="C241" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="242">
@@ -3076,7 +3076,7 @@
         <v>241</v>
       </c>
       <c r="C242" t="n">
-        <v>0.8541300296783447</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="243">
@@ -3087,7 +3087,7 @@
         <v>242</v>
       </c>
       <c r="C243" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="244">
@@ -3098,7 +3098,7 @@
         <v>243</v>
       </c>
       <c r="C244" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="245">
@@ -3109,7 +3109,7 @@
         <v>244</v>
       </c>
       <c r="C245" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="246">
@@ -3120,7 +3120,7 @@
         <v>245</v>
       </c>
       <c r="C246" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="247">
@@ -3131,7 +3131,7 @@
         <v>246</v>
       </c>
       <c r="C247" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="248">
@@ -3142,7 +3142,7 @@
         <v>247</v>
       </c>
       <c r="C248" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="249">
@@ -3153,7 +3153,7 @@
         <v>248</v>
       </c>
       <c r="C249" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="250">
@@ -3164,7 +3164,7 @@
         <v>249</v>
       </c>
       <c r="C250" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="251">
@@ -3175,7 +3175,7 @@
         <v>250</v>
       </c>
       <c r="C251" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="252">
@@ -3186,7 +3186,7 @@
         <v>251</v>
       </c>
       <c r="C252" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="253">
@@ -3197,7 +3197,7 @@
         <v>252</v>
       </c>
       <c r="C253" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="254">
@@ -3208,7 +3208,7 @@
         <v>253</v>
       </c>
       <c r="C254" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="255">
@@ -3219,7 +3219,7 @@
         <v>254</v>
       </c>
       <c r="C255" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="256">
@@ -3230,7 +3230,7 @@
         <v>255</v>
       </c>
       <c r="C256" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="257">
@@ -3241,7 +3241,7 @@
         <v>256</v>
       </c>
       <c r="C257" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="258">
@@ -3252,7 +3252,7 @@
         <v>257</v>
       </c>
       <c r="C258" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="259">
@@ -3263,7 +3263,7 @@
         <v>258</v>
       </c>
       <c r="C259" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="260">
@@ -3274,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="C260" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="261">
@@ -3285,7 +3285,7 @@
         <v>260</v>
       </c>
       <c r="C261" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="262">
@@ -3296,7 +3296,7 @@
         <v>261</v>
       </c>
       <c r="C262" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="263">
@@ -3307,7 +3307,7 @@
         <v>262</v>
       </c>
       <c r="C263" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="264">
@@ -3318,7 +3318,7 @@
         <v>263</v>
       </c>
       <c r="C264" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="265">
@@ -3329,7 +3329,7 @@
         <v>264</v>
       </c>
       <c r="C265" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="266">
@@ -3340,7 +3340,7 @@
         <v>265</v>
       </c>
       <c r="C266" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="267">
@@ -3351,7 +3351,7 @@
         <v>266</v>
       </c>
       <c r="C267" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="268">
@@ -3362,7 +3362,7 @@
         <v>267</v>
       </c>
       <c r="C268" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="269">
@@ -3373,7 +3373,7 @@
         <v>268</v>
       </c>
       <c r="C269" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="270">
@@ -3384,7 +3384,7 @@
         <v>269</v>
       </c>
       <c r="C270" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="271">
@@ -3395,7 +3395,7 @@
         <v>270</v>
       </c>
       <c r="C271" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="272">
@@ -3406,7 +3406,7 @@
         <v>271</v>
       </c>
       <c r="C272" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="273">
@@ -3417,7 +3417,7 @@
         <v>272</v>
       </c>
       <c r="C273" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="274">
@@ -3428,7 +3428,7 @@
         <v>273</v>
       </c>
       <c r="C274" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="275">
@@ -3439,7 +3439,7 @@
         <v>274</v>
       </c>
       <c r="C275" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="276">
@@ -3450,7 +3450,7 @@
         <v>275</v>
       </c>
       <c r="C276" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="277">
@@ -3461,7 +3461,7 @@
         <v>276</v>
       </c>
       <c r="C277" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="278">
@@ -3472,7 +3472,7 @@
         <v>277</v>
       </c>
       <c r="C278" t="n">
-        <v>0.8558875322341919</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="279">
@@ -3483,7 +3483,7 @@
         <v>278</v>
       </c>
       <c r="C279" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="280">
@@ -3494,7 +3494,7 @@
         <v>279</v>
       </c>
       <c r="C280" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="281">
@@ -3505,7 +3505,7 @@
         <v>280</v>
       </c>
       <c r="C281" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="282">
@@ -3516,7 +3516,7 @@
         <v>281</v>
       </c>
       <c r="C282" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8488576412200928</v>
       </c>
     </row>
     <row r="283">
@@ -3527,7 +3527,7 @@
         <v>282</v>
       </c>
       <c r="C283" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="284">
@@ -3538,7 +3538,7 @@
         <v>283</v>
       </c>
       <c r="C284" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="285">
@@ -3549,7 +3549,7 @@
         <v>284</v>
       </c>
       <c r="C285" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="286">
@@ -3560,7 +3560,7 @@
         <v>285</v>
       </c>
       <c r="C286" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="287">
@@ -3571,7 +3571,7 @@
         <v>286</v>
       </c>
       <c r="C287" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="288">
@@ -3582,7 +3582,7 @@
         <v>287</v>
       </c>
       <c r="C288" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="289">
@@ -3593,7 +3593,7 @@
         <v>288</v>
       </c>
       <c r="C289" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="290">
@@ -3604,7 +3604,7 @@
         <v>289</v>
       </c>
       <c r="C290" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="291">
@@ -3615,7 +3615,7 @@
         <v>290</v>
       </c>
       <c r="C291" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8453426957130432</v>
       </c>
     </row>
     <row r="292">
@@ -3626,7 +3626,7 @@
         <v>291</v>
       </c>
       <c r="C292" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8471001982688904</v>
       </c>
     </row>
     <row r="293">
@@ -3637,7 +3637,7 @@
         <v>292</v>
       </c>
       <c r="C293" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="294">
@@ -3648,7 +3648,7 @@
         <v>293</v>
       </c>
       <c r="C294" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="295">
@@ -3659,7 +3659,7 @@
         <v>294</v>
       </c>
       <c r="C295" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="296">
@@ -3670,7 +3670,7 @@
         <v>295</v>
       </c>
       <c r="C296" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8506151437759399</v>
       </c>
     </row>
     <row r="297">
@@ -3681,7 +3681,7 @@
         <v>296</v>
       </c>
       <c r="C297" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="298">
@@ -3692,7 +3692,7 @@
         <v>297</v>
       </c>
       <c r="C298" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="299">
@@ -3703,7 +3703,7 @@
         <v>298</v>
       </c>
       <c r="C299" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="300">
@@ -3714,7 +3714,7 @@
         <v>299</v>
       </c>
       <c r="C300" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="301">
@@ -3725,7 +3725,7 @@
         <v>300</v>
       </c>
       <c r="C301" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="302">
@@ -3736,7 +3736,7 @@
         <v>301</v>
       </c>
       <c r="C302" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="303">
@@ -3747,7 +3747,7 @@
         <v>302</v>
       </c>
       <c r="C303" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8523725867271423</v>
       </c>
     </row>
     <row r="304">
@@ -3758,7 +3758,7 @@
         <v>303</v>
       </c>
       <c r="C304" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="305">
@@ -3769,7 +3769,7 @@
         <v>304</v>
       </c>
       <c r="C305" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="306">
@@ -3780,7 +3780,7 @@
         <v>305</v>
       </c>
       <c r="C306" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="307">
@@ -3791,7 +3791,7 @@
         <v>306</v>
       </c>
       <c r="C307" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="308">
@@ -3802,7 +3802,7 @@
         <v>307</v>
       </c>
       <c r="C308" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="309">
@@ -3813,7 +3813,7 @@
         <v>308</v>
       </c>
       <c r="C309" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="310">
@@ -3824,7 +3824,7 @@
         <v>309</v>
       </c>
       <c r="C310" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="311">
@@ -3835,7 +3835,7 @@
         <v>310</v>
       </c>
       <c r="C311" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="312">
@@ -3846,7 +3846,7 @@
         <v>311</v>
       </c>
       <c r="C312" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="313">
@@ -3857,7 +3857,7 @@
         <v>312</v>
       </c>
       <c r="C313" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="314">
@@ -3868,7 +3868,7 @@
         <v>313</v>
       </c>
       <c r="C314" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="315">
@@ -3879,7 +3879,7 @@
         <v>314</v>
       </c>
       <c r="C315" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="316">
@@ -3890,7 +3890,7 @@
         <v>315</v>
       </c>
       <c r="C316" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="317">
@@ -3901,7 +3901,7 @@
         <v>316</v>
       </c>
       <c r="C317" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="318">
@@ -3912,7 +3912,7 @@
         <v>317</v>
       </c>
       <c r="C318" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="319">
@@ -3923,7 +3923,7 @@
         <v>318</v>
       </c>
       <c r="C319" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="320">
@@ -3934,7 +3934,7 @@
         <v>319</v>
       </c>
       <c r="C320" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="321">
@@ -3956,7 +3956,7 @@
         <v>321</v>
       </c>
       <c r="C322" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="323">
@@ -3967,7 +3967,7 @@
         <v>322</v>
       </c>
       <c r="C323" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="324">
@@ -3978,7 +3978,7 @@
         <v>323</v>
       </c>
       <c r="C324" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="325">
@@ -3989,7 +3989,7 @@
         <v>324</v>
       </c>
       <c r="C325" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="326">
@@ -4000,7 +4000,7 @@
         <v>325</v>
       </c>
       <c r="C326" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="327">
@@ -4044,7 +4044,7 @@
         <v>329</v>
       </c>
       <c r="C330" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="331">
@@ -4055,7 +4055,7 @@
         <v>330</v>
       </c>
       <c r="C331" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="332">
@@ -4066,7 +4066,7 @@
         <v>331</v>
       </c>
       <c r="C332" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="333">
@@ -4099,7 +4099,7 @@
         <v>334</v>
       </c>
       <c r="C335" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="336">
@@ -4110,7 +4110,7 @@
         <v>335</v>
       </c>
       <c r="C336" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="337">
@@ -4121,7 +4121,7 @@
         <v>336</v>
       </c>
       <c r="C337" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="338">
@@ -4132,7 +4132,7 @@
         <v>337</v>
       </c>
       <c r="C338" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="339">
@@ -4143,7 +4143,7 @@
         <v>338</v>
       </c>
       <c r="C339" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="340">
@@ -4154,7 +4154,7 @@
         <v>339</v>
       </c>
       <c r="C340" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="341">
@@ -4165,7 +4165,7 @@
         <v>340</v>
       </c>
       <c r="C341" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="342">
@@ -4176,7 +4176,7 @@
         <v>341</v>
       </c>
       <c r="C342" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="343">
@@ -4187,7 +4187,7 @@
         <v>342</v>
       </c>
       <c r="C343" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="344">
@@ -4198,7 +4198,7 @@
         <v>343</v>
       </c>
       <c r="C344" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="345">
@@ -4209,7 +4209,7 @@
         <v>344</v>
       </c>
       <c r="C345" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="346">
@@ -4220,7 +4220,7 @@
         <v>345</v>
       </c>
       <c r="C346" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="347">
@@ -4242,7 +4242,7 @@
         <v>347</v>
       </c>
       <c r="C348" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="349">
@@ -4253,7 +4253,7 @@
         <v>348</v>
       </c>
       <c r="C349" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="350">
@@ -4264,7 +4264,7 @@
         <v>349</v>
       </c>
       <c r="C350" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="351">
@@ -4275,7 +4275,7 @@
         <v>350</v>
       </c>
       <c r="C351" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="352">
@@ -4286,7 +4286,7 @@
         <v>351</v>
       </c>
       <c r="C352" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="353">
@@ -4297,7 +4297,7 @@
         <v>352</v>
       </c>
       <c r="C353" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="354">
@@ -4308,7 +4308,7 @@
         <v>353</v>
       </c>
       <c r="C354" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8541300296783447</v>
       </c>
     </row>
     <row r="355">
@@ -4319,7 +4319,7 @@
         <v>354</v>
       </c>
       <c r="C355" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="356">
@@ -4330,7 +4330,7 @@
         <v>355</v>
       </c>
       <c r="C356" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="357">
@@ -4341,7 +4341,7 @@
         <v>356</v>
       </c>
       <c r="C357" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="358">
@@ -4352,7 +4352,7 @@
         <v>357</v>
       </c>
       <c r="C358" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="359">
@@ -4363,7 +4363,7 @@
         <v>358</v>
       </c>
       <c r="C359" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="360">
@@ -4374,7 +4374,7 @@
         <v>359</v>
       </c>
       <c r="C360" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="361">
@@ -4385,7 +4385,7 @@
         <v>360</v>
       </c>
       <c r="C361" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="362">
@@ -4396,7 +4396,7 @@
         <v>361</v>
       </c>
       <c r="C362" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="363">
@@ -4407,7 +4407,7 @@
         <v>362</v>
       </c>
       <c r="C363" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="364">
@@ -4429,7 +4429,7 @@
         <v>364</v>
       </c>
       <c r="C365" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="366">
@@ -4451,7 +4451,7 @@
         <v>366</v>
       </c>
       <c r="C367" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="368">
@@ -4473,7 +4473,7 @@
         <v>368</v>
       </c>
       <c r="C369" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="370">
@@ -4484,7 +4484,7 @@
         <v>369</v>
       </c>
       <c r="C370" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="371">
@@ -4495,7 +4495,7 @@
         <v>370</v>
       </c>
       <c r="C371" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="372">
@@ -4506,7 +4506,7 @@
         <v>371</v>
       </c>
       <c r="C372" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="373">
@@ -4517,7 +4517,7 @@
         <v>372</v>
       </c>
       <c r="C373" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="374">
@@ -4528,7 +4528,7 @@
         <v>373</v>
       </c>
       <c r="C374" t="n">
-        <v>0.8576449751853943</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="375">
@@ -4539,7 +4539,7 @@
         <v>374</v>
       </c>
       <c r="C375" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="376">
@@ -4550,7 +4550,7 @@
         <v>375</v>
       </c>
       <c r="C376" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="377">
@@ -4561,7 +4561,7 @@
         <v>376</v>
       </c>
       <c r="C377" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="378">
@@ -4572,7 +4572,7 @@
         <v>377</v>
       </c>
       <c r="C378" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="379">
@@ -4583,7 +4583,7 @@
         <v>378</v>
       </c>
       <c r="C379" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="380">
@@ -4594,7 +4594,7 @@
         <v>379</v>
       </c>
       <c r="C380" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="381">
@@ -4616,7 +4616,7 @@
         <v>381</v>
       </c>
       <c r="C382" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="383">
@@ -4638,7 +4638,7 @@
         <v>383</v>
       </c>
       <c r="C384" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="385">
@@ -4660,7 +4660,7 @@
         <v>385</v>
       </c>
       <c r="C386" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="387">
@@ -4682,7 +4682,7 @@
         <v>387</v>
       </c>
       <c r="C388" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="389">
@@ -4693,7 +4693,7 @@
         <v>388</v>
       </c>
       <c r="C389" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="390">
@@ -4704,7 +4704,7 @@
         <v>389</v>
       </c>
       <c r="C390" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="391">
@@ -4715,7 +4715,7 @@
         <v>390</v>
       </c>
       <c r="C391" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="392">
@@ -4726,7 +4726,7 @@
         <v>391</v>
       </c>
       <c r="C392" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="393">
@@ -4737,7 +4737,7 @@
         <v>392</v>
       </c>
       <c r="C393" t="n">
-        <v>0.862917423248291</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="394">
@@ -4748,7 +4748,7 @@
         <v>393</v>
       </c>
       <c r="C394" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="395">
@@ -4759,7 +4759,7 @@
         <v>394</v>
       </c>
       <c r="C395" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="396">
@@ -4781,7 +4781,7 @@
         <v>396</v>
       </c>
       <c r="C397" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="398">
@@ -4803,7 +4803,7 @@
         <v>398</v>
       </c>
       <c r="C399" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="400">
@@ -4814,7 +4814,7 @@
         <v>399</v>
       </c>
       <c r="C400" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="401">
@@ -4825,7 +4825,7 @@
         <v>400</v>
       </c>
       <c r="C401" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="402">
@@ -4836,7 +4836,7 @@
         <v>401</v>
       </c>
       <c r="C402" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="403">
@@ -4847,7 +4847,7 @@
         <v>402</v>
       </c>
       <c r="C403" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="404">
@@ -4858,7 +4858,7 @@
         <v>403</v>
       </c>
       <c r="C404" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="405">
@@ -4869,7 +4869,7 @@
         <v>404</v>
       </c>
       <c r="C405" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="406">
@@ -4880,7 +4880,7 @@
         <v>405</v>
       </c>
       <c r="C406" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="407">
@@ -4891,7 +4891,7 @@
         <v>406</v>
       </c>
       <c r="C407" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="408">
@@ -4902,7 +4902,7 @@
         <v>407</v>
       </c>
       <c r="C408" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="409">
@@ -4924,7 +4924,7 @@
         <v>409</v>
       </c>
       <c r="C410" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="411">
@@ -4935,7 +4935,7 @@
         <v>410</v>
       </c>
       <c r="C411" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="412">
@@ -4946,7 +4946,7 @@
         <v>411</v>
       </c>
       <c r="C412" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="413">
@@ -4957,7 +4957,7 @@
         <v>412</v>
       </c>
       <c r="C413" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="414">
@@ -4968,7 +4968,7 @@
         <v>413</v>
       </c>
       <c r="C414" t="n">
-        <v>0.868189811706543</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="415">
@@ -4979,7 +4979,7 @@
         <v>414</v>
       </c>
       <c r="C415" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="416">
@@ -4990,7 +4990,7 @@
         <v>415</v>
       </c>
       <c r="C416" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="417">
@@ -5001,7 +5001,7 @@
         <v>416</v>
       </c>
       <c r="C417" t="n">
-        <v>0.868189811706543</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="418">
@@ -5012,7 +5012,7 @@
         <v>417</v>
       </c>
       <c r="C418" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="419">
@@ -5023,7 +5023,7 @@
         <v>418</v>
       </c>
       <c r="C419" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="420">
@@ -5034,7 +5034,7 @@
         <v>419</v>
       </c>
       <c r="C420" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="421">
@@ -5045,7 +5045,7 @@
         <v>420</v>
       </c>
       <c r="C421" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="422">
@@ -5056,7 +5056,7 @@
         <v>421</v>
       </c>
       <c r="C422" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="423">
@@ -5067,7 +5067,7 @@
         <v>422</v>
       </c>
       <c r="C423" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="424">
@@ -5078,7 +5078,7 @@
         <v>423</v>
       </c>
       <c r="C424" t="n">
-        <v>0.8594024777412415</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="425">
@@ -5089,7 +5089,7 @@
         <v>424</v>
       </c>
       <c r="C425" t="n">
-        <v>0.8611599206924438</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="426">
@@ -5100,7 +5100,7 @@
         <v>425</v>
       </c>
       <c r="C426" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="427">
@@ -5111,7 +5111,7 @@
         <v>426</v>
       </c>
       <c r="C427" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="428">
@@ -5122,7 +5122,7 @@
         <v>427</v>
       </c>
       <c r="C428" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="429">
@@ -5133,7 +5133,7 @@
         <v>428</v>
       </c>
       <c r="C429" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="430">
@@ -5144,7 +5144,7 @@
         <v>429</v>
       </c>
       <c r="C430" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="431">
@@ -5155,7 +5155,7 @@
         <v>430</v>
       </c>
       <c r="C431" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="432">
@@ -5166,7 +5166,7 @@
         <v>431</v>
       </c>
       <c r="C432" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="433">
@@ -5177,7 +5177,7 @@
         <v>432</v>
       </c>
       <c r="C433" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="434">
@@ -5188,7 +5188,7 @@
         <v>433</v>
       </c>
       <c r="C434" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="435">
@@ -5199,7 +5199,7 @@
         <v>434</v>
       </c>
       <c r="C435" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="436">
@@ -5210,7 +5210,7 @@
         <v>435</v>
       </c>
       <c r="C436" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="437">
@@ -5221,7 +5221,7 @@
         <v>436</v>
       </c>
       <c r="C437" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="438">
@@ -5232,7 +5232,7 @@
         <v>437</v>
       </c>
       <c r="C438" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="439">
@@ -5243,7 +5243,7 @@
         <v>438</v>
       </c>
       <c r="C439" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="440">
@@ -5254,7 +5254,7 @@
         <v>439</v>
       </c>
       <c r="C440" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="441">
@@ -5265,7 +5265,7 @@
         <v>440</v>
       </c>
       <c r="C441" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="442">
@@ -5276,7 +5276,7 @@
         <v>441</v>
       </c>
       <c r="C442" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="443">
@@ -5287,7 +5287,7 @@
         <v>442</v>
       </c>
       <c r="C443" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="444">
@@ -5298,7 +5298,7 @@
         <v>443</v>
       </c>
       <c r="C444" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="445">
@@ -5309,7 +5309,7 @@
         <v>444</v>
       </c>
       <c r="C445" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="446">
@@ -5320,7 +5320,7 @@
         <v>445</v>
       </c>
       <c r="C446" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="447">
@@ -5331,7 +5331,7 @@
         <v>446</v>
       </c>
       <c r="C447" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="448">
@@ -5342,7 +5342,7 @@
         <v>447</v>
       </c>
       <c r="C448" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="449">
@@ -5353,7 +5353,7 @@
         <v>448</v>
       </c>
       <c r="C449" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="450">
@@ -5364,7 +5364,7 @@
         <v>449</v>
       </c>
       <c r="C450" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="451">
@@ -5375,7 +5375,7 @@
         <v>450</v>
       </c>
       <c r="C451" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="452">
@@ -5386,7 +5386,7 @@
         <v>451</v>
       </c>
       <c r="C452" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="453">
@@ -5397,7 +5397,7 @@
         <v>452</v>
       </c>
       <c r="C453" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8558875322341919</v>
       </c>
     </row>
     <row r="454">
@@ -5408,7 +5408,7 @@
         <v>453</v>
       </c>
       <c r="C454" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="455">
@@ -5419,7 +5419,7 @@
         <v>454</v>
       </c>
       <c r="C455" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="456">
@@ -5430,7 +5430,7 @@
         <v>455</v>
       </c>
       <c r="C456" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="457">
@@ -5441,7 +5441,7 @@
         <v>456</v>
       </c>
       <c r="C457" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8576449751853943</v>
       </c>
     </row>
     <row r="458">
@@ -5452,7 +5452,7 @@
         <v>457</v>
       </c>
       <c r="C458" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="459">
@@ -5463,7 +5463,7 @@
         <v>458</v>
       </c>
       <c r="C459" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="460">
@@ -5474,7 +5474,7 @@
         <v>459</v>
       </c>
       <c r="C460" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="461">
@@ -5485,7 +5485,7 @@
         <v>460</v>
       </c>
       <c r="C461" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="462">
@@ -5496,7 +5496,7 @@
         <v>461</v>
       </c>
       <c r="C462" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="463">
@@ -5507,7 +5507,7 @@
         <v>462</v>
       </c>
       <c r="C463" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="464">
@@ -5518,7 +5518,7 @@
         <v>463</v>
       </c>
       <c r="C464" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="465">
@@ -5529,7 +5529,7 @@
         <v>464</v>
       </c>
       <c r="C465" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="466">
@@ -5540,7 +5540,7 @@
         <v>465</v>
       </c>
       <c r="C466" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="467">
@@ -5551,7 +5551,7 @@
         <v>466</v>
       </c>
       <c r="C467" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="468">
@@ -5562,7 +5562,7 @@
         <v>467</v>
       </c>
       <c r="C468" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="469">
@@ -5573,7 +5573,7 @@
         <v>468</v>
       </c>
       <c r="C469" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="470">
@@ -5584,7 +5584,7 @@
         <v>469</v>
       </c>
       <c r="C470" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="471">
@@ -5595,7 +5595,7 @@
         <v>470</v>
       </c>
       <c r="C471" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="472">
@@ -5606,7 +5606,7 @@
         <v>471</v>
       </c>
       <c r="C472" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="473">
@@ -5617,7 +5617,7 @@
         <v>472</v>
       </c>
       <c r="C473" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8594024777412415</v>
       </c>
     </row>
     <row r="474">
@@ -5628,7 +5628,7 @@
         <v>473</v>
       </c>
       <c r="C474" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="475">
@@ -5639,7 +5639,7 @@
         <v>474</v>
       </c>
       <c r="C475" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="476">
@@ -5650,7 +5650,7 @@
         <v>475</v>
       </c>
       <c r="C476" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="477">
@@ -5661,7 +5661,7 @@
         <v>476</v>
       </c>
       <c r="C477" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="478">
@@ -5672,7 +5672,7 @@
         <v>477</v>
       </c>
       <c r="C478" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="479">
@@ -5683,7 +5683,7 @@
         <v>478</v>
       </c>
       <c r="C479" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="480">
@@ -5694,7 +5694,7 @@
         <v>479</v>
       </c>
       <c r="C480" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="481">
@@ -5705,7 +5705,7 @@
         <v>480</v>
       </c>
       <c r="C481" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="482">
@@ -5716,7 +5716,7 @@
         <v>481</v>
       </c>
       <c r="C482" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="483">
@@ -5727,7 +5727,7 @@
         <v>482</v>
       </c>
       <c r="C483" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="484">
@@ -5738,7 +5738,7 @@
         <v>483</v>
       </c>
       <c r="C484" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="485">
@@ -5749,7 +5749,7 @@
         <v>484</v>
       </c>
       <c r="C485" t="n">
-        <v>0.868189811706543</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="486">
@@ -5760,7 +5760,7 @@
         <v>485</v>
       </c>
       <c r="C486" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="487">
@@ -5771,7 +5771,7 @@
         <v>486</v>
       </c>
       <c r="C487" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="488">
@@ -5782,7 +5782,7 @@
         <v>487</v>
       </c>
       <c r="C488" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="489">
@@ -5793,7 +5793,7 @@
         <v>488</v>
       </c>
       <c r="C489" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="490">
@@ -5804,7 +5804,7 @@
         <v>489</v>
       </c>
       <c r="C490" t="n">
-        <v>0.868189811706543</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="491">
@@ -5815,7 +5815,7 @@
         <v>490</v>
       </c>
       <c r="C491" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="492">
@@ -5826,7 +5826,7 @@
         <v>491</v>
       </c>
       <c r="C492" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="493">
@@ -5837,7 +5837,7 @@
         <v>492</v>
       </c>
       <c r="C493" t="n">
-        <v>0.8664323091506958</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="494">
@@ -5848,7 +5848,7 @@
         <v>493</v>
       </c>
       <c r="C494" t="n">
-        <v>0.868189811706543</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="495">
@@ -5859,7 +5859,7 @@
         <v>494</v>
       </c>
       <c r="C495" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="496">
@@ -5870,7 +5870,7 @@
         <v>495</v>
       </c>
       <c r="C496" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="497">
@@ -5881,7 +5881,7 @@
         <v>496</v>
       </c>
       <c r="C497" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="498">
@@ -5892,7 +5892,7 @@
         <v>497</v>
       </c>
       <c r="C498" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="499">
@@ -5903,7 +5903,7 @@
         <v>498</v>
       </c>
       <c r="C499" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="500">
@@ -5914,7 +5914,7 @@
         <v>499</v>
       </c>
       <c r="C500" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="501">
@@ -5925,7 +5925,7 @@
         <v>500</v>
       </c>
       <c r="C501" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="502">
@@ -5936,7 +5936,7 @@
         <v>501</v>
       </c>
       <c r="C502" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="503">
@@ -5947,7 +5947,7 @@
         <v>502</v>
       </c>
       <c r="C503" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="504">
@@ -5958,7 +5958,7 @@
         <v>503</v>
       </c>
       <c r="C504" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="505">
@@ -5969,7 +5969,7 @@
         <v>504</v>
       </c>
       <c r="C505" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="506">
@@ -5980,7 +5980,7 @@
         <v>505</v>
       </c>
       <c r="C506" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="507">
@@ -5991,7 +5991,7 @@
         <v>506</v>
       </c>
       <c r="C507" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="508">
@@ -6002,7 +6002,7 @@
         <v>507</v>
       </c>
       <c r="C508" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="509">
@@ -6013,7 +6013,7 @@
         <v>508</v>
       </c>
       <c r="C509" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="510">
@@ -6024,7 +6024,7 @@
         <v>509</v>
       </c>
       <c r="C510" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="511">
@@ -6035,7 +6035,7 @@
         <v>510</v>
       </c>
       <c r="C511" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="512">
@@ -6046,7 +6046,7 @@
         <v>511</v>
       </c>
       <c r="C512" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="513">
@@ -6057,7 +6057,7 @@
         <v>512</v>
       </c>
       <c r="C513" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="514">
@@ -6068,7 +6068,7 @@
         <v>513</v>
       </c>
       <c r="C514" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="515">
@@ -6079,7 +6079,7 @@
         <v>514</v>
       </c>
       <c r="C515" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="516">
@@ -6090,7 +6090,7 @@
         <v>515</v>
       </c>
       <c r="C516" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="517">
@@ -6101,7 +6101,7 @@
         <v>516</v>
       </c>
       <c r="C517" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="518">
@@ -6112,7 +6112,7 @@
         <v>517</v>
       </c>
       <c r="C518" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="519">
@@ -6123,7 +6123,7 @@
         <v>518</v>
       </c>
       <c r="C519" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="520">
@@ -6134,7 +6134,7 @@
         <v>519</v>
       </c>
       <c r="C520" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="521">
@@ -6145,7 +6145,7 @@
         <v>520</v>
       </c>
       <c r="C521" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="522">
@@ -6156,7 +6156,7 @@
         <v>521</v>
       </c>
       <c r="C522" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="523">
@@ -6167,7 +6167,7 @@
         <v>522</v>
       </c>
       <c r="C523" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="524">
@@ -6178,7 +6178,7 @@
         <v>523</v>
       </c>
       <c r="C524" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="525">
@@ -6189,7 +6189,7 @@
         <v>524</v>
       </c>
       <c r="C525" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="526">
@@ -6200,7 +6200,7 @@
         <v>525</v>
       </c>
       <c r="C526" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="527">
@@ -6211,7 +6211,7 @@
         <v>526</v>
       </c>
       <c r="C527" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="528">
@@ -6222,7 +6222,7 @@
         <v>527</v>
       </c>
       <c r="C528" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="529">
@@ -6233,7 +6233,7 @@
         <v>528</v>
       </c>
       <c r="C529" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="530">
@@ -6244,7 +6244,7 @@
         <v>529</v>
       </c>
       <c r="C530" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="531">
@@ -6255,7 +6255,7 @@
         <v>530</v>
       </c>
       <c r="C531" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="532">
@@ -6266,7 +6266,7 @@
         <v>531</v>
       </c>
       <c r="C532" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="533">
@@ -6277,7 +6277,7 @@
         <v>532</v>
       </c>
       <c r="C533" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="534">
@@ -6288,7 +6288,7 @@
         <v>533</v>
       </c>
       <c r="C534" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="535">
@@ -6299,7 +6299,7 @@
         <v>534</v>
       </c>
       <c r="C535" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="536">
@@ -6310,7 +6310,7 @@
         <v>535</v>
       </c>
       <c r="C536" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="537">
@@ -6321,7 +6321,7 @@
         <v>536</v>
       </c>
       <c r="C537" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="538">
@@ -6343,7 +6343,7 @@
         <v>538</v>
       </c>
       <c r="C539" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="540">
@@ -6354,7 +6354,7 @@
         <v>539</v>
       </c>
       <c r="C540" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="541">
@@ -6365,7 +6365,7 @@
         <v>540</v>
       </c>
       <c r="C541" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="542">
@@ -6376,7 +6376,7 @@
         <v>541</v>
       </c>
       <c r="C542" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="543">
@@ -6387,7 +6387,7 @@
         <v>542</v>
       </c>
       <c r="C543" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="544">
@@ -6398,7 +6398,7 @@
         <v>543</v>
       </c>
       <c r="C544" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="545">
@@ -6409,7 +6409,7 @@
         <v>544</v>
       </c>
       <c r="C545" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="546">
@@ -6420,7 +6420,7 @@
         <v>545</v>
       </c>
       <c r="C546" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="547">
@@ -6431,7 +6431,7 @@
         <v>546</v>
       </c>
       <c r="C547" t="n">
-        <v>0.8699472546577454</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="548">
@@ -6442,7 +6442,7 @@
         <v>547</v>
       </c>
       <c r="C548" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="549">
@@ -6453,7 +6453,7 @@
         <v>548</v>
       </c>
       <c r="C549" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="550">
@@ -6464,7 +6464,7 @@
         <v>549</v>
       </c>
       <c r="C550" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="551">
@@ -6475,7 +6475,7 @@
         <v>550</v>
       </c>
       <c r="C551" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="552">
@@ -6486,7 +6486,7 @@
         <v>551</v>
       </c>
       <c r="C552" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="553">
@@ -6497,7 +6497,7 @@
         <v>552</v>
       </c>
       <c r="C553" t="n">
-        <v>0.8717047572135925</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="554">
@@ -6508,7 +6508,7 @@
         <v>553</v>
       </c>
       <c r="C554" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="555">
@@ -6519,7 +6519,7 @@
         <v>554</v>
       </c>
       <c r="C555" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="556">
@@ -6530,7 +6530,7 @@
         <v>555</v>
       </c>
       <c r="C556" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="557">
@@ -6541,7 +6541,7 @@
         <v>556</v>
       </c>
       <c r="C557" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="558">
@@ -6552,7 +6552,7 @@
         <v>557</v>
       </c>
       <c r="C558" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="559">
@@ -6563,7 +6563,7 @@
         <v>558</v>
       </c>
       <c r="C559" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="560">
@@ -6574,7 +6574,7 @@
         <v>559</v>
       </c>
       <c r="C560" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="561">
@@ -6585,7 +6585,7 @@
         <v>560</v>
       </c>
       <c r="C561" t="n">
-        <v>0.8734622001647949</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="562">
@@ -6596,7 +6596,7 @@
         <v>561</v>
       </c>
       <c r="C562" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="563">
@@ -6607,7 +6607,7 @@
         <v>562</v>
       </c>
       <c r="C563" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="564">
@@ -6618,7 +6618,7 @@
         <v>563</v>
       </c>
       <c r="C564" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="565">
@@ -6629,7 +6629,7 @@
         <v>564</v>
       </c>
       <c r="C565" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="566">
@@ -6640,7 +6640,7 @@
         <v>565</v>
       </c>
       <c r="C566" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="567">
@@ -6651,7 +6651,7 @@
         <v>566</v>
       </c>
       <c r="C567" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="568">
@@ -6662,7 +6662,7 @@
         <v>567</v>
       </c>
       <c r="C568" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="569">
@@ -6673,7 +6673,7 @@
         <v>568</v>
       </c>
       <c r="C569" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="570">
@@ -6684,7 +6684,7 @@
         <v>569</v>
       </c>
       <c r="C570" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="571">
@@ -6695,7 +6695,7 @@
         <v>570</v>
       </c>
       <c r="C571" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="572">
@@ -6706,7 +6706,7 @@
         <v>571</v>
       </c>
       <c r="C572" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="573">
@@ -6717,7 +6717,7 @@
         <v>572</v>
       </c>
       <c r="C573" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="574">
@@ -6728,7 +6728,7 @@
         <v>573</v>
       </c>
       <c r="C574" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="575">
@@ -6739,7 +6739,7 @@
         <v>574</v>
       </c>
       <c r="C575" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="576">
@@ -6750,7 +6750,7 @@
         <v>575</v>
       </c>
       <c r="C576" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="577">
@@ -6761,7 +6761,7 @@
         <v>576</v>
       </c>
       <c r="C577" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="578">
@@ -6772,7 +6772,7 @@
         <v>577</v>
       </c>
       <c r="C578" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="579">
@@ -6783,7 +6783,7 @@
         <v>578</v>
       </c>
       <c r="C579" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="580">
@@ -6794,7 +6794,7 @@
         <v>579</v>
       </c>
       <c r="C580" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="581">
@@ -6805,7 +6805,7 @@
         <v>580</v>
       </c>
       <c r="C581" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="582">
@@ -6816,7 +6816,7 @@
         <v>581</v>
       </c>
       <c r="C582" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="583">
@@ -6827,7 +6827,7 @@
         <v>582</v>
       </c>
       <c r="C583" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="584">
@@ -6838,7 +6838,7 @@
         <v>583</v>
       </c>
       <c r="C584" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="585">
@@ -6849,7 +6849,7 @@
         <v>584</v>
       </c>
       <c r="C585" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="586">
@@ -6860,7 +6860,7 @@
         <v>585</v>
       </c>
       <c r="C586" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="587">
@@ -6871,7 +6871,7 @@
         <v>586</v>
       </c>
       <c r="C587" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="588">
@@ -6882,7 +6882,7 @@
         <v>587</v>
       </c>
       <c r="C588" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="589">
@@ -6893,7 +6893,7 @@
         <v>588</v>
       </c>
       <c r="C589" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="590">
@@ -6904,7 +6904,7 @@
         <v>589</v>
       </c>
       <c r="C590" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="591">
@@ -6915,7 +6915,7 @@
         <v>590</v>
       </c>
       <c r="C591" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="592">
@@ -6926,7 +6926,7 @@
         <v>591</v>
       </c>
       <c r="C592" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="593">
@@ -6937,7 +6937,7 @@
         <v>592</v>
       </c>
       <c r="C593" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="594">
@@ -6948,7 +6948,7 @@
         <v>593</v>
       </c>
       <c r="C594" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="595">
@@ -6959,7 +6959,7 @@
         <v>594</v>
       </c>
       <c r="C595" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="596">
@@ -6970,7 +6970,7 @@
         <v>595</v>
       </c>
       <c r="C596" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="597">
@@ -6981,7 +6981,7 @@
         <v>596</v>
       </c>
       <c r="C597" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="598">
@@ -6992,7 +6992,7 @@
         <v>597</v>
       </c>
       <c r="C598" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="599">
@@ -7003,7 +7003,7 @@
         <v>598</v>
       </c>
       <c r="C599" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="600">
@@ -7014,7 +7014,7 @@
         <v>599</v>
       </c>
       <c r="C600" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="601">
@@ -7025,7 +7025,7 @@
         <v>600</v>
       </c>
       <c r="C601" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="602">
@@ -7036,7 +7036,7 @@
         <v>601</v>
       </c>
       <c r="C602" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="603">
@@ -7047,7 +7047,7 @@
         <v>602</v>
       </c>
       <c r="C603" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="604">
@@ -7058,7 +7058,7 @@
         <v>603</v>
       </c>
       <c r="C604" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="605">
@@ -7069,7 +7069,7 @@
         <v>604</v>
       </c>
       <c r="C605" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="606">
@@ -7080,7 +7080,7 @@
         <v>605</v>
       </c>
       <c r="C606" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="607">
@@ -7091,7 +7091,7 @@
         <v>606</v>
       </c>
       <c r="C607" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="608">
@@ -7102,7 +7102,7 @@
         <v>607</v>
       </c>
       <c r="C608" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="609">
@@ -7113,7 +7113,7 @@
         <v>608</v>
       </c>
       <c r="C609" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="610">
@@ -7124,7 +7124,7 @@
         <v>609</v>
       </c>
       <c r="C610" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="611">
@@ -7135,7 +7135,7 @@
         <v>610</v>
       </c>
       <c r="C611" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="612">
@@ -7146,7 +7146,7 @@
         <v>611</v>
       </c>
       <c r="C612" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="613">
@@ -7157,7 +7157,7 @@
         <v>612</v>
       </c>
       <c r="C613" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="614">
@@ -7168,7 +7168,7 @@
         <v>613</v>
       </c>
       <c r="C614" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="615">
@@ -7179,7 +7179,7 @@
         <v>614</v>
       </c>
       <c r="C615" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="616">
@@ -7190,7 +7190,7 @@
         <v>615</v>
       </c>
       <c r="C616" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="617">
@@ -7201,7 +7201,7 @@
         <v>616</v>
       </c>
       <c r="C617" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="618">
@@ -7212,7 +7212,7 @@
         <v>617</v>
       </c>
       <c r="C618" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="619">
@@ -7223,7 +7223,7 @@
         <v>618</v>
       </c>
       <c r="C619" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="620">
@@ -7234,7 +7234,7 @@
         <v>619</v>
       </c>
       <c r="C620" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="621">
@@ -7245,7 +7245,7 @@
         <v>620</v>
       </c>
       <c r="C621" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="622">
@@ -7256,7 +7256,7 @@
         <v>621</v>
       </c>
       <c r="C622" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="623">
@@ -7267,7 +7267,7 @@
         <v>622</v>
       </c>
       <c r="C623" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="624">
@@ -7278,7 +7278,7 @@
         <v>623</v>
       </c>
       <c r="C624" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="625">
@@ -7289,7 +7289,7 @@
         <v>624</v>
       </c>
       <c r="C625" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="626">
@@ -7300,7 +7300,7 @@
         <v>625</v>
       </c>
       <c r="C626" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="627">
@@ -7311,7 +7311,7 @@
         <v>626</v>
       </c>
       <c r="C627" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="628">
@@ -7322,7 +7322,7 @@
         <v>627</v>
       </c>
       <c r="C628" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="629">
@@ -7333,7 +7333,7 @@
         <v>628</v>
       </c>
       <c r="C629" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="630">
@@ -7344,7 +7344,7 @@
         <v>629</v>
       </c>
       <c r="C630" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="631">
@@ -7355,7 +7355,7 @@
         <v>630</v>
       </c>
       <c r="C631" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="632">
@@ -7366,7 +7366,7 @@
         <v>631</v>
       </c>
       <c r="C632" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="633">
@@ -7377,7 +7377,7 @@
         <v>632</v>
       </c>
       <c r="C633" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="634">
@@ -7388,7 +7388,7 @@
         <v>633</v>
       </c>
       <c r="C634" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="635">
@@ -7399,7 +7399,7 @@
         <v>634</v>
       </c>
       <c r="C635" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="636">
@@ -7410,7 +7410,7 @@
         <v>635</v>
       </c>
       <c r="C636" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="637">
@@ -7421,7 +7421,7 @@
         <v>636</v>
       </c>
       <c r="C637" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="638">
@@ -7432,7 +7432,7 @@
         <v>637</v>
       </c>
       <c r="C638" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="639">
@@ -7443,7 +7443,7 @@
         <v>638</v>
       </c>
       <c r="C639" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="640">
@@ -7454,7 +7454,7 @@
         <v>639</v>
       </c>
       <c r="C640" t="n">
-        <v>0.8752197027206421</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="641">
@@ -7465,7 +7465,7 @@
         <v>640</v>
       </c>
       <c r="C641" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="642">
@@ -7476,7 +7476,7 @@
         <v>641</v>
       </c>
       <c r="C642" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="643">
@@ -7487,7 +7487,7 @@
         <v>642</v>
       </c>
       <c r="C643" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="644">
@@ -7498,7 +7498,7 @@
         <v>643</v>
       </c>
       <c r="C644" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="645">
@@ -7509,7 +7509,7 @@
         <v>644</v>
       </c>
       <c r="C645" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="646">
@@ -7520,7 +7520,7 @@
         <v>645</v>
       </c>
       <c r="C646" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="647">
@@ -7531,7 +7531,7 @@
         <v>646</v>
       </c>
       <c r="C647" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="648">
@@ -7542,7 +7542,7 @@
         <v>647</v>
       </c>
       <c r="C648" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="649">
@@ -7553,7 +7553,7 @@
         <v>648</v>
       </c>
       <c r="C649" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="650">
@@ -7564,7 +7564,7 @@
         <v>649</v>
       </c>
       <c r="C650" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="651">
@@ -7575,7 +7575,7 @@
         <v>650</v>
       </c>
       <c r="C651" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="652">
@@ -7586,7 +7586,7 @@
         <v>651</v>
       </c>
       <c r="C652" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="653">
@@ -7597,7 +7597,7 @@
         <v>652</v>
       </c>
       <c r="C653" t="n">
-        <v>0.880492091178894</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="654">
@@ -7608,7 +7608,7 @@
         <v>653</v>
       </c>
       <c r="C654" t="n">
-        <v>0.880492091178894</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="655">
@@ -7619,7 +7619,7 @@
         <v>654</v>
       </c>
       <c r="C655" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="656">
@@ -7630,7 +7630,7 @@
         <v>655</v>
       </c>
       <c r="C656" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="657">
@@ -7641,7 +7641,7 @@
         <v>656</v>
       </c>
       <c r="C657" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="658">
@@ -7652,7 +7652,7 @@
         <v>657</v>
       </c>
       <c r="C658" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="659">
@@ -7663,7 +7663,7 @@
         <v>658</v>
       </c>
       <c r="C659" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="660">
@@ -7674,7 +7674,7 @@
         <v>659</v>
       </c>
       <c r="C660" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="661">
@@ -7685,7 +7685,7 @@
         <v>660</v>
       </c>
       <c r="C661" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="662">
@@ -7696,7 +7696,7 @@
         <v>661</v>
       </c>
       <c r="C662" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="663">
@@ -7707,7 +7707,7 @@
         <v>662</v>
       </c>
       <c r="C663" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="664">
@@ -7718,7 +7718,7 @@
         <v>663</v>
       </c>
       <c r="C664" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="665">
@@ -7729,7 +7729,7 @@
         <v>664</v>
       </c>
       <c r="C665" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="666">
@@ -7740,7 +7740,7 @@
         <v>665</v>
       </c>
       <c r="C666" t="n">
-        <v>0.880492091178894</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="667">
@@ -7751,7 +7751,7 @@
         <v>666</v>
       </c>
       <c r="C667" t="n">
-        <v>0.880492091178894</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="668">
@@ -7762,7 +7762,7 @@
         <v>667</v>
       </c>
       <c r="C668" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="669">
@@ -7773,7 +7773,7 @@
         <v>668</v>
       </c>
       <c r="C669" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="670">
@@ -7784,7 +7784,7 @@
         <v>669</v>
       </c>
       <c r="C670" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="671">
@@ -7795,7 +7795,7 @@
         <v>670</v>
       </c>
       <c r="C671" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8611599206924438</v>
       </c>
     </row>
     <row r="672">
@@ -7806,7 +7806,7 @@
         <v>671</v>
       </c>
       <c r="C672" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="673">
@@ -7817,7 +7817,7 @@
         <v>672</v>
       </c>
       <c r="C673" t="n">
-        <v>0.8769771456718445</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="674">
@@ -7828,7 +7828,7 @@
         <v>673</v>
       </c>
       <c r="C674" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="675">
@@ -7839,7 +7839,7 @@
         <v>674</v>
       </c>
       <c r="C675" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="676">
@@ -7850,7 +7850,7 @@
         <v>675</v>
       </c>
       <c r="C676" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="677">
@@ -7861,7 +7861,7 @@
         <v>676</v>
       </c>
       <c r="C677" t="n">
-        <v>0.880492091178894</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="678">
@@ -7872,7 +7872,7 @@
         <v>677</v>
       </c>
       <c r="C678" t="n">
-        <v>0.880492091178894</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="679">
@@ -7883,7 +7883,7 @@
         <v>678</v>
       </c>
       <c r="C679" t="n">
-        <v>0.880492091178894</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="680">
@@ -7894,7 +7894,7 @@
         <v>679</v>
       </c>
       <c r="C680" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="681">
@@ -7905,7 +7905,7 @@
         <v>680</v>
       </c>
       <c r="C681" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="682">
@@ -7916,7 +7916,7 @@
         <v>681</v>
       </c>
       <c r="C682" t="n">
-        <v>0.880492091178894</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="683">
@@ -7927,7 +7927,7 @@
         <v>682</v>
       </c>
       <c r="C683" t="n">
-        <v>0.880492091178894</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="684">
@@ -7938,7 +7938,7 @@
         <v>683</v>
       </c>
       <c r="C684" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="685">
@@ -7949,7 +7949,7 @@
         <v>684</v>
       </c>
       <c r="C685" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="686">
@@ -7960,7 +7960,7 @@
         <v>685</v>
       </c>
       <c r="C686" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="687">
@@ -7971,7 +7971,7 @@
         <v>686</v>
       </c>
       <c r="C687" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.862917423248291</v>
       </c>
     </row>
     <row r="688">
@@ -7982,7 +7982,7 @@
         <v>687</v>
       </c>
       <c r="C688" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="689">
@@ -7993,7 +7993,7 @@
         <v>688</v>
       </c>
       <c r="C689" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8664323091506958</v>
       </c>
     </row>
     <row r="690">
@@ -8004,7 +8004,7 @@
         <v>689</v>
       </c>
       <c r="C690" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8646748661994934</v>
       </c>
     </row>
     <row r="691">
@@ -8015,7 +8015,7 @@
         <v>690</v>
       </c>
       <c r="C691" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="692">
@@ -8026,7 +8026,7 @@
         <v>691</v>
       </c>
       <c r="C692" t="n">
-        <v>0.880492091178894</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="693">
@@ -8037,7 +8037,7 @@
         <v>692</v>
       </c>
       <c r="C693" t="n">
-        <v>0.880492091178894</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="694">
@@ -8048,7 +8048,7 @@
         <v>693</v>
       </c>
       <c r="C694" t="n">
-        <v>0.880492091178894</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="695">
@@ -8059,7 +8059,7 @@
         <v>694</v>
       </c>
       <c r="C695" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="696">
@@ -8070,7 +8070,7 @@
         <v>695</v>
       </c>
       <c r="C696" t="n">
-        <v>0.880492091178894</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="697">
@@ -8081,7 +8081,7 @@
         <v>696</v>
       </c>
       <c r="C697" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="698">
@@ -8092,7 +8092,7 @@
         <v>697</v>
       </c>
       <c r="C698" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.868189811706543</v>
       </c>
     </row>
     <row r="699">
@@ -8103,7 +8103,7 @@
         <v>698</v>
       </c>
       <c r="C699" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="700">
@@ -8114,7 +8114,7 @@
         <v>699</v>
       </c>
       <c r="C700" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="701">
@@ -8125,7 +8125,7 @@
         <v>700</v>
       </c>
       <c r="C701" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="702">
@@ -8136,7 +8136,7 @@
         <v>701</v>
       </c>
       <c r="C702" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="703">
@@ -8147,7 +8147,7 @@
         <v>702</v>
       </c>
       <c r="C703" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="704">
@@ -8158,7 +8158,7 @@
         <v>703</v>
       </c>
       <c r="C704" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="705">
@@ -8169,7 +8169,7 @@
         <v>704</v>
       </c>
       <c r="C705" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="706">
@@ -8180,7 +8180,7 @@
         <v>705</v>
       </c>
       <c r="C706" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="707">
@@ -8191,7 +8191,7 @@
         <v>706</v>
       </c>
       <c r="C707" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="708">
@@ -8202,7 +8202,7 @@
         <v>707</v>
       </c>
       <c r="C708" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="709">
@@ -8213,7 +8213,7 @@
         <v>708</v>
       </c>
       <c r="C709" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="710">
@@ -8224,7 +8224,7 @@
         <v>709</v>
       </c>
       <c r="C710" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="711">
@@ -8235,7 +8235,7 @@
         <v>710</v>
       </c>
       <c r="C711" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="712">
@@ -8246,7 +8246,7 @@
         <v>711</v>
       </c>
       <c r="C712" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="713">
@@ -8257,7 +8257,7 @@
         <v>712</v>
       </c>
       <c r="C713" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="714">
@@ -8268,7 +8268,7 @@
         <v>713</v>
       </c>
       <c r="C714" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="715">
@@ -8279,7 +8279,7 @@
         <v>714</v>
       </c>
       <c r="C715" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="716">
@@ -8290,7 +8290,7 @@
         <v>715</v>
       </c>
       <c r="C716" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="717">
@@ -8301,7 +8301,7 @@
         <v>716</v>
       </c>
       <c r="C717" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="718">
@@ -8312,7 +8312,7 @@
         <v>717</v>
       </c>
       <c r="C718" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="719">
@@ -8323,7 +8323,7 @@
         <v>718</v>
       </c>
       <c r="C719" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="720">
@@ -8334,7 +8334,7 @@
         <v>719</v>
       </c>
       <c r="C720" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8699472546577454</v>
       </c>
     </row>
     <row r="721">
@@ -8345,7 +8345,7 @@
         <v>720</v>
       </c>
       <c r="C721" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="722">
@@ -8356,7 +8356,7 @@
         <v>721</v>
       </c>
       <c r="C722" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="723">
@@ -8367,7 +8367,7 @@
         <v>722</v>
       </c>
       <c r="C723" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="724">
@@ -8378,7 +8378,7 @@
         <v>723</v>
       </c>
       <c r="C724" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="725">
@@ -8389,7 +8389,7 @@
         <v>724</v>
       </c>
       <c r="C725" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="726">
@@ -8400,7 +8400,7 @@
         <v>725</v>
       </c>
       <c r="C726" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8717047572135925</v>
       </c>
     </row>
     <row r="727">
@@ -8411,7 +8411,7 @@
         <v>726</v>
       </c>
       <c r="C727" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="728">
@@ -8422,7 +8422,7 @@
         <v>727</v>
       </c>
       <c r="C728" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="729">
@@ -8433,7 +8433,7 @@
         <v>728</v>
       </c>
       <c r="C729" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="730">
@@ -8444,7 +8444,7 @@
         <v>729</v>
       </c>
       <c r="C730" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="731">
@@ -8455,7 +8455,7 @@
         <v>730</v>
       </c>
       <c r="C731" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="732">
@@ -8466,7 +8466,7 @@
         <v>731</v>
       </c>
       <c r="C732" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="733">
@@ -8477,7 +8477,7 @@
         <v>732</v>
       </c>
       <c r="C733" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="734">
@@ -8488,7 +8488,7 @@
         <v>733</v>
       </c>
       <c r="C734" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="735">
@@ -8499,7 +8499,7 @@
         <v>734</v>
       </c>
       <c r="C735" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="736">
@@ -8510,7 +8510,7 @@
         <v>735</v>
       </c>
       <c r="C736" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="737">
@@ -8521,7 +8521,7 @@
         <v>736</v>
       </c>
       <c r="C737" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="738">
@@ -8532,7 +8532,7 @@
         <v>737</v>
       </c>
       <c r="C738" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="739">
@@ -8543,7 +8543,7 @@
         <v>738</v>
       </c>
       <c r="C739" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="740">
@@ -8554,7 +8554,7 @@
         <v>739</v>
       </c>
       <c r="C740" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="741">
@@ -8565,7 +8565,7 @@
         <v>740</v>
       </c>
       <c r="C741" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="742">
@@ -8576,7 +8576,7 @@
         <v>741</v>
       </c>
       <c r="C742" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="743">
@@ -8587,7 +8587,7 @@
         <v>742</v>
       </c>
       <c r="C743" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="744">
@@ -8598,7 +8598,7 @@
         <v>743</v>
       </c>
       <c r="C744" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="745">
@@ -8609,7 +8609,7 @@
         <v>744</v>
       </c>
       <c r="C745" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="746">
@@ -8620,7 +8620,7 @@
         <v>745</v>
       </c>
       <c r="C746" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="747">
@@ -8631,7 +8631,7 @@
         <v>746</v>
       </c>
       <c r="C747" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="748">
@@ -8642,7 +8642,7 @@
         <v>747</v>
       </c>
       <c r="C748" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="749">
@@ -8653,7 +8653,7 @@
         <v>748</v>
       </c>
       <c r="C749" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="750">
@@ -8664,7 +8664,7 @@
         <v>749</v>
       </c>
       <c r="C750" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="751">
@@ -8675,7 +8675,7 @@
         <v>750</v>
       </c>
       <c r="C751" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="752">
@@ -8686,7 +8686,7 @@
         <v>751</v>
       </c>
       <c r="C752" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="753">
@@ -8697,7 +8697,7 @@
         <v>752</v>
       </c>
       <c r="C753" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="754">
@@ -8708,7 +8708,7 @@
         <v>753</v>
       </c>
       <c r="C754" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="755">
@@ -8719,7 +8719,7 @@
         <v>754</v>
       </c>
       <c r="C755" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="756">
@@ -8730,7 +8730,7 @@
         <v>755</v>
       </c>
       <c r="C756" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="757">
@@ -8741,7 +8741,7 @@
         <v>756</v>
       </c>
       <c r="C757" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="758">
@@ -8752,7 +8752,7 @@
         <v>757</v>
       </c>
       <c r="C758" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="759">
@@ -8763,7 +8763,7 @@
         <v>758</v>
       </c>
       <c r="C759" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="760">
@@ -8774,7 +8774,7 @@
         <v>759</v>
       </c>
       <c r="C760" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="761">
@@ -8785,7 +8785,7 @@
         <v>760</v>
       </c>
       <c r="C761" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="762">
@@ -8796,7 +8796,7 @@
         <v>761</v>
       </c>
       <c r="C762" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="763">
@@ -8807,7 +8807,7 @@
         <v>762</v>
       </c>
       <c r="C763" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="764">
@@ -8818,7 +8818,7 @@
         <v>763</v>
       </c>
       <c r="C764" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="765">
@@ -8829,7 +8829,7 @@
         <v>764</v>
       </c>
       <c r="C765" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="766">
@@ -8840,7 +8840,7 @@
         <v>765</v>
       </c>
       <c r="C766" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="767">
@@ -8851,7 +8851,7 @@
         <v>766</v>
       </c>
       <c r="C767" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="768">
@@ -8862,7 +8862,7 @@
         <v>767</v>
       </c>
       <c r="C768" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="769">
@@ -8873,7 +8873,7 @@
         <v>768</v>
       </c>
       <c r="C769" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="770">
@@ -8884,7 +8884,7 @@
         <v>769</v>
       </c>
       <c r="C770" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="771">
@@ -8895,7 +8895,7 @@
         <v>770</v>
       </c>
       <c r="C771" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="772">
@@ -8906,7 +8906,7 @@
         <v>771</v>
       </c>
       <c r="C772" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="773">
@@ -8917,7 +8917,7 @@
         <v>772</v>
       </c>
       <c r="C773" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="774">
@@ -8928,7 +8928,7 @@
         <v>773</v>
       </c>
       <c r="C774" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="775">
@@ -8939,7 +8939,7 @@
         <v>774</v>
       </c>
       <c r="C775" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="776">
@@ -8950,7 +8950,7 @@
         <v>775</v>
       </c>
       <c r="C776" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="777">
@@ -8961,7 +8961,7 @@
         <v>776</v>
       </c>
       <c r="C777" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="778">
@@ -8972,7 +8972,7 @@
         <v>777</v>
       </c>
       <c r="C778" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="779">
@@ -8983,7 +8983,7 @@
         <v>778</v>
       </c>
       <c r="C779" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="780">
@@ -8994,7 +8994,7 @@
         <v>779</v>
       </c>
       <c r="C780" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="781">
@@ -9005,7 +9005,7 @@
         <v>780</v>
       </c>
       <c r="C781" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="782">
@@ -9016,7 +9016,7 @@
         <v>781</v>
       </c>
       <c r="C782" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="783">
@@ -9027,7 +9027,7 @@
         <v>782</v>
       </c>
       <c r="C783" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="784">
@@ -9038,7 +9038,7 @@
         <v>783</v>
       </c>
       <c r="C784" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="785">
@@ -9049,7 +9049,7 @@
         <v>784</v>
       </c>
       <c r="C785" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="786">
@@ -9060,7 +9060,7 @@
         <v>785</v>
       </c>
       <c r="C786" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="787">
@@ -9071,7 +9071,7 @@
         <v>786</v>
       </c>
       <c r="C787" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="788">
@@ -9082,7 +9082,7 @@
         <v>787</v>
       </c>
       <c r="C788" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="789">
@@ -9093,7 +9093,7 @@
         <v>788</v>
       </c>
       <c r="C789" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="790">
@@ -9104,7 +9104,7 @@
         <v>789</v>
       </c>
       <c r="C790" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="791">
@@ -9115,7 +9115,7 @@
         <v>790</v>
       </c>
       <c r="C791" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="792">
@@ -9126,7 +9126,7 @@
         <v>791</v>
       </c>
       <c r="C792" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="793">
@@ -9137,7 +9137,7 @@
         <v>792</v>
       </c>
       <c r="C793" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="794">
@@ -9148,7 +9148,7 @@
         <v>793</v>
       </c>
       <c r="C794" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="795">
@@ -9159,7 +9159,7 @@
         <v>794</v>
       </c>
       <c r="C795" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="796">
@@ -9170,7 +9170,7 @@
         <v>795</v>
       </c>
       <c r="C796" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="797">
@@ -9181,7 +9181,7 @@
         <v>796</v>
       </c>
       <c r="C797" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="798">
@@ -9192,7 +9192,7 @@
         <v>797</v>
       </c>
       <c r="C798" t="n">
-        <v>0.8787346482276917</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="799">
@@ -9203,7 +9203,7 @@
         <v>798</v>
       </c>
       <c r="C799" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="800">
@@ -9214,7 +9214,7 @@
         <v>799</v>
       </c>
       <c r="C800" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="801">
@@ -9225,7 +9225,7 @@
         <v>800</v>
       </c>
       <c r="C801" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="802">
@@ -9236,7 +9236,7 @@
         <v>801</v>
       </c>
       <c r="C802" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="803">
@@ -9247,7 +9247,7 @@
         <v>802</v>
       </c>
       <c r="C803" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="804">
@@ -9258,7 +9258,7 @@
         <v>803</v>
       </c>
       <c r="C804" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="805">
@@ -9269,7 +9269,7 @@
         <v>804</v>
       </c>
       <c r="C805" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="806">
@@ -9280,7 +9280,7 @@
         <v>805</v>
       </c>
       <c r="C806" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="807">
@@ -9291,7 +9291,7 @@
         <v>806</v>
       </c>
       <c r="C807" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="808">
@@ -9302,7 +9302,7 @@
         <v>807</v>
       </c>
       <c r="C808" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="809">
@@ -9313,7 +9313,7 @@
         <v>808</v>
       </c>
       <c r="C809" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="810">
@@ -9324,7 +9324,7 @@
         <v>809</v>
       </c>
       <c r="C810" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="811">
@@ -9335,7 +9335,7 @@
         <v>810</v>
       </c>
       <c r="C811" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="812">
@@ -9346,7 +9346,7 @@
         <v>811</v>
       </c>
       <c r="C812" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="813">
@@ -9357,7 +9357,7 @@
         <v>812</v>
       </c>
       <c r="C813" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="814">
@@ -9368,7 +9368,7 @@
         <v>813</v>
       </c>
       <c r="C814" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="815">
@@ -9379,7 +9379,7 @@
         <v>814</v>
       </c>
       <c r="C815" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="816">
@@ -9390,7 +9390,7 @@
         <v>815</v>
       </c>
       <c r="C816" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="817">
@@ -9401,7 +9401,7 @@
         <v>816</v>
       </c>
       <c r="C817" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="818">
@@ -9412,7 +9412,7 @@
         <v>817</v>
       </c>
       <c r="C818" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="819">
@@ -9423,7 +9423,7 @@
         <v>818</v>
       </c>
       <c r="C819" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="820">
@@ -9434,7 +9434,7 @@
         <v>819</v>
       </c>
       <c r="C820" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="821">
@@ -9445,7 +9445,7 @@
         <v>820</v>
       </c>
       <c r="C821" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="822">
@@ -9456,7 +9456,7 @@
         <v>821</v>
       </c>
       <c r="C822" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="823">
@@ -9467,7 +9467,7 @@
         <v>822</v>
       </c>
       <c r="C823" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="824">
@@ -9478,7 +9478,7 @@
         <v>823</v>
       </c>
       <c r="C824" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="825">
@@ -9489,7 +9489,7 @@
         <v>824</v>
       </c>
       <c r="C825" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="826">
@@ -9500,7 +9500,7 @@
         <v>825</v>
       </c>
       <c r="C826" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="827">
@@ -9511,7 +9511,7 @@
         <v>826</v>
       </c>
       <c r="C827" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="828">
@@ -9522,7 +9522,7 @@
         <v>827</v>
       </c>
       <c r="C828" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="829">
@@ -9533,7 +9533,7 @@
         <v>828</v>
       </c>
       <c r="C829" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="830">
@@ -9544,7 +9544,7 @@
         <v>829</v>
       </c>
       <c r="C830" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="831">
@@ -9555,7 +9555,7 @@
         <v>830</v>
       </c>
       <c r="C831" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="832">
@@ -9566,7 +9566,7 @@
         <v>831</v>
       </c>
       <c r="C832" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="833">
@@ -9577,7 +9577,7 @@
         <v>832</v>
       </c>
       <c r="C833" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="834">
@@ -9588,7 +9588,7 @@
         <v>833</v>
       </c>
       <c r="C834" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="835">
@@ -9599,7 +9599,7 @@
         <v>834</v>
       </c>
       <c r="C835" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="836">
@@ -9610,7 +9610,7 @@
         <v>835</v>
       </c>
       <c r="C836" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="837">
@@ -9621,7 +9621,7 @@
         <v>836</v>
       </c>
       <c r="C837" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="838">
@@ -9632,7 +9632,7 @@
         <v>837</v>
       </c>
       <c r="C838" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="839">
@@ -9643,7 +9643,7 @@
         <v>838</v>
       </c>
       <c r="C839" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="840">
@@ -9654,7 +9654,7 @@
         <v>839</v>
       </c>
       <c r="C840" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="841">
@@ -9665,7 +9665,7 @@
         <v>840</v>
       </c>
       <c r="C841" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="842">
@@ -9676,7 +9676,7 @@
         <v>841</v>
       </c>
       <c r="C842" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="843">
@@ -9687,7 +9687,7 @@
         <v>842</v>
       </c>
       <c r="C843" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="844">
@@ -9698,7 +9698,7 @@
         <v>843</v>
       </c>
       <c r="C844" t="n">
-        <v>0.8875219821929932</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="845">
@@ -9709,7 +9709,7 @@
         <v>844</v>
       </c>
       <c r="C845" t="n">
-        <v>0.8875219821929932</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="846">
@@ -9720,7 +9720,7 @@
         <v>845</v>
       </c>
       <c r="C846" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="847">
@@ -9731,7 +9731,7 @@
         <v>846</v>
       </c>
       <c r="C847" t="n">
-        <v>0.885764479637146</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="848">
@@ -9742,7 +9742,7 @@
         <v>847</v>
       </c>
       <c r="C848" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="849">
@@ -9753,7 +9753,7 @@
         <v>848</v>
       </c>
       <c r="C849" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="850">
@@ -9764,7 +9764,7 @@
         <v>849</v>
       </c>
       <c r="C850" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="851">
@@ -9775,7 +9775,7 @@
         <v>850</v>
       </c>
       <c r="C851" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="852">
@@ -9786,7 +9786,7 @@
         <v>851</v>
       </c>
       <c r="C852" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="853">
@@ -9797,7 +9797,7 @@
         <v>852</v>
       </c>
       <c r="C853" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="854">
@@ -9808,7 +9808,7 @@
         <v>853</v>
       </c>
       <c r="C854" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="855">
@@ -9830,7 +9830,7 @@
         <v>855</v>
       </c>
       <c r="C856" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="857">
@@ -9841,7 +9841,7 @@
         <v>856</v>
       </c>
       <c r="C857" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="858">
@@ -9852,7 +9852,7 @@
         <v>857</v>
       </c>
       <c r="C858" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="859">
@@ -9863,7 +9863,7 @@
         <v>858</v>
       </c>
       <c r="C859" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="860">
@@ -9874,7 +9874,7 @@
         <v>859</v>
       </c>
       <c r="C860" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="861">
@@ -9885,7 +9885,7 @@
         <v>860</v>
       </c>
       <c r="C861" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="862">
@@ -9896,7 +9896,7 @@
         <v>861</v>
       </c>
       <c r="C862" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="863">
@@ -9907,7 +9907,7 @@
         <v>862</v>
       </c>
       <c r="C863" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="864">
@@ -9918,7 +9918,7 @@
         <v>863</v>
       </c>
       <c r="C864" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="865">
@@ -9929,7 +9929,7 @@
         <v>864</v>
       </c>
       <c r="C865" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="866">
@@ -9940,7 +9940,7 @@
         <v>865</v>
       </c>
       <c r="C866" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="867">
@@ -9951,7 +9951,7 @@
         <v>866</v>
       </c>
       <c r="C867" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="868">
@@ -9984,7 +9984,7 @@
         <v>869</v>
       </c>
       <c r="C870" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="871">
@@ -9995,7 +9995,7 @@
         <v>870</v>
       </c>
       <c r="C871" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="872">
@@ -10006,7 +10006,7 @@
         <v>871</v>
       </c>
       <c r="C872" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="873">
@@ -10017,7 +10017,7 @@
         <v>872</v>
       </c>
       <c r="C873" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="874">
@@ -10028,7 +10028,7 @@
         <v>873</v>
       </c>
       <c r="C874" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="875">
@@ -10039,7 +10039,7 @@
         <v>874</v>
       </c>
       <c r="C875" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="876">
@@ -10050,7 +10050,7 @@
         <v>875</v>
       </c>
       <c r="C876" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="877">
@@ -10061,7 +10061,7 @@
         <v>876</v>
       </c>
       <c r="C877" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="878">
@@ -10072,7 +10072,7 @@
         <v>877</v>
       </c>
       <c r="C878" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="879">
@@ -10083,7 +10083,7 @@
         <v>878</v>
       </c>
       <c r="C879" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="880">
@@ -10094,7 +10094,7 @@
         <v>879</v>
       </c>
       <c r="C880" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="881">
@@ -10105,7 +10105,7 @@
         <v>880</v>
       </c>
       <c r="C881" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="882">
@@ -10116,7 +10116,7 @@
         <v>881</v>
       </c>
       <c r="C882" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="883">
@@ -10127,7 +10127,7 @@
         <v>882</v>
       </c>
       <c r="C883" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="884">
@@ -10138,7 +10138,7 @@
         <v>883</v>
       </c>
       <c r="C884" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="885">
@@ -10149,7 +10149,7 @@
         <v>884</v>
       </c>
       <c r="C885" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="886">
@@ -10160,7 +10160,7 @@
         <v>885</v>
       </c>
       <c r="C886" t="n">
-        <v>0.885764479637146</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="887">
@@ -10171,7 +10171,7 @@
         <v>886</v>
       </c>
       <c r="C887" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="888">
@@ -10182,7 +10182,7 @@
         <v>887</v>
       </c>
       <c r="C888" t="n">
-        <v>0.885764479637146</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="889">
@@ -10193,7 +10193,7 @@
         <v>888</v>
       </c>
       <c r="C889" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="890">
@@ -10204,7 +10204,7 @@
         <v>889</v>
       </c>
       <c r="C890" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="891">
@@ -10215,7 +10215,7 @@
         <v>890</v>
       </c>
       <c r="C891" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="892">
@@ -10226,7 +10226,7 @@
         <v>891</v>
       </c>
       <c r="C892" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="893">
@@ -10237,7 +10237,7 @@
         <v>892</v>
       </c>
       <c r="C893" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="894">
@@ -10248,7 +10248,7 @@
         <v>893</v>
       </c>
       <c r="C894" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="895">
@@ -10259,7 +10259,7 @@
         <v>894</v>
       </c>
       <c r="C895" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="896">
@@ -10270,7 +10270,7 @@
         <v>895</v>
       </c>
       <c r="C896" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="897">
@@ -10281,7 +10281,7 @@
         <v>896</v>
       </c>
       <c r="C897" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="898">
@@ -10292,7 +10292,7 @@
         <v>897</v>
       </c>
       <c r="C898" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="899">
@@ -10303,7 +10303,7 @@
         <v>898</v>
       </c>
       <c r="C899" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="900">
@@ -10314,7 +10314,7 @@
         <v>899</v>
       </c>
       <c r="C900" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="901">
@@ -10325,7 +10325,7 @@
         <v>900</v>
       </c>
       <c r="C901" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="902">
@@ -10336,7 +10336,7 @@
         <v>901</v>
       </c>
       <c r="C902" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="903">
@@ -10347,7 +10347,7 @@
         <v>902</v>
       </c>
       <c r="C903" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="904">
@@ -10358,7 +10358,7 @@
         <v>903</v>
       </c>
       <c r="C904" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="905">
@@ -10369,7 +10369,7 @@
         <v>904</v>
       </c>
       <c r="C905" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="906">
@@ -10380,7 +10380,7 @@
         <v>905</v>
       </c>
       <c r="C906" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="907">
@@ -10391,7 +10391,7 @@
         <v>906</v>
       </c>
       <c r="C907" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="908">
@@ -10402,7 +10402,7 @@
         <v>907</v>
       </c>
       <c r="C908" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="909">
@@ -10413,7 +10413,7 @@
         <v>908</v>
       </c>
       <c r="C909" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="910">
@@ -10424,7 +10424,7 @@
         <v>909</v>
       </c>
       <c r="C910" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="911">
@@ -10435,7 +10435,7 @@
         <v>910</v>
       </c>
       <c r="C911" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="912">
@@ -10446,7 +10446,7 @@
         <v>911</v>
       </c>
       <c r="C912" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="913">
@@ -10457,7 +10457,7 @@
         <v>912</v>
       </c>
       <c r="C913" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="914">
@@ -10468,7 +10468,7 @@
         <v>913</v>
       </c>
       <c r="C914" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="915">
@@ -10479,7 +10479,7 @@
         <v>914</v>
       </c>
       <c r="C915" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="916">
@@ -10490,7 +10490,7 @@
         <v>915</v>
       </c>
       <c r="C916" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="917">
@@ -10501,7 +10501,7 @@
         <v>916</v>
       </c>
       <c r="C917" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="918">
@@ -10512,7 +10512,7 @@
         <v>917</v>
       </c>
       <c r="C918" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="919">
@@ -10523,7 +10523,7 @@
         <v>918</v>
       </c>
       <c r="C919" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="920">
@@ -10534,7 +10534,7 @@
         <v>919</v>
       </c>
       <c r="C920" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="921">
@@ -10545,7 +10545,7 @@
         <v>920</v>
       </c>
       <c r="C921" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="922">
@@ -10556,7 +10556,7 @@
         <v>921</v>
       </c>
       <c r="C922" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="923">
@@ -10567,7 +10567,7 @@
         <v>922</v>
       </c>
       <c r="C923" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="924">
@@ -10578,7 +10578,7 @@
         <v>923</v>
       </c>
       <c r="C924" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="925">
@@ -10589,7 +10589,7 @@
         <v>924</v>
       </c>
       <c r="C925" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="926">
@@ -10600,7 +10600,7 @@
         <v>925</v>
       </c>
       <c r="C926" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="927">
@@ -10611,7 +10611,7 @@
         <v>926</v>
       </c>
       <c r="C927" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="928">
@@ -10622,7 +10622,7 @@
         <v>927</v>
       </c>
       <c r="C928" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="929">
@@ -10633,7 +10633,7 @@
         <v>928</v>
       </c>
       <c r="C929" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="930">
@@ -10644,7 +10644,7 @@
         <v>929</v>
       </c>
       <c r="C930" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="931">
@@ -10655,7 +10655,7 @@
         <v>930</v>
       </c>
       <c r="C931" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="932">
@@ -10666,7 +10666,7 @@
         <v>931</v>
       </c>
       <c r="C932" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="933">
@@ -10677,7 +10677,7 @@
         <v>932</v>
       </c>
       <c r="C933" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="934">
@@ -10688,7 +10688,7 @@
         <v>933</v>
       </c>
       <c r="C934" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="935">
@@ -10699,7 +10699,7 @@
         <v>934</v>
       </c>
       <c r="C935" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="936">
@@ -10710,7 +10710,7 @@
         <v>935</v>
       </c>
       <c r="C936" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="937">
@@ -10721,7 +10721,7 @@
         <v>936</v>
       </c>
       <c r="C937" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="938">
@@ -10732,7 +10732,7 @@
         <v>937</v>
       </c>
       <c r="C938" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="939">
@@ -10743,7 +10743,7 @@
         <v>938</v>
       </c>
       <c r="C939" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="940">
@@ -10754,7 +10754,7 @@
         <v>939</v>
       </c>
       <c r="C940" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="941">
@@ -10765,7 +10765,7 @@
         <v>940</v>
       </c>
       <c r="C941" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="942">
@@ -10776,7 +10776,7 @@
         <v>941</v>
       </c>
       <c r="C942" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="943">
@@ -10787,7 +10787,7 @@
         <v>942</v>
       </c>
       <c r="C943" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="944">
@@ -10798,7 +10798,7 @@
         <v>943</v>
       </c>
       <c r="C944" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="945">
@@ -10809,7 +10809,7 @@
         <v>944</v>
       </c>
       <c r="C945" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="946">
@@ -10820,7 +10820,7 @@
         <v>945</v>
       </c>
       <c r="C946" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="947">
@@ -10831,7 +10831,7 @@
         <v>946</v>
       </c>
       <c r="C947" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="948">
@@ -10842,7 +10842,7 @@
         <v>947</v>
       </c>
       <c r="C948" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="949">
@@ -10853,7 +10853,7 @@
         <v>948</v>
       </c>
       <c r="C949" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="950">
@@ -10864,7 +10864,7 @@
         <v>949</v>
       </c>
       <c r="C950" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="951">
@@ -10875,7 +10875,7 @@
         <v>950</v>
       </c>
       <c r="C951" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="952">
@@ -10886,7 +10886,7 @@
         <v>951</v>
       </c>
       <c r="C952" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="953">
@@ -10897,7 +10897,7 @@
         <v>952</v>
       </c>
       <c r="C953" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="954">
@@ -10908,7 +10908,7 @@
         <v>953</v>
       </c>
       <c r="C954" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="955">
@@ -10919,7 +10919,7 @@
         <v>954</v>
       </c>
       <c r="C955" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="956">
@@ -10930,7 +10930,7 @@
         <v>955</v>
       </c>
       <c r="C956" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="957">
@@ -10941,7 +10941,7 @@
         <v>956</v>
       </c>
       <c r="C957" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="958">
@@ -10952,7 +10952,7 @@
         <v>957</v>
       </c>
       <c r="C958" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="959">
@@ -10963,7 +10963,7 @@
         <v>958</v>
       </c>
       <c r="C959" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="960">
@@ -10974,7 +10974,7 @@
         <v>959</v>
       </c>
       <c r="C960" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="961">
@@ -10985,7 +10985,7 @@
         <v>960</v>
       </c>
       <c r="C961" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="962">
@@ -10996,7 +10996,7 @@
         <v>961</v>
       </c>
       <c r="C962" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="963">
@@ -11007,7 +11007,7 @@
         <v>962</v>
       </c>
       <c r="C963" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="964">
@@ -11018,7 +11018,7 @@
         <v>963</v>
       </c>
       <c r="C964" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="965">
@@ -11029,7 +11029,7 @@
         <v>964</v>
       </c>
       <c r="C965" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="966">
@@ -11040,7 +11040,7 @@
         <v>965</v>
       </c>
       <c r="C966" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="967">
@@ -11051,7 +11051,7 @@
         <v>966</v>
       </c>
       <c r="C967" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="968">
@@ -11062,7 +11062,7 @@
         <v>967</v>
       </c>
       <c r="C968" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="969">
@@ -11073,7 +11073,7 @@
         <v>968</v>
       </c>
       <c r="C969" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="970">
@@ -11084,7 +11084,7 @@
         <v>969</v>
       </c>
       <c r="C970" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="971">
@@ -11095,7 +11095,7 @@
         <v>970</v>
       </c>
       <c r="C971" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="972">
@@ -11106,7 +11106,7 @@
         <v>971</v>
       </c>
       <c r="C972" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="973">
@@ -11117,7 +11117,7 @@
         <v>972</v>
       </c>
       <c r="C973" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="974">
@@ -11128,7 +11128,7 @@
         <v>973</v>
       </c>
       <c r="C974" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="975">
@@ -11139,7 +11139,7 @@
         <v>974</v>
       </c>
       <c r="C975" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="976">
@@ -11150,7 +11150,7 @@
         <v>975</v>
       </c>
       <c r="C976" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="977">
@@ -11161,7 +11161,7 @@
         <v>976</v>
       </c>
       <c r="C977" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="978">
@@ -11172,7 +11172,7 @@
         <v>977</v>
       </c>
       <c r="C978" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="979">
@@ -11183,7 +11183,7 @@
         <v>978</v>
       </c>
       <c r="C979" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="980">
@@ -11194,7 +11194,7 @@
         <v>979</v>
       </c>
       <c r="C980" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="981">
@@ -11205,7 +11205,7 @@
         <v>980</v>
       </c>
       <c r="C981" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="982">
@@ -11216,7 +11216,7 @@
         <v>981</v>
       </c>
       <c r="C982" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="983">
@@ -11227,7 +11227,7 @@
         <v>982</v>
       </c>
       <c r="C983" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="984">
@@ -11238,7 +11238,7 @@
         <v>983</v>
       </c>
       <c r="C984" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="985">
@@ -11249,7 +11249,7 @@
         <v>984</v>
       </c>
       <c r="C985" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="986">
@@ -11260,7 +11260,7 @@
         <v>985</v>
       </c>
       <c r="C986" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="987">
@@ -11271,7 +11271,7 @@
         <v>986</v>
       </c>
       <c r="C987" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="988">
@@ -11282,7 +11282,7 @@
         <v>987</v>
       </c>
       <c r="C988" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8752197027206421</v>
       </c>
     </row>
     <row r="989">
@@ -11293,7 +11293,7 @@
         <v>988</v>
       </c>
       <c r="C989" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8734622001647949</v>
       </c>
     </row>
     <row r="990">
@@ -11304,7 +11304,7 @@
         <v>989</v>
       </c>
       <c r="C990" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="991">
@@ -11315,7 +11315,7 @@
         <v>990</v>
       </c>
       <c r="C991" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="992">
@@ -11326,7 +11326,7 @@
         <v>991</v>
       </c>
       <c r="C992" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="993">
@@ -11337,7 +11337,7 @@
         <v>992</v>
       </c>
       <c r="C993" t="n">
-        <v>0.8840070366859436</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="994">
@@ -11348,7 +11348,7 @@
         <v>993</v>
       </c>
       <c r="C994" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="995">
@@ -11359,7 +11359,7 @@
         <v>994</v>
       </c>
       <c r="C995" t="n">
-        <v>0.885764479637146</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="996">
@@ -11370,7 +11370,7 @@
         <v>995</v>
       </c>
       <c r="C996" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="997">
@@ -11381,7 +11381,7 @@
         <v>996</v>
       </c>
       <c r="C997" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="998">
@@ -11392,7 +11392,7 @@
         <v>997</v>
       </c>
       <c r="C998" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8787346482276917</v>
       </c>
     </row>
     <row r="999">
@@ -11403,7 +11403,7 @@
         <v>998</v>
       </c>
       <c r="C999" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.880492091178894</v>
       </c>
     </row>
     <row r="1000">
@@ -11414,7 +11414,7 @@
         <v>999</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.880492091178894</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
     <row r="1001">
@@ -11425,7 +11425,7 @@
         <v>1000</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.8822495341300964</v>
+        <v>0.8769771456718445</v>
       </c>
     </row>
   </sheetData>
